--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ \z\ł"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -59,11 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -138,6 +147,154 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Salsa Cutthroat C Frameset - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'FM2797'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'FM2797'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FM2797'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -497,32 +654,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8567.110000000001</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>8567.110000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
         </is>
       </c>
     </row>
@@ -569,6 +722,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -579,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -640,6 +796,47 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FM2797</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Salsa Cutthroat C Frameset</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>8567.110000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1999</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -651,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -682,8 +879,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>8567.110000000001</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -670,12 +670,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>goldsprintshop.com</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
         </is>
       </c>
     </row>
@@ -813,10 +813,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1999</v>
+        <v>1899.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -825,16 +825,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>goldsprintshop.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>goldsprintshop.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Historia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="FM2797" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="LAUF-CARBONARA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lake MX190-X Wide" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -270,7 +271,155 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Lake MX190-X Wide - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Lake MX190-X Wide'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lake MX190-X Wide'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lake MX190-X Wide'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -586,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -658,10 +807,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8142.4</v>
+        <v>8567.110000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8142.4</v>
+        <v>8567.110000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -670,12 +819,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>goldsprintshop.com</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
+          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
         </is>
       </c>
     </row>
@@ -718,12 +867,51 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -735,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -813,10 +1001,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8142.4</v>
+        <v>8567.110000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1899.9</v>
+        <v>1999</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -825,16 +1013,57 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>goldsprintshop.com</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
+          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>165</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -886,16 +1115,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8142.4</v>
+        <v>8567.110000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>goldsprintshop.com</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
+          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
         </is>
       </c>
     </row>
@@ -945,4 +1174,67 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
 </file>
--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -284,6 +284,127 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Lauf Carbonara fork - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'LAUF-CARBONARA'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'LAUF-CARBONARA'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'LAUF-CARBONARA'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Lake MX190-X Wide - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -420,6 +541,33 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -807,10 +955,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -819,12 +967,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>goldsprintshop.com</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
         </is>
       </c>
     </row>
@@ -841,32 +989,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>4714.27</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4714.27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>fatbikeadventures-store.com</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://fatbikeadventures-store.com/products/lauf-carbonara-fatbike-fork?srsltid=AfmBOor2rhbPi7b08dcfior11nfpLW30UFlIYNyUJy28QAZfWkXu3lC2</t>
         </is>
       </c>
     </row>
@@ -911,7 +1055,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -923,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1001,10 +1146,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="E2" t="n">
-        <v>1999</v>
+        <v>1899.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1013,16 +1158,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>goldsprintshop.com</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1033,19 +1178,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>707.14</v>
+        <v>4714.27</v>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>1100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1054,16 +1199,57 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>fatbikeadventures-store.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
+          <t>https://fatbikeadventures-store.com/products/lauf-carbonara-fatbike-fork?srsltid=AfmBOor2rhbPi7b08dcfior11nfpLW30UFlIYNyUJy28QAZfWkXu3lC2</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>165</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -1115,16 +1301,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8567.110000000001</v>
+        <v>8142.4</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>goldsprintshop.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-cutthroat-c-frameset-rahmenkit-29-black</t>
+          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1171,8 +1357,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>4714.27</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>fatbikeadventures-store.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://fatbikeadventures-store.com/products/lauf-carbonara-fatbike-fork?srsltid=AfmBOor2rhbPi7b08dcfior11nfpLW30UFlIYNyUJy28QAZfWkXu3lC2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8142.4</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8142.4</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -967,12 +967,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>goldsprintshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>8142.4</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>1899.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1158,16 +1158,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>goldsprintshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1301,16 +1301,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>8142.4</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>goldsprintshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.goldsprintshop.com/Salsa-Cutthroat-C-Rahmenset-Black-2025</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4714.27</v>
+        <v>4452.98</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4714.27</v>
+        <v>4452.98</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fatbikeadventures-store.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>https://fatbikeadventures-store.com/products/lauf-carbonara-fatbike-fork?srsltid=AfmBOor2rhbPi7b08dcfior11nfpLW30UFlIYNyUJy28QAZfWkXu3lC2</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -1187,28 +1187,28 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4714.27</v>
+        <v>4452.98</v>
       </c>
       <c r="E3" t="n">
-        <v>1100</v>
+        <v>1190</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fatbikeadventures-store.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://fatbikeadventures-store.com/products/lauf-carbonara-fatbike-fork?srsltid=AfmBOor2rhbPi7b08dcfior11nfpLW30UFlIYNyUJy28QAZfWkXu3lC2</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1364,16 +1364,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4714.27</v>
+        <v>4452.98</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fatbikeadventures-store.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://fatbikeadventures-store.com/products/lauf-carbonara-fatbike-fork?srsltid=AfmBOor2rhbPi7b08dcfior11nfpLW30UFlIYNyUJy28QAZfWkXu3lC2</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -12,6 +12,13 @@
     <sheet name="FM2797" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="LAUF-CARBONARA" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Lake MX190-X Wide" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DT Swiss Fatbike" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DT SWISS 350 12x148" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Canyon S14 VCLS 2.0" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="SRAM GX Eagle Transmission" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SRAM GX Eagle Transmission1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cane Creek 40 IS41-IS52" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -202,6 +209,127 @@
           <val>
             <numRef>
               <f>'FM2797'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Cane Creek 40 IS41/IS52 - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Cane Creek 40 IS41-IS52'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -513,7 +641,760 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>DT Swiss Fatbike - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DT Swiss Fatbike'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DT Swiss Fatbike'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DT Swiss Fatbike'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>DT SWISS 350 12x148 - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DT SWISS 350 12x148'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'DT SWISS 350 12x148'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DT SWISS 350 12x148'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Ritchey WCS Carbon ErgoMax - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Ritchey WCS Carbon ErgoMax'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Canyon S14 VCLS 2.0 - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Canyon S14 VCLS 2.0'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Canyon S14 VCLS 2.0'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Canyon S14 VCLS 2.0'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SRAM GX Eagle Transmission - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'SRAM GX Eagle Transmission'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'SRAM GX Eagle Transmission'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'SRAM GX Eagle Transmission'!$B$2:$B$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SRAM GX Eagle Transmission - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'SRAM GX Eagle Transmission1'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'SRAM GX Eagle Transmission1'!$A$2:$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'SRAM GX Eagle Transmission1'!$B$2:$B$3</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -568,6 +1449,168 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -883,7 +1926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1048,7 +2091,273 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DT Swiss Fatbike</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DT Swiss Fatbike</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>308.53</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>308.53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DT SWISS 350 12x148</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DT SWISS 350 12x148</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>514.24</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>514.24</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/Ritchey/WCS-ErgoMax-31-8-Lenker-p68501/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Canyon S14 VCLS 2.0</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Canyon S14 VCLS 2.0</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>679.99</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>679.99</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-pl/gear/bike-parts/posts-and-clamps/canyon-s13-vcls-27.2mm-cf-seatpost/9100564.html?dwvar_9100564_pv_farbe=BK%2FWH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Cane Creek 40 IS41/IS52</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cane Creek 40 IS41/IS52</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ceneo.pl</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ceneo.pl/46296895</t>
         </is>
       </c>
     </row>
@@ -1057,8 +2366,244 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>249.7</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ceneo.pl</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.ceneo.pl/46296895</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1068,7 +2613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1137,37 +2682,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>249.7</v>
       </c>
       <c r="E2" t="n">
-        <v>2317.5</v>
+        <v>249.7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>ceneo.pl</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.ceneo.pl/46296895</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -1178,37 +2723,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4452.98</v>
+        <v>679.99</v>
       </c>
       <c r="E3" t="n">
-        <v>1190</v>
+        <v>679.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.canyon.com/en-pl/gear/bike-parts/posts-and-clamps/canyon-s13-vcls-27.2mm-cf-seatpost/9100564.html?dwvar_9100564_pv_farbe=BK%2FWH</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -1219,37 +2764,324 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>DT SWISS 350 12x148</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DT SWISS 350 12x148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>514.24</v>
+      </c>
+      <c r="E4" t="n">
+        <v>119.99</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DT Swiss Fatbike</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>DT Swiss Fatbike</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>308.53</v>
+      </c>
+      <c r="E5" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FM2797</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Salsa Cutthroat C Frameset</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>9932.110000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2317.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>4452.98</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Lake MX190-X Wide</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Lake MX190-X Wide</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D8" s="2" t="n">
         <v>707.14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E8" t="n">
         <v>165</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>sport-bittl.com</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="E9" t="n">
+        <v>85.98999999999999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/Ritchey/WCS-ErgoMax-31-8-Lenker-p68501/</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>gocycle.de</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +3268,259 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html?srsltid=AfmBOopCcIXeGqeppniVUaErX3eq_if08HnrPFGDTtWKXofiVmcqqOEV</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>308.53</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>514.24</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>368.53</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/Ritchey/WCS-ErgoMax-31-8-Lenker-p68501/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>679.99</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-pl/gear/bike-parts/posts-and-clamps/canyon-s13-vcls-27.2mm-cf-seatpost/9100564.html?dwvar_9100564_pv_farbe=BK%2FWH</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -16,8 +16,8 @@
     <sheet name="DT SWISS 350 12x148" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Canyon S14 VCLS 2.0" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="SRAM GX Eagle Transmission" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SRAM GX Eagle Transmission1" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GX-T-KIT" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GX-T-CHAIN" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Cane Creek 40 IS41-IS52" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
@@ -1138,7 +1138,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SRAM GX Eagle Transmission - najniższa cena dzienna (PLN)</a:t>
+              <a:t>SRAM GX Eagle Transmission Upgrade Kit - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1152,7 +1152,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'SRAM GX Eagle Transmission'!B1</f>
+              <f>'GX-T-KIT'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -1171,12 +1171,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SRAM GX Eagle Transmission'!$A$2:$A$3</f>
+              <f>'GX-T-KIT'!$A$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SRAM GX Eagle Transmission'!$B$2:$B$3</f>
+              <f>'GX-T-KIT'!$B$2</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1259,7 +1259,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SRAM GX Eagle Transmission - najniższa cena dzienna (PLN)</a:t>
+              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1273,7 +1273,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'SRAM GX Eagle Transmission1'!B1</f>
+              <f>'GX-T-CHAIN'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -1292,12 +1292,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SRAM GX Eagle Transmission1'!$A$2:$A$3</f>
+              <f>'GX-T-CHAIN'!$A$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SRAM GX Eagle Transmission1'!$B$2:$B$3</f>
+              <f>'GX-T-CHAIN'!$B$2</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>368.53</v>
+        <v>1074.05</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>368.53</v>
+        <v>1074.05</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/Ritchey/WCS-ErgoMax-31-8-Lenker-p68501/</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>679.99</v>
+        <v>857.1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>679.99</v>
+        <v>857.1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2243,19 +2243,19 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-pl/gear/bike-parts/posts-and-clamps/canyon-s13-vcls-27.2mm-cf-seatpost/9100564.html?dwvar_9100564_pv_farbe=BK%2FWH</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2264,10 +2264,10 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>29.96</v>
+        <v>1281.42</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>29.96</v>
+        <v>1281.42</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -2276,24 +2276,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>gocycle.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2302,10 +2302,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>29.96</v>
+        <v>128.53</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>29.96</v>
+        <v>128.53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>gocycle.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>249.7</v>
+        <v>239.99</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>249.7</v>
+        <v>239.99</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ceneo.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.ceneo.pl/46296895</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2422,36 +2422,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>29.96</v>
+        <v>1281.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gocycle.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>gocycle.de</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2505,36 +2485,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>29.96</v>
+        <v>128.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>gocycle.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>gocycle.de</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -2588,16 +2548,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>249.7</v>
+        <v>239.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ceneo.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.ceneo.pl/46296895</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
@@ -2691,10 +2651,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>249.7</v>
+        <v>239.99</v>
       </c>
       <c r="E2" t="n">
-        <v>249.7</v>
+        <v>239.99</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -2703,16 +2663,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ceneo.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.ceneo.pl/46296895</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2732,14 +2692,14 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>679.99</v>
+        <v>857.1</v>
       </c>
       <c r="E3" t="n">
-        <v>679.99</v>
+        <v>199.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2749,11 +2709,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-pl/gear/bike-parts/posts-and-clamps/canyon-s13-vcls-27.2mm-cf-seatpost/9100564.html?dwvar_9100564_pv_farbe=BK%2FWH</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -2794,7 +2754,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2887,37 +2847,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>4452.98</v>
+        <v>128.53</v>
       </c>
       <c r="E7" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -2928,19 +2888,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>707.14</v>
+        <v>1281.42</v>
       </c>
       <c r="E8" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2949,16 +2909,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -2969,37 +2929,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>368.53</v>
+        <v>4452.98</v>
       </c>
       <c r="E9" t="n">
-        <v>85.98999999999999</v>
+        <v>1190</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/Ritchey/WCS-ErgoMax-31-8-Lenker-p68501/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3010,19 +2970,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>29.96</v>
+        <v>707.14</v>
       </c>
       <c r="E10" t="n">
-        <v>6.99</v>
+        <v>165</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3031,16 +2991,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>gocycle.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -3051,37 +3011,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>29.96</v>
+        <v>1074.05</v>
       </c>
       <c r="E11" t="n">
-        <v>6.99</v>
+        <v>230.34</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>gocycle.de</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.gocycle.de/a.php/shop/gocycle/lang/en/a/69562/kw/SRAM-GX-Transmission-T-Type-1-x-12-Upgrade-Kit-Eagle-70-90-Schaltgruppe/</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3448,16 +3408,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>368.53</v>
+        <v>1074.05</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/Ritchey/WCS-ErgoMax-31-8-Lenker-p68501/</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3471,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>679.99</v>
+        <v>857.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3520,7 +3480,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-pl/gear/bike-parts/posts-and-clamps/canyon-s13-vcls-27.2mm-cf-seatpost/9100564.html?dwvar_9100564_pv_farbe=BK%2FWH</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -19,6 +19,7 @@
     <sheet name="GX-T-KIT" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="GX-T-CHAIN" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Cane Creek 40 IS41-IS52" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ROCK SHOX SID" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -203,12 +204,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2</f>
+              <f>'FM2797'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2</f>
+              <f>'FM2797'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -324,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -445,12 +446,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -566,12 +567,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -687,12 +688,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -808,12 +809,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -929,12 +930,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1050,12 +1051,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1171,12 +1172,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2</f>
+              <f>'GX-T-KIT'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2</f>
+              <f>'GX-T-KIT'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1292,12 +1293,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1926,7 +1927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1994,11 +1995,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>9935.59</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2032,11 +2033,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4452.98</v>
+        <v>4467.26</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>4452.98</v>
@@ -2070,11 +2071,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>707.14</v>
+        <v>707.39</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>707.14</v>
@@ -2108,11 +2109,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>308.53</v>
+        <v>308.64</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>308.53</v>
@@ -2146,11 +2147,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>514.24</v>
+        <v>514.42</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>514.24</v>
@@ -2184,18 +2185,18 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1074.05</v>
+        <v>1073.61</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1074.05</v>
+        <v>1073.61</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2222,11 +2223,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>857.1</v>
+        <v>857.4</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>857.1</v>
@@ -2260,11 +2261,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1281.42</v>
+        <v>1281.87</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1281.42</v>
@@ -2298,11 +2299,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>128.53</v>
+        <v>128.57</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2336,7 +2337,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -2358,6 +2359,48 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2430,6 +2473,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1281.87</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -2447,7 +2510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2493,6 +2556,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>128.57</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alutech-cycles.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
@@ -2510,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2561,9 +2644,71 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2573,7 +2718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2678,42 +2823,42 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>857.1</v>
+        <v>239.99</v>
       </c>
       <c r="E3" t="n">
-        <v>199.99</v>
+        <v>239.99</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -2724,19 +2869,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>514.24</v>
+        <v>857.1</v>
       </c>
       <c r="E4" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -2745,39 +2890,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>308.53</v>
+        <v>857.4</v>
       </c>
       <c r="E5" t="n">
-        <v>71.98999999999999</v>
+        <v>199.99</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -2786,12 +2931,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -2806,19 +2951,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>514.24</v>
       </c>
       <c r="E6" t="n">
-        <v>2317.5</v>
+        <v>119.99</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2827,39 +2972,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>128.53</v>
+        <v>514.42</v>
       </c>
       <c r="E7" t="n">
-        <v>29.99</v>
+        <v>119.99</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2868,16 +3013,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -2888,19 +3033,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1281.42</v>
+        <v>308.53</v>
       </c>
       <c r="E8" t="n">
-        <v>299</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -2909,57 +3054,57 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4452.98</v>
+        <v>308.64</v>
       </c>
       <c r="E9" t="n">
-        <v>1190</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -2970,19 +3115,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>707.14</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>165</v>
+        <v>2317.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -2991,56 +3136,466 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FM2797</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Salsa Cutthroat C Frameset</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>9935.59</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2317.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GX-T-CHAIN</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>128.53</v>
+      </c>
+      <c r="E12" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>alutech-cycles.com</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GX-T-CHAIN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>128.57</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>alutech-cycles.com</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GX-T-KIT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1281.42</v>
+      </c>
+      <c r="E14" t="n">
+        <v>299</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GX-T-KIT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1281.87</v>
+      </c>
+      <c r="E15" t="n">
+        <v>299</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>4452.98</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>4467.26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>165</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>707.39</v>
+      </c>
+      <c r="E19" t="n">
+        <v>165</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D20" s="2" t="n">
         <v>1074.05</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E20" t="n">
         <v>230.34</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I11" t="n">
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E21" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3055,7 +3610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3101,6 +3656,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>9935.59</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -3118,7 +3693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3164,6 +3739,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>4467.26</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
@@ -3181,7 +3776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3227,6 +3822,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>707.39</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
@@ -3244,7 +3859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3290,6 +3905,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>308.64</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
@@ -3307,7 +3942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3353,6 +3988,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>514.42</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
@@ -3370,7 +4025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3416,6 +4071,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -3433,7 +4108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3484,6 +4159,26 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>857.4</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -20,6 +20,7 @@
     <sheet name="GX-T-CHAIN" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Cane Creek 40 IS41-IS52" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="ROCK SHOX SID" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Lake MX242" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,12 +205,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$3</f>
+              <f>'FM2797'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$3</f>
+              <f>'FM2797'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -325,12 +326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$3</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$3</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -446,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$3</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$3</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -567,12 +568,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$3</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$3</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -688,12 +689,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$3</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$3</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -809,12 +810,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$3</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$3</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -930,12 +931,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$3</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$3</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1051,12 +1052,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$3</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$3</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1172,12 +1173,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$3</f>
+              <f>'GX-T-KIT'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$3</f>
+              <f>'GX-T-KIT'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1293,12 +1294,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$3</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$3</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1927,7 +1928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1995,7 +1996,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -2033,7 +2034,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -2071,7 +2072,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -2109,7 +2110,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -2147,7 +2148,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -2185,7 +2186,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -2223,7 +2224,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -2261,7 +2262,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -2299,7 +2300,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -2337,7 +2338,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -2399,6 +2400,48 @@
         </is>
       </c>
       <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2427,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2493,6 +2536,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1281.87</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -2510,7 +2573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2576,6 +2639,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>128.57</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>alutech-cycles.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
@@ -2593,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2659,6 +2742,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
@@ -2712,13 +2815,55 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2864,48 +3009,48 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>857.1</v>
+        <v>239.99</v>
       </c>
       <c r="E4" t="n">
-        <v>199.99</v>
+        <v>239.99</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2919,7 +3064,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E5" t="n">
         <v>199.99</v>
@@ -2946,24 +3091,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>514.24</v>
+        <v>857.4</v>
       </c>
       <c r="E6" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2972,39 +3117,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>514.42</v>
+        <v>857.4</v>
       </c>
       <c r="E7" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3013,16 +3158,16 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -3033,19 +3178,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>308.53</v>
+        <v>514.24</v>
       </c>
       <c r="E8" t="n">
-        <v>71.98999999999999</v>
+        <v>119.99</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3054,16 +3199,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -3074,19 +3219,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>308.64</v>
+        <v>514.42</v>
       </c>
       <c r="E9" t="n">
-        <v>71.98999999999999</v>
+        <v>119.99</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3095,39 +3240,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>514.42</v>
       </c>
       <c r="E10" t="n">
-        <v>2317.5</v>
+        <v>119.99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3136,39 +3281,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>9935.59</v>
+        <v>308.53</v>
       </c>
       <c r="E11" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3177,39 +3322,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>128.53</v>
+        <v>308.64</v>
       </c>
       <c r="E12" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3218,39 +3363,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>128.57</v>
+        <v>308.64</v>
       </c>
       <c r="E13" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3259,16 +3404,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3279,19 +3424,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1281.42</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>299</v>
+        <v>2317.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3300,16 +3445,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -3320,19 +3465,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1281.87</v>
+        <v>9935.59</v>
       </c>
       <c r="E15" t="n">
-        <v>299</v>
+        <v>2317.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3341,53 +3486,53 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4452.98</v>
+        <v>9935.59</v>
       </c>
       <c r="E16" t="n">
-        <v>1190</v>
+        <v>2317.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -3397,65 +3542,65 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>4467.26</v>
+        <v>128.53</v>
       </c>
       <c r="E17" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>707.14</v>
+        <v>128.57</v>
       </c>
       <c r="E18" t="n">
-        <v>165</v>
+        <v>29.99</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3464,39 +3609,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>707.39</v>
+        <v>128.57</v>
       </c>
       <c r="E19" t="n">
-        <v>165</v>
+        <v>29.99</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3505,16 +3650,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -3525,37 +3670,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1074.05</v>
+        <v>1281.42</v>
       </c>
       <c r="E20" t="n">
-        <v>230.34</v>
+        <v>299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -3566,36 +3711,446 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>GX-T-KIT</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>1281.87</v>
+      </c>
+      <c r="E21" t="n">
+        <v>299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GX-T-KIT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1281.87</v>
+      </c>
+      <c r="E22" t="n">
+        <v>299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>4452.98</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>4467.26</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>4467.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="E26" t="n">
+        <v>165</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>707.39</v>
+      </c>
+      <c r="E27" t="n">
+        <v>165</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>707.39</v>
+      </c>
+      <c r="E28" t="n">
+        <v>165</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n">
+      <c r="D29" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>1073.61</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E30" t="n">
         <v>230.34</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E31" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3610,7 +4165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3676,6 +4231,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>9935.59</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -3693,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3759,6 +4334,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>4467.26</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
@@ -3776,7 +4371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3842,6 +4437,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>707.39</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
@@ -3859,7 +4474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3925,6 +4540,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>308.64</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
@@ -3942,7 +4577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4008,6 +4643,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>514.42</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
@@ -4025,7 +4680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4091,6 +4746,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -4108,7 +4783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4179,6 +4854,26 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>857.4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2152,24 +2152,24 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>514.42</v>
+        <v>398.28</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>514.24</v>
+        <v>398.28</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>514.42</v>
+        <v>398.28</v>
       </c>
       <c r="E10" t="n">
-        <v>119.99</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3281,16 +3281,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
@@ -4028,7 +4028,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -4655,16 +4655,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>514.42</v>
+        <v>398.28</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9935.59</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4467.26</v>
+        <v>4471.19</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>4452.98</v>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>707.39</v>
+        <v>708.48</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>707.14</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>308.64</v>
+        <v>309.11</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>308.53</v>
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>398.28</v>
+        <v>398.89</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>398.28</v>
+        <v>398.89</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2190,14 +2190,14 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1073.61</v>
+        <v>1073.29</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1073.61</v>
+        <v>1073.29</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>857.4</v>
+        <v>858.72</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>857.1</v>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1281.87</v>
+        <v>1283.85</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1281.42</v>
@@ -2304,7 +2304,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>128.57</v>
+        <v>128.77</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1281.87</v>
+        <v>1283.85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>128.57</v>
+        <v>128.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>857.4</v>
+        <v>858.72</v>
       </c>
       <c r="E7" t="n">
         <v>199.99</v>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>398.28</v>
+        <v>398.89</v>
       </c>
       <c r="E10" t="n">
         <v>92.90000000000001</v>
@@ -3392,7 +3392,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>308.64</v>
+        <v>309.11</v>
       </c>
       <c r="E13" t="n">
         <v>71.98999999999999</v>
@@ -3515,7 +3515,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9935.59</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E16" t="n">
         <v>2317.5</v>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>128.57</v>
+        <v>128.77</v>
       </c>
       <c r="E19" t="n">
         <v>29.99</v>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1281.87</v>
+        <v>1283.85</v>
       </c>
       <c r="E22" t="n">
         <v>299</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4467.26</v>
+        <v>4471.19</v>
       </c>
       <c r="E25" t="n">
         <v>1190</v>
@@ -4007,7 +4007,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>707.39</v>
+        <v>708.48</v>
       </c>
       <c r="E28" t="n">
         <v>165</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1073.61</v>
+        <v>1073.29</v>
       </c>
       <c r="E31" t="n">
         <v>230.34</v>
@@ -4243,7 +4243,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9935.59</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4346,7 +4346,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>4467.26</v>
+        <v>4471.19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>707.39</v>
+        <v>708.48</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>308.64</v>
+        <v>309.11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>398.28</v>
+        <v>398.89</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1073.61</v>
+        <v>1073.29</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>857.4</v>
+        <v>858.72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -332,6 +332,248 @@
           <val>
             <numRef>
               <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$4</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ROCK SHOX SID SL Select+ - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'ROCK SHOX SID'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ROCK SHOX SID'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ROCK SHOX SID'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Lake MX242 - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Lake MX242'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Lake MX242'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Lake MX242'!$B$2</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1423,6 +1665,60 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -2376,32 +2672,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1455.6</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1455.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/RockShox/ZEB-Select-RC2-A3-DebonAir-Boost-29-suspension-fork-for-e-MTBs-OE-p251308/?v=64157-black</t>
         </is>
       </c>
     </row>
@@ -2418,32 +2710,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>463.69</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>463.69</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>alltricks.de</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.de/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -2459,6 +2747,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2779,7 +3069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2810,8 +3100,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1455.6</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/RockShox/ZEB-Select-RC2-A3-DebonAir-Boost-29-suspension-fork-for-e-MTBs-OE-p251308/?v=64157-black</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2821,7 +3132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2852,8 +3163,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>463.69</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>alltricks.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.de/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2863,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3044,7 +3376,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -4034,79 +4366,79 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1074.05</v>
+        <v>463.69</v>
       </c>
       <c r="E29" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.de</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.de/C-1586355-lake</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1073.61</v>
+        <v>1455.6</v>
       </c>
       <c r="E30" t="n">
-        <v>230.34</v>
+        <v>339</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/en/RockShox/ZEB-Select-RC2-A3-DebonAir-Boost-29-suspension-fork-for-e-MTBs-OE-p251308/?v=64157-black</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4116,7 +4448,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4130,7 +4462,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1073.29</v>
+        <v>1074.05</v>
       </c>
       <c r="E31" t="n">
         <v>230.34</v>
@@ -4151,6 +4483,88 @@
         </is>
       </c>
       <c r="I31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E32" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E33" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -402,127 +402,6 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>ROCK SHOX SID SL Select+ - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'ROCK SHOX SID'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'ROCK SHOX SID'!$A$2</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'ROCK SHOX SID'!$B$2</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1692,33 +1571,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7920000" cy="3240000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -2672,28 +2524,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>1455.6</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1455.6</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bike-components.de/en/RockShox/ZEB-Select-RC2-A3-DebonAir-Boost-29-suspension-fork-for-e-MTBs-OE-p251308/?v=64157-black</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2714,10 +2570,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>463.69</v>
+        <v>1288.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>463.69</v>
+        <v>1288.1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2726,12 +2582,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>alltricks.de</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.alltricks.de/C-1586355-lake</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
     </row>
@@ -2747,8 +2603,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3069,7 +2924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3100,29 +2955,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1455.6</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>bike-components.de</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.bike-components.de/en/RockShox/ZEB-Select-RC2-A3-DebonAir-Boost-29-suspension-fork-for-e-MTBs-OE-p251308/?v=64157-black</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3170,16 +3004,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>463.69</v>
+        <v>1288.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alltricks.de</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.alltricks.de/C-1586355-lake</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4380,10 +4214,10 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>463.69</v>
+        <v>1288.1</v>
       </c>
       <c r="E29" t="n">
-        <v>107.99</v>
+        <v>299.99</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4392,53 +4226,53 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>alltricks.de</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.alltricks.de/C-1586355-lake</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1455.6</v>
+        <v>1074.05</v>
       </c>
       <c r="E30" t="n">
-        <v>339</v>
+        <v>230.34</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/RockShox/ZEB-Select-RC2-A3-DebonAir-Boost-29-suspension-fork-for-e-MTBs-OE-p251308/?v=64157-black</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4448,7 +4282,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4462,7 +4296,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1074.05</v>
+        <v>1073.61</v>
       </c>
       <c r="E31" t="n">
         <v>230.34</v>
@@ -4489,7 +4323,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4503,7 +4337,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1073.61</v>
+        <v>1073.29</v>
       </c>
       <c r="E32" t="n">
         <v>230.34</v>
@@ -4524,47 +4358,6 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>1073.29</v>
-      </c>
-      <c r="E33" t="n">
-        <v>230.34</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>CHF</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>bikeshopzizers.ch</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -402,6 +402,127 @@
 </file>
 
 <file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>ROCK SHOX SID SL Select+ - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'ROCK SHOX SID'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ROCK SHOX SID'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ROCK SHOX SID'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1571,6 +1692,33 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -2524,32 +2672,28 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2747,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2924,7 +3069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2955,8 +3100,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3029,7 +3195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4241,38 +4407,38 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1074.05</v>
+        <v>1799</v>
       </c>
       <c r="E30" t="n">
-        <v>230.34</v>
+        <v>1799</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -4282,7 +4448,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4296,7 +4462,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1073.61</v>
+        <v>1074.05</v>
       </c>
       <c r="E31" t="n">
         <v>230.34</v>
@@ -4323,7 +4489,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4337,7 +4503,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1073.29</v>
+        <v>1073.61</v>
       </c>
       <c r="E32" t="n">
         <v>230.34</v>
@@ -4358,6 +4524,47 @@
         </is>
       </c>
       <c r="I32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E33" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
         <v>1</v>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -205,12 +205,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$4</f>
+              <f>'FM2797'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$4</f>
+              <f>'FM2797'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -326,12 +326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$4</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$4</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -568,12 +568,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2</f>
+              <f>'Lake MX242'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2</f>
+              <f>'Lake MX242'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -689,12 +689,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$4</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$4</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -810,12 +810,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$4</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$4</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -931,12 +931,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$4</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$4</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1052,12 +1052,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$4</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$4</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1173,12 +1173,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$4</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$4</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1294,12 +1294,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$4</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$4</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1415,12 +1415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$4</f>
+              <f>'GX-T-KIT'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$4</f>
+              <f>'GX-T-KIT'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1536,12 +1536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$4</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$4</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -2558,7 +2558,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -2760,7 +2760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2846,6 +2846,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1283.85</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -2863,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2949,6 +2969,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>128.77</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>alutech-cycles.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
@@ -2966,7 +3006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3052,6 +3092,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
@@ -3069,7 +3129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3115,6 +3175,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
@@ -3132,7 +3212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3178,6 +3258,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1288.1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
@@ -3195,7 +3295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3382,48 +3482,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>857.1</v>
+        <v>239.99</v>
       </c>
       <c r="E5" t="n">
-        <v>199.99</v>
+        <v>239.99</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3437,7 +3537,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E6" t="n">
         <v>199.99</v>
@@ -3464,7 +3564,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3478,7 +3578,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E7" t="n">
         <v>199.99</v>
@@ -3505,24 +3605,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>514.24</v>
+        <v>858.72</v>
       </c>
       <c r="E8" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -3531,39 +3631,39 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>514.42</v>
+        <v>858.72</v>
       </c>
       <c r="E9" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3572,22 +3672,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3601,10 +3701,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E10" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3613,39 +3713,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>308.53</v>
+        <v>514.42</v>
       </c>
       <c r="E11" t="n">
-        <v>71.98999999999999</v>
+        <v>119.99</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3654,39 +3754,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>308.64</v>
+        <v>398.89</v>
       </c>
       <c r="E12" t="n">
-        <v>71.98999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3695,39 +3795,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>309.11</v>
+        <v>398.89</v>
       </c>
       <c r="E13" t="n">
-        <v>71.98999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3736,16 +3836,16 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -3756,19 +3856,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>308.53</v>
       </c>
       <c r="E14" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3777,16 +3877,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -3797,19 +3897,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>9935.59</v>
+        <v>308.64</v>
       </c>
       <c r="E15" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3818,16 +3918,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -3838,19 +3938,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>309.11</v>
       </c>
       <c r="E16" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3859,39 +3959,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>128.53</v>
+        <v>309.11</v>
       </c>
       <c r="E17" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -3900,39 +4000,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>128.57</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -3941,39 +4041,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>128.77</v>
+        <v>9935.59</v>
       </c>
       <c r="E19" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -3982,39 +4082,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1281.42</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>299</v>
+        <v>2317.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4023,39 +4123,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1281.87</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>299</v>
+        <v>2317.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4064,39 +4164,39 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1283.85</v>
+        <v>128.53</v>
       </c>
       <c r="E22" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4105,139 +4205,139 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>4452.98</v>
+        <v>128.57</v>
       </c>
       <c r="E23" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>4467.26</v>
+        <v>128.77</v>
       </c>
       <c r="E24" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>4471.19</v>
+        <v>128.77</v>
       </c>
       <c r="E25" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -4248,19 +4348,19 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>707.14</v>
+        <v>1281.42</v>
       </c>
       <c r="E26" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4269,16 +4369,16 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -4289,19 +4389,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>707.39</v>
+        <v>1281.87</v>
       </c>
       <c r="E27" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4310,16 +4410,16 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
@@ -4330,19 +4430,19 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>708.48</v>
+        <v>1283.85</v>
       </c>
       <c r="E28" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4351,39 +4451,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1288.1</v>
+        <v>1283.85</v>
       </c>
       <c r="E29" t="n">
-        <v>299.99</v>
+        <v>299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4392,179 +4492,671 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1799</v>
+        <v>4452.98</v>
       </c>
       <c r="E30" t="n">
-        <v>1799</v>
+        <v>1190</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1074.05</v>
+        <v>4467.26</v>
       </c>
       <c r="E31" t="n">
-        <v>230.34</v>
+        <v>1190</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1073.61</v>
+        <v>4471.19</v>
       </c>
       <c r="E32" t="n">
-        <v>230.34</v>
+        <v>1190</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LAUF-CARBONARA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Lauf Carbonara fork</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>4471.19</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1190</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>707.14</v>
+      </c>
+      <c r="E34" t="n">
+        <v>165</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>707.39</v>
+      </c>
+      <c r="E35" t="n">
+        <v>165</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>708.48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>165</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>708.48</v>
+      </c>
+      <c r="E37" t="n">
+        <v>165</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1288.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>1288.1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D33" s="2" t="n">
+      <c r="D42" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E42" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E43" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>1073.29</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E44" t="n">
         <v>230.34</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I33" t="n">
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E45" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4579,7 +5171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4665,6 +5257,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>9950.879999999999</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -4682,7 +5294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4768,6 +5380,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>4471.19</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
@@ -4785,7 +5417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4871,6 +5503,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>708.48</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
@@ -4888,7 +5540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4974,6 +5626,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>309.11</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
@@ -4991,7 +5663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5077,6 +5749,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>398.89</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
@@ -5094,7 +5786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5180,6 +5872,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -5197,7 +5909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5288,6 +6000,26 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>858.72</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4471.19</v>
+        <v>4492.85</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>4452.98</v>
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>708.48</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>707.14</v>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>309.11</v>
+        <v>310.13</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>308.53</v>
@@ -2448,7 +2448,7 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>398.89</v>
+        <v>400.21</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>398.89</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1073.29</v>
+        <v>1076.61</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1073.29</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>858.72</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>857.1</v>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1283.85</v>
+        <v>1288.09</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1281.42</v>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>128.77</v>
+        <v>129.2</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>239.99</v>
+        <v>253.96</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>239.99</v>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>maciag-offroad.de</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://www.maciag-offroad.de/cane-creek-steuersatz-40-is41-28-6-is52-40-short-tapered-sid88363.html</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1799</v>
+        <v>2580.49</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1799</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>nanobike.de</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://nanobike.de/en/Rock-Shox-SID-SL-Select-Charger-RL-3P-29-Suspension-Fork-black-110-mm</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1288.1</v>
+        <v>1292.36</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1288.1</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1283.85</v>
+        <v>1288.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>128.77</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>239.99</v>
+        <v>253.96</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>maciag-offroad.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://www.maciag-offroad.de/cane-creek-steuersatz-40-is41-28-6-is52-40-short-tapered-sid88363.html</t>
         </is>
       </c>
     </row>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1799</v>
+        <v>2580.49</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>nanobike.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://nanobike.de/en/Rock-Shox-SID-SL-Select-Charger-RL-3P-29-Suspension-Fork-black-110-mm</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1288.1</v>
+        <v>1292.36</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3496,24 +3496,24 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>239.99</v>
+        <v>253.96</v>
       </c>
       <c r="E5" t="n">
-        <v>239.99</v>
+        <v>58.95</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>maciag-offroad.de</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://www.maciag-offroad.de/cane-creek-steuersatz-40-is41-28-6-is52-40-short-tapered-sid88363.html</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -3660,7 +3660,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>858.72</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E9" t="n">
         <v>199.99</v>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>398.89</v>
+        <v>400.21</v>
       </c>
       <c r="E13" t="n">
         <v>92.90000000000001</v>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>309.11</v>
+        <v>310.13</v>
       </c>
       <c r="E17" t="n">
         <v>71.98999999999999</v>
@@ -4152,7 +4152,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E21" t="n">
         <v>2317.5</v>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>128.77</v>
+        <v>129.2</v>
       </c>
       <c r="E25" t="n">
         <v>29.99</v>
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1283.85</v>
+        <v>1288.09</v>
       </c>
       <c r="E29" t="n">
         <v>299</v>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4471.19</v>
+        <v>4492.85</v>
       </c>
       <c r="E33" t="n">
         <v>1190</v>
@@ -4665,7 +4665,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -4808,7 +4808,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>708.48</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E37" t="n">
         <v>165</v>
@@ -4890,7 +4890,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1288.1</v>
+        <v>1292.36</v>
       </c>
       <c r="E39" t="n">
         <v>299.99</v>
@@ -4911,7 +4911,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -4972,28 +4972,28 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1799</v>
+        <v>2580.49</v>
       </c>
       <c r="E41" t="n">
-        <v>1799</v>
+        <v>599</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>nanobike.de</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://nanobike.de/en/Rock-Shox-SID-SL-Select-Charger-RL-3P-29-Suspension-Fork-black-110-mm</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1073.29</v>
+        <v>1076.61</v>
       </c>
       <c r="E45" t="n">
         <v>230.34</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4471.19</v>
+        <v>4492.85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5515,7 +5515,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>708.48</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>309.11</v>
+        <v>310.13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>398.89</v>
+        <v>400.21</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1073.29</v>
+        <v>1076.61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>858.72</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>253.96</v>
+        <v>239.99</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>239.99</v>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>maciag-offroad.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.maciag-offroad.de/cane-creek-steuersatz-40-is41-28-6-is52-40-short-tapered-sid88363.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2580.49</v>
+        <v>1799</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1799</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>nanobike.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://nanobike.de/en/Rock-Shox-SID-SL-Select-Charger-RL-3P-29-Suspension-Fork-black-110-mm</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -3104,16 +3104,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>253.96</v>
+        <v>239.99</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>maciag-offroad.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.maciag-offroad.de/cane-creek-steuersatz-40-is41-28-6-is52-40-short-tapered-sid88363.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
@@ -3187,16 +3187,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2580.49</v>
+        <v>1799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nanobike.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://nanobike.de/en/Rock-Shox-SID-SL-Select-Charger-RL-3P-29-Suspension-Fork-black-110-mm</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -3496,28 +3496,28 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>253.96</v>
+        <v>239.99</v>
       </c>
       <c r="E5" t="n">
-        <v>58.95</v>
+        <v>239.99</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>maciag-offroad.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.maciag-offroad.de/cane-creek-steuersatz-40-is41-28-6-is52-40-short-tapered-sid88363.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -4972,28 +4972,28 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>2580.49</v>
+        <v>1799</v>
       </c>
       <c r="E41" t="n">
-        <v>599</v>
+        <v>1799</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>nanobike.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://nanobike.de/en/Rock-Shox-SID-SL-Select-Charger-RL-3P-29-Suspension-Fork-black-110-mm</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2731,7 +2731,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -4907,11 +4907,11 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>129.2</v>
+        <v>159.35</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
         </is>
       </c>
     </row>
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>129.2</v>
+        <v>159.35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>129.2</v>
+        <v>159.35</v>
       </c>
       <c r="E25" t="n">
-        <v>29.99</v>
+        <v>36.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4328,16 +4328,16 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>159.35</v>
+        <v>129.2</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>159.35</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>159.35</v>
+        <v>129.2</v>
       </c>
       <c r="E25" t="n">
-        <v>36.99</v>
+        <v>29.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4328,16 +4328,16 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -3517,7 +3517,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -4337,7 +4337,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>776.86</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>707.14</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>varuste.net</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
         </is>
       </c>
     </row>
@@ -2448,14 +2448,14 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>400.21</v>
+        <v>227.89</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>398.89</v>
+        <v>227.89</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>129.2</v>
+        <v>159.35</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
         </is>
       </c>
     </row>
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>129.2</v>
+        <v>159.35</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
         </is>
       </c>
     </row>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>400.21</v>
+        <v>227.89</v>
       </c>
       <c r="E13" t="n">
-        <v>92.90000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3841,11 +3841,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>129.2</v>
+        <v>159.35</v>
       </c>
       <c r="E25" t="n">
-        <v>29.99</v>
+        <v>36.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4328,16 +4328,16 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>776.86</v>
       </c>
       <c r="E37" t="n">
-        <v>165</v>
+        <v>180.33</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4820,16 +4820,16 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>varuste.net</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -5515,16 +5515,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>776.86</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>varuste.net</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>400.21</v>
+        <v>227.89</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2372,7 +2372,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>776.86</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>707.14</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>varuste.net</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>159.35</v>
+        <v>129.2</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2612,12 +2612,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -2981,16 +2981,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>159.35</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>159.35</v>
+        <v>129.2</v>
       </c>
       <c r="E25" t="n">
-        <v>36.99</v>
+        <v>29.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4328,16 +4328,16 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/SRAM/GX-Eagle-Transmission-12-fach-PowerLock-T-Type-Kette-p90547/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -4808,10 +4808,10 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>776.86</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>180.33</v>
+        <v>165</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4820,16 +4820,16 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>varuste.net</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -5515,16 +5515,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>776.86</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>varuste.net</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -205,12 +205,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$5</f>
+              <f>'FM2797'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$5</f>
+              <f>'FM2797'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -326,12 +326,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$5</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$5</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -447,12 +447,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$3</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$3</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -568,12 +568,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$3</f>
+              <f>'Lake MX242'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$3</f>
+              <f>'Lake MX242'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -689,12 +689,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$5</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$5</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -810,12 +810,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$5</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$5</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -931,12 +931,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$5</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$5</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1052,12 +1052,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$5</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$5</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1173,12 +1173,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$5</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$5</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1294,12 +1294,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$5</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$5</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1415,12 +1415,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$5</f>
+              <f>'GX-T-KIT'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$5</f>
+              <f>'GX-T-KIT'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1536,12 +1536,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$5</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$5</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2292,11 +2292,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>9981.24</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4492.85</v>
+        <v>4485.35</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>4452.98</v>
@@ -2368,11 +2368,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>776.66</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>707.14</v>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>varuste.net</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
         </is>
       </c>
     </row>
@@ -2406,11 +2406,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>310.13</v>
+        <v>310.05</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>308.53</v>
@@ -2444,18 +2444,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>227.89</v>
+        <v>227.84</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>227.89</v>
+        <v>227.84</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2482,11 +2482,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1076.61</v>
+        <v>1075.73</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>1073.29</v>
@@ -2520,11 +2520,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>861.34</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>857.1</v>
@@ -2558,11 +2558,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1288.09</v>
+        <v>1287.76</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1281.42</v>
@@ -2596,11 +2596,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>129.2</v>
+        <v>129.16</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>128.53</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -2710,18 +2710,18 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1292.36</v>
+        <v>1112.47</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1288.1</v>
+        <v>1112.47</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2760,7 +2760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2866,6 +2866,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1287.76</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -2883,7 +2903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2989,6 +3009,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>129.16</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>alutech-cycles.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
@@ -3006,7 +3046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3112,6 +3152,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
@@ -3129,7 +3189,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3195,6 +3255,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
@@ -3212,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3278,6 +3358,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -3295,7 +3395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3523,48 +3623,48 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>857.1</v>
+        <v>239.99</v>
       </c>
       <c r="E6" t="n">
-        <v>199.99</v>
+        <v>239.99</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3578,7 +3678,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E7" t="n">
         <v>199.99</v>
@@ -3605,7 +3705,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3619,7 +3719,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E8" t="n">
         <v>199.99</v>
@@ -3646,7 +3746,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3660,7 +3760,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E9" t="n">
         <v>199.99</v>
@@ -3687,24 +3787,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>514.24</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3713,39 +3813,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>514.42</v>
+        <v>861.34</v>
       </c>
       <c r="E11" t="n">
-        <v>119.99</v>
+        <v>199.99</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3754,22 +3854,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3783,10 +3883,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E12" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -3795,22 +3895,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3824,10 +3924,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E13" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3836,39 +3936,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>308.53</v>
+        <v>398.89</v>
       </c>
       <c r="E14" t="n">
-        <v>71.98999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3877,39 +3977,39 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>308.64</v>
+        <v>227.89</v>
       </c>
       <c r="E15" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -3918,39 +4018,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>309.11</v>
+        <v>227.84</v>
       </c>
       <c r="E16" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -3959,22 +4059,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3988,7 +4088,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E17" t="n">
         <v>71.98999999999999</v>
@@ -4015,24 +4115,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>308.64</v>
       </c>
       <c r="E18" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4041,39 +4141,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9935.59</v>
+        <v>309.11</v>
       </c>
       <c r="E19" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4082,39 +4182,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>310.13</v>
       </c>
       <c r="E20" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -4123,39 +4223,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>310.05</v>
       </c>
       <c r="E21" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -4164,16 +4264,16 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -4184,19 +4284,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>128.53</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4205,16 +4305,16 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4225,19 +4325,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>128.57</v>
+        <v>9935.59</v>
       </c>
       <c r="E23" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4246,16 +4346,16 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -4266,19 +4366,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>128.77</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4287,16 +4387,16 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4307,19 +4407,19 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>129.2</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4328,39 +4428,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1281.42</v>
+        <v>9981.24</v>
       </c>
       <c r="E26" t="n">
-        <v>299</v>
+        <v>2317.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4369,39 +4469,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1281.87</v>
+        <v>128.53</v>
       </c>
       <c r="E27" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4410,39 +4510,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1283.85</v>
+        <v>128.57</v>
       </c>
       <c r="E28" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4451,39 +4551,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1288.09</v>
+        <v>128.77</v>
       </c>
       <c r="E29" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4492,203 +4592,203 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>4452.98</v>
+        <v>129.2</v>
       </c>
       <c r="E30" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4467.26</v>
+        <v>129.16</v>
       </c>
       <c r="E31" t="n">
-        <v>1190</v>
+        <v>29.99</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>4471.19</v>
+        <v>1281.42</v>
       </c>
       <c r="E32" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>4492.85</v>
+        <v>1281.87</v>
       </c>
       <c r="E33" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>707.14</v>
+        <v>1283.85</v>
       </c>
       <c r="E34" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4697,39 +4797,39 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>707.39</v>
+        <v>1288.09</v>
       </c>
       <c r="E35" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4738,39 +4838,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>708.48</v>
+        <v>1287.76</v>
       </c>
       <c r="E36" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4779,221 +4879,221 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4452.98</v>
       </c>
       <c r="E37" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1288.1</v>
+        <v>4467.26</v>
       </c>
       <c r="E38" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1292.36</v>
+        <v>4471.19</v>
       </c>
       <c r="E39" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1799</v>
+        <v>4492.85</v>
       </c>
       <c r="E40" t="n">
-        <v>1799</v>
+        <v>1190</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1799</v>
+        <v>4485.35</v>
       </c>
       <c r="E41" t="n">
-        <v>1799</v>
+        <v>1190</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -5004,37 +5104,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1074.05</v>
+        <v>707.14</v>
       </c>
       <c r="E42" t="n">
-        <v>230.34</v>
+        <v>165</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
@@ -5045,37 +5145,37 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1073.61</v>
+        <v>707.39</v>
       </c>
       <c r="E43" t="n">
-        <v>230.34</v>
+        <v>165</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -5086,37 +5186,37 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1073.29</v>
+        <v>708.48</v>
       </c>
       <c r="E44" t="n">
-        <v>230.34</v>
+        <v>165</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -5127,36 +5227,528 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>710.8200000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>165</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>sport-bittl.com</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Lake MX190-X Wide</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>776.66</v>
+      </c>
+      <c r="E46" t="n">
+        <v>180.33</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>varuste.net</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1288.1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>1292.36</v>
+      </c>
+      <c r="E48" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="E49" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D45" s="2" t="n">
+      <c r="D53" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E53" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E54" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E55" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
         <v>1076.61</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E56" t="n">
         <v>230.34</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E57" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5171,7 +5763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5277,6 +5869,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>9981.24</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -5294,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5400,6 +6012,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>4485.35</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
@@ -5417,7 +6049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5525,6 +6157,26 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>776.66</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>varuste.net</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
         </is>
       </c>
     </row>
@@ -5540,7 +6192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5646,6 +6298,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>310.05</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rczbikeshop.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
@@ -5663,7 +6335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5769,6 +6441,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
@@ -5786,7 +6478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5892,6 +6584,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -5909,7 +6621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6020,6 +6732,26 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>861.34</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2486,24 +2486,24 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1075.73</v>
+        <v>702.51</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1073.29</v>
+        <v>702.51</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike24.pl</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+42cm&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -2562,24 +2562,24 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1287.76</v>
+        <v>1281.3</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1281.42</v>
+        <v>1281.3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>r2-bike.com</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=SRAM+GX+Eagle+Transmission+1x12+Upgrade+Kit&amp;prds=localAnnotatedOfferId:1,catalogid:13461610079305402116,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -2676,24 +2676,24 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1799</v>
+        <v>1378.16</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1799</v>
+        <v>1378.16</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Amortyzator+rowerowy+ROCK+SHOX+SID+SL+Select+E1+3P+100mm&amp;prds=localAnnotatedOfferId:1,catalogid:95201058617068160,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1287.76</v>
+        <v>1281.3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>r2-bike.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=SRAM+GX+Eagle+Transmission+1x12+Upgrade+Kit&amp;prds=localAnnotatedOfferId:1,catalogid:13461610079305402116,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -3267,16 +3267,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1799</v>
+        <v>1378.16</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Amortyzator+rowerowy+ROCK+SHOX+SID+SL+Select+E1+3P+100mm&amp;prds=localAnnotatedOfferId:1,catalogid:95201058617068160,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -3658,7 +3658,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -4683,7 +4683,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1287.76</v>
+        <v>1281.3</v>
       </c>
       <c r="E36" t="n">
-        <v>299</v>
+        <v>297.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4879,16 +4879,16 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>r2-bike.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=SRAM+GX+Eagle+Transmission+1x12+Upgrade+Kit&amp;prds=localAnnotatedOfferId:1,catalogid:13461610079305402116,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -5523,28 +5523,28 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1799</v>
+        <v>1378.16</v>
       </c>
       <c r="E52" t="n">
-        <v>1799</v>
+        <v>319.99</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Amortyzator+rowerowy+ROCK+SHOX+SID+SL+Select+E1+3P+100mm&amp;prds=localAnnotatedOfferId:1,catalogid:95201058617068160,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -5728,28 +5728,28 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1075.73</v>
+        <v>702.51</v>
       </c>
       <c r="E57" t="n">
-        <v>230.34</v>
+        <v>702.51</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike24.pl</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+42cm&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6596,16 +6596,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1075.73</v>
+        <v>702.51</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike24.pl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+42cm&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2372,24 +2372,24 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>776.66</v>
+        <v>465.1</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>707.14</v>
+        <v>465.1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>varuste.net</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -2486,24 +2486,24 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>702.51</v>
+        <v>1075.73</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>702.51</v>
+        <v>1073.29</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+42cm&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2524,14 +2524,14 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>861.34</v>
+        <v>840.59</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>857.1</v>
+        <v>840.59</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -2562,24 +2562,24 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1281.3</v>
+        <v>1287.76</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1281.3</v>
+        <v>1281.42</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>r2-bike.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=SRAM+GX+Eagle+Transmission+1x12+Upgrade+Kit&amp;prds=localAnnotatedOfferId:1,catalogid:13461610079305402116,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -2600,24 +2600,24 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>129.16</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>128.53</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -2638,24 +2638,24 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>239.99</v>
+        <v>150.31</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>239.99</v>
+        <v>150.31</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1378.16</v>
+        <v>1399</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1378.16</v>
+        <v>1399</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Amortyzator+rowerowy+ROCK+SHOX+SID+SL+Select+E1+3P+100mm&amp;prds=localAnnotatedOfferId:1,catalogid:95201058617068160,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1281.3</v>
+        <v>1287.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>r2-bike.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=SRAM+GX+Eagle+Transmission+1x12+Upgrade+Kit&amp;prds=localAnnotatedOfferId:1,catalogid:13461610079305402116,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3021,16 +3021,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>129.16</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -3164,16 +3164,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>239.99</v>
+        <v>150.31</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
@@ -3267,16 +3267,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1378.16</v>
+        <v>1399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Amortyzator+rowerowy+ROCK+SHOX+SID+SL+Select+E1+3P+100mm&amp;prds=localAnnotatedOfferId:1,catalogid:95201058617068160,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -3637,28 +3637,28 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>239.99</v>
+        <v>150.31</v>
       </c>
       <c r="E6" t="n">
-        <v>239.99</v>
+        <v>34.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -3842,14 +3842,14 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>861.34</v>
+        <v>840.59</v>
       </c>
       <c r="E11" t="n">
-        <v>199.99</v>
+        <v>179.99</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3859,11 +3859,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>129.16</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>29.99</v>
+        <v>18.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4674,16 +4674,16 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32">
@@ -4867,10 +4867,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1281.3</v>
+        <v>1287.76</v>
       </c>
       <c r="E36" t="n">
-        <v>297.5</v>
+        <v>299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4879,16 +4879,16 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>r2-bike.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=SRAM+GX+Eagle+Transmission+1x12+Upgrade+Kit&amp;prds=localAnnotatedOfferId:1,catalogid:13461610079305402116,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
@@ -5277,10 +5277,10 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>776.66</v>
+        <v>465.1</v>
       </c>
       <c r="E46" t="n">
-        <v>180.33</v>
+        <v>107.99</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5289,16 +5289,16 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>varuste.net</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47">
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
@@ -5523,28 +5523,28 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1378.16</v>
+        <v>1399</v>
       </c>
       <c r="E52" t="n">
-        <v>319.99</v>
+        <v>1399</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Amortyzator+rowerowy+ROCK+SHOX+SID+SL+Select+E1+3P+100mm&amp;prds=localAnnotatedOfferId:1,catalogid:95201058617068160,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
@@ -5728,28 +5728,28 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>702.51</v>
+        <v>1075.73</v>
       </c>
       <c r="E57" t="n">
-        <v>702.51</v>
+        <v>230.34</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+42cm&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6167,16 +6167,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>776.66</v>
+        <v>465.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>varuste.net</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://varuste.net/en/p140724/lake-mx190-x-wide</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -6596,16 +6596,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>702.51</v>
+        <v>1075.73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+42cm&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>861.34</v>
+        <v>840.59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6748,7 +6748,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -10,17 +10,18 @@
     <sheet name="Podsumowanie" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Historia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="FM2797" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="LAUF-CARBONARA" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Lake MX190-X Wide" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DT Swiss Fatbike" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DT SWISS 350 12x148" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Canyon S14 VCLS 2.0" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="GX-T-KIT" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="GX-T-CHAIN" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Cane Creek 40 IS41-IS52" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="ROCK SHOX SID" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Lake MX242" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="FARGO-TI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="LAUF-CARBONARA" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Lake MX190-X Wide" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DT Swiss Fatbike" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DT SWISS 350 12x148" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Canyon S14 VCLS 2.0" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="GX-T-KIT" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GX-T-CHAIN" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Cane Creek 40 IS41-IS52" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ROCK SHOX SID" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Lake MX242" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -205,12 +206,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$6</f>
+              <f>'FM2797'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$6</f>
+              <f>'FM2797'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -326,12 +327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$6</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$6</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -447,12 +448,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$4</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$4</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -568,12 +569,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$4</f>
+              <f>'Lake MX242'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$4</f>
+              <f>'Lake MX242'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -689,12 +690,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$6</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$6</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -810,12 +811,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$6</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$6</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -931,12 +932,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$6</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$6</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1052,12 +1053,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$6</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$6</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1173,12 +1174,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$6</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$6</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1294,12 +1295,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$6</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$6</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1415,12 +1416,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$6</f>
+              <f>'GX-T-KIT'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$6</f>
+              <f>'GX-T-KIT'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1536,12 +1537,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$6</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$6</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2224,7 +2225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2292,7 +2293,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -2320,416 +2321,458 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>4485.35</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>4452.98</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>465.1</v>
+        <v>4485.35</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>465.1</v>
+        <v>4452.98</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>310.05</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>308.53</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>227.84</v>
+        <v>129.16</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>227.84</v>
+        <v>129.16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>1075.73</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1073.29</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>840.59</v>
+        <v>1075.73</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>840.59</v>
+        <v>1073.29</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>840.59</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>840.59</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>1287.76</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>1281.42</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1287.76</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1281.42</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
-        <v>150.31</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>150.31</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
-        <v>1112.47</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>1112.47</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>bike-discount.de</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -2738,17 +2781,17 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2760,7 +2803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2798,16 +2841,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1281.42</v>
+        <v>857.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -2818,16 +2861,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1281.87</v>
+        <v>857.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -2838,16 +2881,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1283.85</v>
+        <v>858.72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -2858,16 +2901,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1288.09</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -2878,16 +2921,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1287.76</v>
+        <v>840.59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>840.59</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2941,16 +3004,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>128.53</v>
+        <v>1281.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -2961,16 +3024,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>128.57</v>
+        <v>1281.87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -2981,16 +3044,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>128.77</v>
+        <v>1283.85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3001,16 +3064,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>129.2</v>
+        <v>1288.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3021,16 +3084,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1287.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1287.76</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3084,16 +3167,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>239.99</v>
+        <v>128.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3104,16 +3187,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>239.99</v>
+        <v>128.57</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3124,16 +3207,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>239.99</v>
+        <v>128.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3144,16 +3227,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>239.99</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3164,16 +3247,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>150.31</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>81.40000000000001</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3223,11 +3326,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3236,18 +3339,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3256,27 +3359,87 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>centrumrowerowe.pl</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+      <c r="B6" s="2" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3330,16 +3493,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1288.1</v>
+        <v>1799</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -3350,16 +3513,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1292.36</v>
+        <v>1799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -3370,6 +3533,129 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1288.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1292.36</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
         <v>1112.47</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -3378,6 +3664,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -3395,7 +3701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3664,24 +3970,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>857.1</v>
+        <v>150.31</v>
       </c>
       <c r="E7" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -3690,22 +3996,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3719,7 +4025,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E8" t="n">
         <v>199.99</v>
@@ -3746,7 +4052,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3760,7 +4066,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E9" t="n">
         <v>199.99</v>
@@ -3787,7 +4093,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3801,7 +4107,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E10" t="n">
         <v>199.99</v>
@@ -3828,7 +4134,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3842,14 +4148,14 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3859,99 +4165,99 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>514.24</v>
+        <v>840.59</v>
       </c>
       <c r="E12" t="n">
-        <v>119.99</v>
+        <v>179.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>514.42</v>
+        <v>840.59</v>
       </c>
       <c r="E13" t="n">
-        <v>119.99</v>
+        <v>179.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3965,10 +4271,10 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E14" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -3977,22 +4283,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -4006,10 +4312,10 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E15" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4018,22 +4324,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4047,10 +4353,10 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E16" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4064,34 +4370,34 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>308.53</v>
+        <v>227.89</v>
       </c>
       <c r="E17" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4100,39 +4406,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>308.64</v>
+        <v>227.84</v>
       </c>
       <c r="E18" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4141,39 +4447,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>309.11</v>
+        <v>227.84</v>
       </c>
       <c r="E19" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4182,22 +4488,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4211,7 +4517,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E20" t="n">
         <v>71.98999999999999</v>
@@ -4238,7 +4544,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4252,7 +4558,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E21" t="n">
         <v>71.98999999999999</v>
@@ -4273,30 +4579,30 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>309.11</v>
       </c>
       <c r="E22" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -4305,39 +4611,39 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>9935.59</v>
+        <v>310.13</v>
       </c>
       <c r="E23" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -4346,39 +4652,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>310.05</v>
       </c>
       <c r="E24" t="n">
-        <v>2317.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4387,39 +4693,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>129.16</v>
       </c>
       <c r="E25" t="n">
-        <v>2317.5</v>
+        <v>29.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4428,22 +4734,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4457,7 +4763,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9981.24</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E26" t="n">
         <v>2317.5</v>
@@ -4478,30 +4784,30 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>128.53</v>
+        <v>9935.59</v>
       </c>
       <c r="E27" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4510,39 +4816,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>128.57</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4551,39 +4857,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>128.77</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4592,39 +4898,39 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>129.2</v>
+        <v>9981.24</v>
       </c>
       <c r="E30" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4633,39 +4939,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>9981.24</v>
       </c>
       <c r="E31" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4674,16 +4980,16 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
@@ -4694,19 +5000,19 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1281.42</v>
+        <v>128.53</v>
       </c>
       <c r="E32" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4715,16 +5021,16 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -4735,19 +5041,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1281.87</v>
+        <v>128.57</v>
       </c>
       <c r="E33" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4756,16 +5062,16 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -4776,19 +5082,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1283.85</v>
+        <v>128.77</v>
       </c>
       <c r="E34" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4797,16 +5103,16 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -4817,19 +5123,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1288.09</v>
+        <v>129.2</v>
       </c>
       <c r="E35" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4838,16 +5144,16 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
@@ -4858,19 +5164,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1287.76</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4879,244 +5185,244 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>4452.98</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>1190</v>
+        <v>18.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>4467.26</v>
+        <v>1281.42</v>
       </c>
       <c r="E38" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>4471.19</v>
+        <v>1281.87</v>
       </c>
       <c r="E39" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4492.85</v>
+        <v>1283.85</v>
       </c>
       <c r="E40" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>4485.35</v>
+        <v>1288.09</v>
       </c>
       <c r="E41" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>707.14</v>
+        <v>1287.76</v>
       </c>
       <c r="E42" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5125,39 +5431,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>707.39</v>
+        <v>1287.76</v>
       </c>
       <c r="E43" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5166,217 +5472,217 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>708.48</v>
+        <v>4452.98</v>
       </c>
       <c r="E44" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4467.26</v>
       </c>
       <c r="E45" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>465.1</v>
+        <v>4471.19</v>
       </c>
       <c r="E46" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1288.1</v>
+        <v>4492.85</v>
       </c>
       <c r="E47" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1292.36</v>
+        <v>4485.35</v>
       </c>
       <c r="E48" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -5386,325 +5692,325 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1112.47</v>
+        <v>4485.35</v>
       </c>
       <c r="E49" t="n">
-        <v>258.3</v>
+        <v>1190</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1799</v>
+        <v>707.14</v>
       </c>
       <c r="E50" t="n">
-        <v>1799</v>
+        <v>165</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1799</v>
+        <v>707.39</v>
       </c>
       <c r="E51" t="n">
-        <v>1799</v>
+        <v>165</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1399</v>
+        <v>708.48</v>
       </c>
       <c r="E52" t="n">
-        <v>1399</v>
+        <v>165</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1074.05</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>230.34</v>
+        <v>165</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1073.61</v>
+        <v>465.1</v>
       </c>
       <c r="E54" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1073.29</v>
+        <v>465.1</v>
       </c>
       <c r="E55" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1076.61</v>
+        <v>1288.1</v>
       </c>
       <c r="E56" t="n">
-        <v>230.34</v>
+        <v>299.99</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -5714,41 +6020,533 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>1292.36</v>
+      </c>
+      <c r="E57" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="E58" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="E59" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D57" s="2" t="n">
+      <c r="D64" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E64" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E65" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E66" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E67" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
         <v>1075.73</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E68" t="n">
         <v>230.34</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I57" t="n">
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E69" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5763,7 +6561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5889,6 +6687,26 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>9981.24</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -5906,7 +6724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5937,109 +6755,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>4452.98</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>4467.26</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>4471.19</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4492.85</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>4485.35</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6049,7 +6766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6087,16 +6804,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>707.14</v>
+        <v>4452.98</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -6107,16 +6824,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>707.39</v>
+        <v>4467.26</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -6127,16 +6844,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>708.48</v>
+        <v>4471.19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -6147,16 +6864,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4492.85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -6167,16 +6884,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>465.1</v>
+        <v>4485.35</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>4485.35</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6230,16 +6967,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>308.53</v>
+        <v>707.14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -6250,16 +6987,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>308.64</v>
+        <v>707.39</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -6270,16 +7007,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>309.11</v>
+        <v>708.48</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -6290,16 +7027,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>310.13</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -6310,16 +7047,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>310.05</v>
+        <v>465.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>465.1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -6335,7 +7092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6373,16 +7130,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>514.24</v>
+        <v>308.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -6393,16 +7150,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>514.42</v>
+        <v>308.64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -6413,16 +7170,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>398.89</v>
+        <v>309.11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -6433,16 +7190,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>227.89</v>
+        <v>310.13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -6453,16 +7210,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>227.84</v>
+        <v>310.05</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>129.16</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bike24.de</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -6478,7 +7255,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6516,16 +7293,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1074.05</v>
+        <v>514.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
     </row>
@@ -6536,16 +7313,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1073.61</v>
+        <v>514.42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
     </row>
@@ -6556,16 +7333,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1073.29</v>
+        <v>398.89</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
     </row>
@@ -6576,16 +7353,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1076.61</v>
+        <v>227.89</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -6596,16 +7373,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1075.73</v>
+        <v>227.84</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>227.84</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -6621,7 +7418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6659,16 +7456,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>857.1</v>
+        <v>1074.05</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -6679,16 +7476,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>857.4</v>
+        <v>1073.61</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -6699,16 +7496,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>858.72</v>
+        <v>1073.29</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -6719,16 +7516,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>1076.61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -6739,16 +7536,36 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>840.59</v>
+        <v>1075.73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -294,6 +294,127 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GX-T-CHAIN'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Cane Creek 40 IS41/IS52 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -402,7 +523,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -523,7 +644,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -657,6 +778,127 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Salsa Fargo Ti Frameset - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'FARGO-TI'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'FARGO-TI'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FARGO-TI'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Lauf Carbonara fork - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -765,7 +1007,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -886,7 +1128,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1007,7 +1249,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1128,7 +1370,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1249,7 +1491,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1370,7 +1612,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1422,127 +1664,6 @@
           <val>
             <numRef>
               <f>'GX-T-KIT'!$B$2:$B$7</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'GX-T-CHAIN'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1694,6 +1815,33 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2297,7 +2445,7 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>9981.24</v>
+        <v>10073.01</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2331,32 +2479,28 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>11731.2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>11731.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2521,7 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4485.35</v>
+        <v>4524.98</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>4452.98</v>
@@ -2415,7 +2559,7 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>465.1</v>
+        <v>469.38</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>465.1</v>
@@ -2453,10 +2597,10 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>129.16</v>
+        <v>130.35</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>129.16</v>
+        <v>130.35</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2491,7 +2635,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>227.84</v>
+        <v>229.93</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>227.84</v>
@@ -2529,7 +2673,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1075.73</v>
+        <v>1086.21</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>1073.29</v>
@@ -2567,14 +2711,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>840.59</v>
+        <v>738.86</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>840.59</v>
+        <v>738.86</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2584,7 +2728,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2749,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1287.76</v>
+        <v>1299.6</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1281.42</v>
@@ -2643,7 +2787,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>81.40000000000001</v>
@@ -2681,7 +2825,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>150.31</v>
+        <v>151.69</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>150.31</v>
@@ -2719,24 +2863,24 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1399</v>
+        <v>1386.53</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1399</v>
+        <v>1386.53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2901,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1112.47</v>
+        <v>1122.7</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1112.47</v>
@@ -2781,17 +2925,18 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2941,7 +3086,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>840.59</v>
+        <v>738.86</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2950,7 +3095,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3249,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1287.76</v>
+        <v>1299.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3267,7 +3412,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3430,7 +3575,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>150.31</v>
+        <v>151.69</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3553,16 +3698,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1399</v>
+        <v>1386.53</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3821,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1112.47</v>
+        <v>1122.7</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3701,7 +3846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3984,7 +4129,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>150.31</v>
+        <v>151.69</v>
       </c>
       <c r="E7" t="n">
         <v>34.9</v>
@@ -4005,7 +4150,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -4230,14 +4375,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>840.59</v>
+        <v>738.86</v>
       </c>
       <c r="E13" t="n">
-        <v>179.99</v>
+        <v>169.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4247,11 +4392,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -4476,7 +4621,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>227.84</v>
+        <v>229.93</v>
       </c>
       <c r="E19" t="n">
         <v>52.9</v>
@@ -4497,7 +4642,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
@@ -4722,7 +4867,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>129.16</v>
+        <v>130.35</v>
       </c>
       <c r="E25" t="n">
         <v>29.99</v>
@@ -4743,30 +4888,30 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E26" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4775,22 +4920,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4804,7 +4949,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9935.59</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E27" t="n">
         <v>2317.5</v>
@@ -4831,7 +4976,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4845,7 +4990,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>9935.59</v>
       </c>
       <c r="E28" t="n">
         <v>2317.5</v>
@@ -4872,7 +5017,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4886,7 +5031,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E29" t="n">
         <v>2317.5</v>
@@ -4907,13 +5052,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4927,7 +5072,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9981.24</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E30" t="n">
         <v>2317.5</v>
@@ -4948,13 +5093,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4995,24 +5140,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>128.53</v>
+        <v>10073.01</v>
       </c>
       <c r="E32" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5021,22 +5166,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5050,7 +5195,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>128.57</v>
+        <v>128.53</v>
       </c>
       <c r="E33" t="n">
         <v>29.99</v>
@@ -5077,7 +5222,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5091,7 +5236,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>128.77</v>
+        <v>128.57</v>
       </c>
       <c r="E34" t="n">
         <v>29.99</v>
@@ -5112,13 +5257,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5132,7 +5277,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>129.2</v>
+        <v>128.77</v>
       </c>
       <c r="E35" t="n">
         <v>29.99</v>
@@ -5153,13 +5298,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5173,10 +5318,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>129.2</v>
       </c>
       <c r="E36" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5185,22 +5330,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>69</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5235,30 +5380,30 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1281.42</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5267,22 +5412,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5296,7 +5441,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1281.87</v>
+        <v>1281.42</v>
       </c>
       <c r="E39" t="n">
         <v>299</v>
@@ -5323,7 +5468,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5337,7 +5482,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1283.85</v>
+        <v>1281.87</v>
       </c>
       <c r="E40" t="n">
         <v>299</v>
@@ -5364,7 +5509,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5378,7 +5523,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1288.09</v>
+        <v>1283.85</v>
       </c>
       <c r="E41" t="n">
         <v>299</v>
@@ -5405,7 +5550,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5419,7 +5564,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1287.76</v>
+        <v>1288.09</v>
       </c>
       <c r="E42" t="n">
         <v>299</v>
@@ -5440,13 +5585,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5481,54 +5626,54 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4452.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E44" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5542,7 +5687,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4467.26</v>
+        <v>4452.98</v>
       </c>
       <c r="E45" t="n">
         <v>1190</v>
@@ -5569,7 +5714,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5583,7 +5728,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4471.19</v>
+        <v>4467.26</v>
       </c>
       <c r="E46" t="n">
         <v>1190</v>
@@ -5610,7 +5755,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5624,7 +5769,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4492.85</v>
+        <v>4471.19</v>
       </c>
       <c r="E47" t="n">
         <v>1190</v>
@@ -5645,13 +5790,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5665,7 +5810,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4485.35</v>
+        <v>4492.85</v>
       </c>
       <c r="E48" t="n">
         <v>1190</v>
@@ -5692,7 +5837,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5733,48 +5878,48 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>707.14</v>
+        <v>4524.98</v>
       </c>
       <c r="E50" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5788,7 +5933,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>707.39</v>
+        <v>707.14</v>
       </c>
       <c r="E51" t="n">
         <v>165</v>
@@ -5815,7 +5960,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5829,7 +5974,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>708.48</v>
+        <v>707.39</v>
       </c>
       <c r="E52" t="n">
         <v>165</v>
@@ -5850,13 +5995,13 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5870,7 +6015,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>708.48</v>
       </c>
       <c r="E53" t="n">
         <v>165</v>
@@ -5897,7 +6042,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5911,10 +6056,10 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>465.1</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>107.99</v>
+        <v>165</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5923,22 +6068,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5973,30 +6118,30 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1288.1</v>
+        <v>469.38</v>
       </c>
       <c r="E56" t="n">
-        <v>299.99</v>
+        <v>107.99</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6005,22 +6150,22 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6034,7 +6179,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1292.36</v>
+        <v>1288.1</v>
       </c>
       <c r="E57" t="n">
         <v>299.99</v>
@@ -6051,17 +6196,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6075,10 +6220,10 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1112.47</v>
+        <v>1292.36</v>
       </c>
       <c r="E58" t="n">
-        <v>258.3</v>
+        <v>299.99</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6096,13 +6241,13 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6137,54 +6282,54 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1799</v>
+        <v>1122.7</v>
       </c>
       <c r="E60" t="n">
-        <v>1799</v>
+        <v>258.3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6219,13 +6364,13 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6239,10 +6384,10 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="E62" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6256,17 +6401,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6301,54 +6446,54 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1074.05</v>
+        <v>1386.53</v>
       </c>
       <c r="E64" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6362,7 +6507,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1073.61</v>
+        <v>1074.05</v>
       </c>
       <c r="E65" t="n">
         <v>230.34</v>
@@ -6389,7 +6534,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6403,7 +6548,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1073.29</v>
+        <v>1073.61</v>
       </c>
       <c r="E66" t="n">
         <v>230.34</v>
@@ -6430,7 +6575,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6444,7 +6589,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1076.61</v>
+        <v>1073.29</v>
       </c>
       <c r="E67" t="n">
         <v>230.34</v>
@@ -6471,7 +6616,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6485,7 +6630,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1075.73</v>
+        <v>1076.61</v>
       </c>
       <c r="E68" t="n">
         <v>230.34</v>
@@ -6512,7 +6657,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6547,6 +6692,47 @@
         </is>
       </c>
       <c r="I69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E70" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6699,7 +6885,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>9981.24</v>
+        <v>10073.01</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6724,7 +6910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6755,8 +6941,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>11731.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6904,7 +7111,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4485.35</v>
+        <v>4524.98</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7067,7 +7274,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>465.1</v>
+        <v>469.38</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7230,7 +7437,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>129.16</v>
+        <v>130.35</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7393,7 +7600,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>227.84</v>
+        <v>229.93</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7556,7 +7763,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1075.73</v>
+        <v>1086.21</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -294,127 +294,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'GX-T-CHAIN'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Cane Creek 40 IS41/IS52 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -523,7 +402,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -644,7 +523,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -778,127 +657,6 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Salsa Fargo Ti Frameset - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'FARGO-TI'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'FARGO-TI'!$A$2</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'FARGO-TI'!$B$2</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
               <a:t>Lauf Carbonara fork - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -1007,7 +765,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1128,7 +886,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1249,7 +1007,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1370,7 +1128,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1491,7 +1249,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1612,7 +1370,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1664,6 +1422,127 @@
           <val>
             <numRef>
               <f>'GX-T-KIT'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GX-T-CHAIN'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1815,33 +1694,6 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7920000" cy="3240000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2479,28 +2331,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>11731.2</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>11731.2</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2635,24 +2491,24 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>229.93</v>
+        <v>225.97</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>227.84</v>
+        <v>225.97</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+hub+12x148+Sram+XD&amp;prds=localAnnotatedOfferId:1,catalogid:11670089183688159097,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -2711,14 +2567,14 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>738.86</v>
+        <v>840.59</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2728,7 +2584,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -2863,24 +2719,24 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1386.53</v>
+        <v>1399</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1386.53</v>
+        <v>1399</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -2925,18 +2781,17 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3086,7 +2941,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3095,7 +2950,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3698,16 +3553,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1386.53</v>
+        <v>1399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4150,7 +4005,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -4375,14 +4230,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E13" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4392,11 +4247,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -4621,10 +4476,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>229.93</v>
+        <v>225.97</v>
       </c>
       <c r="E19" t="n">
-        <v>52.9</v>
+        <v>51.99</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4633,16 +4488,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+hub+12x148+Sram+XD&amp;prds=localAnnotatedOfferId:1,catalogid:11670089183688159097,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
@@ -4888,30 +4743,30 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>11731.2</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>2699</v>
+        <v>2317.5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4920,22 +4775,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4949,7 +4804,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>9935.59</v>
       </c>
       <c r="E27" t="n">
         <v>2317.5</v>
@@ -4976,7 +4831,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4990,7 +4845,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9935.59</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E28" t="n">
         <v>2317.5</v>
@@ -5017,7 +4872,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5031,7 +4886,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E29" t="n">
         <v>2317.5</v>
@@ -5052,13 +4907,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5072,7 +4927,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>9981.24</v>
       </c>
       <c r="E30" t="n">
         <v>2317.5</v>
@@ -5093,13 +4948,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5113,7 +4968,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9981.24</v>
+        <v>10073.01</v>
       </c>
       <c r="E31" t="n">
         <v>2317.5</v>
@@ -5140,24 +4995,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>10073.01</v>
+        <v>128.53</v>
       </c>
       <c r="E32" t="n">
-        <v>2317.5</v>
+        <v>29.99</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5166,22 +5021,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5195,7 +5050,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>128.53</v>
+        <v>128.57</v>
       </c>
       <c r="E33" t="n">
         <v>29.99</v>
@@ -5222,7 +5077,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5236,7 +5091,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>128.57</v>
+        <v>128.77</v>
       </c>
       <c r="E34" t="n">
         <v>29.99</v>
@@ -5257,13 +5112,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5277,7 +5132,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>128.77</v>
+        <v>129.2</v>
       </c>
       <c r="E35" t="n">
         <v>29.99</v>
@@ -5298,13 +5153,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5318,10 +5173,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>129.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>29.99</v>
+        <v>18.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5330,22 +5185,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5359,7 +5214,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>18.9</v>
@@ -5380,30 +5235,30 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1281.42</v>
       </c>
       <c r="E38" t="n">
-        <v>18.9</v>
+        <v>299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5412,22 +5267,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5441,7 +5296,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1281.42</v>
+        <v>1281.87</v>
       </c>
       <c r="E39" t="n">
         <v>299</v>
@@ -5468,7 +5323,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5482,7 +5337,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1281.87</v>
+        <v>1283.85</v>
       </c>
       <c r="E40" t="n">
         <v>299</v>
@@ -5509,7 +5364,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5523,7 +5378,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1283.85</v>
+        <v>1288.09</v>
       </c>
       <c r="E41" t="n">
         <v>299</v>
@@ -5550,7 +5405,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5564,7 +5419,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1288.09</v>
+        <v>1287.76</v>
       </c>
       <c r="E42" t="n">
         <v>299</v>
@@ -5585,13 +5440,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5605,7 +5460,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1287.76</v>
+        <v>1299.6</v>
       </c>
       <c r="E43" t="n">
         <v>299</v>
@@ -5626,54 +5481,54 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1299.6</v>
+        <v>4452.98</v>
       </c>
       <c r="E44" t="n">
-        <v>299</v>
+        <v>1190</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5687,7 +5542,7 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4452.98</v>
+        <v>4467.26</v>
       </c>
       <c r="E45" t="n">
         <v>1190</v>
@@ -5714,7 +5569,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5728,7 +5583,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4467.26</v>
+        <v>4471.19</v>
       </c>
       <c r="E46" t="n">
         <v>1190</v>
@@ -5755,7 +5610,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5769,7 +5624,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4471.19</v>
+        <v>4492.85</v>
       </c>
       <c r="E47" t="n">
         <v>1190</v>
@@ -5790,13 +5645,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5810,7 +5665,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4492.85</v>
+        <v>4485.35</v>
       </c>
       <c r="E48" t="n">
         <v>1190</v>
@@ -5837,7 +5692,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5851,7 +5706,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4485.35</v>
+        <v>4524.98</v>
       </c>
       <c r="E49" t="n">
         <v>1190</v>
@@ -5878,48 +5733,48 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4524.98</v>
+        <v>707.14</v>
       </c>
       <c r="E50" t="n">
-        <v>1190</v>
+        <v>165</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5933,7 +5788,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>707.14</v>
+        <v>707.39</v>
       </c>
       <c r="E51" t="n">
         <v>165</v>
@@ -5960,7 +5815,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5974,7 +5829,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>707.39</v>
+        <v>708.48</v>
       </c>
       <c r="E52" t="n">
         <v>165</v>
@@ -5995,13 +5850,13 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6015,7 +5870,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>708.48</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E53" t="n">
         <v>165</v>
@@ -6042,7 +5897,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6056,10 +5911,10 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>465.1</v>
       </c>
       <c r="E54" t="n">
-        <v>165</v>
+        <v>107.99</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6068,22 +5923,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6097,7 +5952,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>465.1</v>
+        <v>469.38</v>
       </c>
       <c r="E55" t="n">
         <v>107.99</v>
@@ -6118,30 +5973,30 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>469.38</v>
+        <v>1288.1</v>
       </c>
       <c r="E56" t="n">
-        <v>107.99</v>
+        <v>299.99</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6150,22 +6005,22 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6179,7 +6034,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1288.1</v>
+        <v>1292.36</v>
       </c>
       <c r="E57" t="n">
         <v>299.99</v>
@@ -6196,17 +6051,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6220,10 +6075,10 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1292.36</v>
+        <v>1112.47</v>
       </c>
       <c r="E58" t="n">
-        <v>299.99</v>
+        <v>258.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6241,13 +6096,13 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6261,7 +6116,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1112.47</v>
+        <v>1122.7</v>
       </c>
       <c r="E59" t="n">
         <v>258.3</v>
@@ -6282,54 +6137,54 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1122.7</v>
+        <v>1799</v>
       </c>
       <c r="E60" t="n">
-        <v>258.3</v>
+        <v>1799</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6364,13 +6219,13 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6384,10 +6239,10 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1799</v>
+        <v>1399</v>
       </c>
       <c r="E62" t="n">
-        <v>1799</v>
+        <v>1399</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6401,17 +6256,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6446,54 +6301,54 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1386.53</v>
+        <v>1074.05</v>
       </c>
       <c r="E64" t="n">
-        <v>319</v>
+        <v>230.34</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6507,7 +6362,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1074.05</v>
+        <v>1073.61</v>
       </c>
       <c r="E65" t="n">
         <v>230.34</v>
@@ -6534,7 +6389,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6548,7 +6403,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1073.61</v>
+        <v>1073.29</v>
       </c>
       <c r="E66" t="n">
         <v>230.34</v>
@@ -6575,7 +6430,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6589,7 +6444,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1073.29</v>
+        <v>1076.61</v>
       </c>
       <c r="E67" t="n">
         <v>230.34</v>
@@ -6616,7 +6471,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6630,7 +6485,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1076.61</v>
+        <v>1075.73</v>
       </c>
       <c r="E68" t="n">
         <v>230.34</v>
@@ -6657,7 +6512,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6671,7 +6526,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1075.73</v>
+        <v>1086.21</v>
       </c>
       <c r="E69" t="n">
         <v>230.34</v>
@@ -6692,47 +6547,6 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>1086.21</v>
-      </c>
-      <c r="E70" t="n">
-        <v>230.34</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>CHF</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>bikeshopzizers.ch</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
-        </is>
-      </c>
-      <c r="I70" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6910,7 +6724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6941,29 +6755,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>11731.2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>bike-packing.de</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7600,16 +7393,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>229.93</v>
+        <v>225.97</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+hub+12x148+Sram+XD&amp;prds=localAnnotatedOfferId:1,catalogid:11670089183688159097,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -11,17 +11,18 @@
     <sheet name="Historia" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="FM2797" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="FARGO-TI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="LAUF-CARBONARA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Lake MX190-X Wide" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DT Swiss Fatbike" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DT SWISS 350 12x148" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Canyon S14 VCLS 2.0" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="GX-T-KIT" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="GX-T-CHAIN" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Cane Creek 40 IS41-IS52" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ROCK SHOX SID" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Lake MX242" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="FARGO-STEEL" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="LAUF-CARBONARA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Lake MX190-X Wide" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DT Swiss Fatbike" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DT SWISS 350 12x148" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Canyon S14 VCLS 2.0" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="GX-T-KIT" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GX-T-CHAIN" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Cane Creek 40 IS41-IS52" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ROCK SHOX SID" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Lake MX242" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -294,6 +295,248 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>SRAM GX Eagle Transmission Upgrade Kit - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GX-T-KIT'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GX-T-KIT'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GX-T-KIT'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'GX-T-CHAIN'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Cane Creek 40 IS41/IS52 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -402,7 +645,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -523,7 +766,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -657,6 +900,248 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Salsa Fargo Ti Frameset - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'FARGO-TI'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'FARGO-TI'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FARGO-TI'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'FARGO-STEEL'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'FARGO-STEEL'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'FARGO-STEEL'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Lauf Carbonara fork - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -765,7 +1250,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -886,7 +1371,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1007,7 +1492,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1128,7 +1613,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1249,7 +1734,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1301,248 +1786,6 @@
           <val>
             <numRef>
               <f>'Canyon S14 VCLS 2.0'!$B$2:$B$7</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>SRAM GX Eagle Transmission Upgrade Kit - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'GX-T-KIT'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$7</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'GX-T-CHAIN'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1694,6 +1937,60 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2225,7 +2522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2331,44 +2628,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>11731.2</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>11731.2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2377,36 +2670,36 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4524.98</v>
+        <v>5211.45</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4452.98</v>
+        <v>5211.45</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2415,36 +2708,36 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>465.1</v>
+        <v>4452.98</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2453,36 +2746,36 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>130.35</v>
+        <v>469.38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>130.35</v>
+        <v>465.1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2491,10 +2784,10 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>225.97</v>
+        <v>130.35</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>225.97</v>
+        <v>130.35</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -2508,19 +2801,19 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+hub+12x148+Sram+XD&amp;prds=localAnnotatedOfferId:1,catalogid:11670089183688159097,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2529,36 +2822,36 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1086.21</v>
+        <v>229.93</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1073.29</v>
+        <v>227.84</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2567,36 +2860,36 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>848.78</v>
+        <v>1086.21</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>840.59</v>
+        <v>1073.29</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2605,36 +2898,36 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1299.6</v>
+        <v>738.86</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1281.42</v>
+        <v>738.86</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2643,36 +2936,36 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1281.42</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2681,10 +2974,10 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>150.31</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2693,24 +2986,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2719,10 +3012,10 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1399</v>
+        <v>151.69</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1399</v>
+        <v>150.31</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2731,48 +3024,86 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D15" s="2" t="n">
         <v>1122.7</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E15" s="2" t="n">
         <v>1112.47</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>bike-discount.de</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H15" s="3" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -2781,17 +3112,19 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2841,16 +3174,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>857.1</v>
+        <v>1074.05</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2861,16 +3194,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>857.4</v>
+        <v>1073.61</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2881,16 +3214,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>858.72</v>
+        <v>1073.29</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2901,16 +3234,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>1076.61</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2921,16 +3254,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>840.59</v>
+        <v>1075.73</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2941,16 +3274,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>848.78</v>
+        <v>1086.21</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -3004,16 +3337,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1281.42</v>
+        <v>857.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3024,16 +3357,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1281.87</v>
+        <v>857.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3044,16 +3377,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1283.85</v>
+        <v>858.72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3064,16 +3397,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1288.09</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3084,16 +3417,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1287.76</v>
+        <v>840.59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3104,16 +3437,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1299.6</v>
+        <v>738.86</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3167,16 +3500,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>128.53</v>
+        <v>1281.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3187,16 +3520,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>128.57</v>
+        <v>1281.87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3207,16 +3540,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>128.77</v>
+        <v>1283.85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3227,16 +3560,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>129.2</v>
+        <v>1288.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3247,16 +3580,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1287.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3267,16 +3600,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3330,16 +3663,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>239.99</v>
+        <v>128.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3350,16 +3683,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>239.99</v>
+        <v>128.57</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3370,16 +3703,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>239.99</v>
+        <v>128.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3390,16 +3723,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>239.99</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3410,16 +3743,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>150.31</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -3430,16 +3763,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3489,11 +3822,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3502,18 +3835,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3522,18 +3855,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1399</v>
+        <v>239.99</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3542,27 +3875,67 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>centrumrowerowe.pl</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+      <c r="B7" s="2" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
@@ -3616,6 +3989,129 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>1288.1</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -3701,7 +4197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4005,7 +4501,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
@@ -4230,14 +4726,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>848.78</v>
+        <v>738.86</v>
       </c>
       <c r="E13" t="n">
-        <v>179.99</v>
+        <v>169.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4247,11 +4743,11 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -4476,10 +4972,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>225.97</v>
+        <v>229.93</v>
       </c>
       <c r="E19" t="n">
-        <v>51.99</v>
+        <v>52.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -4488,16 +4984,16 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+hub+12x148+Sram+XD&amp;prds=localAnnotatedOfferId:1,catalogid:11670089183688159097,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20">
@@ -4743,30 +5239,30 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>5211.45</v>
       </c>
       <c r="E26" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4775,39 +5271,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>9935.59</v>
+        <v>11731.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4816,22 +5312,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4845,7 +5341,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E28" t="n">
         <v>2317.5</v>
@@ -4872,7 +5368,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4886,7 +5382,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>9935.59</v>
       </c>
       <c r="E29" t="n">
         <v>2317.5</v>
@@ -4907,13 +5403,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4927,7 +5423,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9981.24</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E30" t="n">
         <v>2317.5</v>
@@ -4948,13 +5444,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4968,7 +5464,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>10073.01</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E31" t="n">
         <v>2317.5</v>
@@ -4989,30 +5485,30 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>128.53</v>
+        <v>9981.24</v>
       </c>
       <c r="E32" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5021,39 +5517,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>128.57</v>
+        <v>10073.01</v>
       </c>
       <c r="E33" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5062,22 +5558,22 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5091,7 +5587,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>128.77</v>
+        <v>128.53</v>
       </c>
       <c r="E34" t="n">
         <v>29.99</v>
@@ -5112,13 +5608,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5132,7 +5628,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>129.2</v>
+        <v>128.57</v>
       </c>
       <c r="E35" t="n">
         <v>29.99</v>
@@ -5153,13 +5649,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5173,10 +5669,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>128.77</v>
       </c>
       <c r="E36" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5185,22 +5681,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5214,10 +5710,10 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>129.2</v>
       </c>
       <c r="E37" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5226,39 +5722,39 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>64</v>
+        <v>23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>1281.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5267,39 +5763,39 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>1281.87</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5308,22 +5804,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5337,7 +5833,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1283.85</v>
+        <v>1281.42</v>
       </c>
       <c r="E40" t="n">
         <v>299</v>
@@ -5364,7 +5860,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5378,7 +5874,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1288.09</v>
+        <v>1281.87</v>
       </c>
       <c r="E41" t="n">
         <v>299</v>
@@ -5405,7 +5901,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5419,7 +5915,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1287.76</v>
+        <v>1283.85</v>
       </c>
       <c r="E42" t="n">
         <v>299</v>
@@ -5440,13 +5936,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5460,7 +5956,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1299.6</v>
+        <v>1288.09</v>
       </c>
       <c r="E43" t="n">
         <v>299</v>
@@ -5481,95 +5977,95 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4452.98</v>
+        <v>1287.76</v>
       </c>
       <c r="E44" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>4467.26</v>
+        <v>1299.6</v>
       </c>
       <c r="E45" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5583,7 +6079,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4471.19</v>
+        <v>4452.98</v>
       </c>
       <c r="E46" t="n">
         <v>1190</v>
@@ -5610,7 +6106,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5624,7 +6120,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4492.85</v>
+        <v>4467.26</v>
       </c>
       <c r="E47" t="n">
         <v>1190</v>
@@ -5645,13 +6141,13 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5665,7 +6161,7 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4485.35</v>
+        <v>4471.19</v>
       </c>
       <c r="E48" t="n">
         <v>1190</v>
@@ -5686,13 +6182,13 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5706,7 +6202,7 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4524.98</v>
+        <v>4492.85</v>
       </c>
       <c r="E49" t="n">
         <v>1190</v>
@@ -5733,89 +6229,89 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>707.14</v>
+        <v>4485.35</v>
       </c>
       <c r="E50" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>707.39</v>
+        <v>4524.98</v>
       </c>
       <c r="E51" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5829,7 +6325,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>708.48</v>
+        <v>707.14</v>
       </c>
       <c r="E52" t="n">
         <v>165</v>
@@ -5850,13 +6346,13 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5870,7 +6366,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>707.39</v>
       </c>
       <c r="E53" t="n">
         <v>165</v>
@@ -5891,13 +6387,13 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5911,10 +6407,10 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>465.1</v>
+        <v>708.48</v>
       </c>
       <c r="E54" t="n">
-        <v>107.99</v>
+        <v>165</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5923,22 +6419,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5952,10 +6448,10 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>469.38</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>107.99</v>
+        <v>165</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5964,39 +6460,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1288.1</v>
+        <v>465.1</v>
       </c>
       <c r="E56" t="n">
-        <v>299.99</v>
+        <v>107.99</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6005,39 +6501,39 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1292.36</v>
+        <v>469.38</v>
       </c>
       <c r="E57" t="n">
-        <v>299.99</v>
+        <v>107.99</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6046,22 +6542,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6075,10 +6571,10 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1112.47</v>
+        <v>1288.1</v>
       </c>
       <c r="E58" t="n">
-        <v>258.3</v>
+        <v>299.99</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6092,17 +6588,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6116,10 +6612,10 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1122.7</v>
+        <v>1292.36</v>
       </c>
       <c r="E59" t="n">
-        <v>258.3</v>
+        <v>299.99</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6137,95 +6633,95 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1799</v>
+        <v>1112.47</v>
       </c>
       <c r="E60" t="n">
-        <v>1799</v>
+        <v>258.3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1799</v>
+        <v>1122.7</v>
       </c>
       <c r="E61" t="n">
-        <v>1799</v>
+        <v>258.3</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6239,10 +6735,10 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="E62" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6256,17 +6752,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6280,10 +6776,10 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="E63" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6297,99 +6793,99 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1074.05</v>
+        <v>1399</v>
       </c>
       <c r="E64" t="n">
-        <v>230.34</v>
+        <v>1399</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1073.61</v>
+        <v>1386.53</v>
       </c>
       <c r="E65" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6403,7 +6899,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1073.29</v>
+        <v>1074.05</v>
       </c>
       <c r="E66" t="n">
         <v>230.34</v>
@@ -6430,7 +6926,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6444,7 +6940,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1076.61</v>
+        <v>1073.61</v>
       </c>
       <c r="E67" t="n">
         <v>230.34</v>
@@ -6471,7 +6967,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6485,7 +6981,7 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1075.73</v>
+        <v>1073.29</v>
       </c>
       <c r="E68" t="n">
         <v>230.34</v>
@@ -6512,7 +7008,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6526,7 +7022,7 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1086.21</v>
+        <v>1076.61</v>
       </c>
       <c r="E69" t="n">
         <v>230.34</v>
@@ -6547,6 +7043,88 @@
         </is>
       </c>
       <c r="I69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E70" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E71" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6724,7 +7302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6755,8 +7333,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>11731.2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6766,7 +7365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6800,120 +7399,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4452.98</v>
+        <v>5211.45</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>4467.26</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>4471.19</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>4492.85</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>4485.35</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>4524.98</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>laufcycles.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
     </row>
@@ -6967,16 +7466,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>707.14</v>
+        <v>4452.98</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -6987,16 +7486,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>707.39</v>
+        <v>4467.26</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -7007,16 +7506,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>708.48</v>
+        <v>4471.19</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -7027,16 +7526,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4492.85</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -7047,16 +7546,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>465.1</v>
+        <v>4485.35</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -7067,16 +7566,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -7130,16 +7629,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>308.53</v>
+        <v>707.14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -7150,16 +7649,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>308.64</v>
+        <v>707.39</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -7170,16 +7669,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>309.11</v>
+        <v>708.48</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -7190,16 +7689,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>310.13</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -7210,16 +7709,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>310.05</v>
+        <v>465.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -7230,16 +7729,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>130.35</v>
+        <v>469.38</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -7293,16 +7792,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>514.24</v>
+        <v>308.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -7313,16 +7812,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>514.42</v>
+        <v>308.64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -7333,16 +7832,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>398.89</v>
+        <v>309.11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7852,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>227.89</v>
+        <v>310.13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -7373,16 +7872,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>227.84</v>
+        <v>310.05</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -7393,7 +7892,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>225.97</v>
+        <v>130.35</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -7402,7 +7901,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+hub+12x148+Sram+XD&amp;prds=localAnnotatedOfferId:1,catalogid:11670089183688159097,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -7456,16 +7955,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1074.05</v>
+        <v>514.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
     </row>
@@ -7476,16 +7975,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1073.61</v>
+        <v>514.42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
     </row>
@@ -7496,16 +7995,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1073.29</v>
+        <v>398.89</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
     </row>
@@ -7516,16 +8015,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1076.61</v>
+        <v>227.89</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -7536,16 +8035,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1075.73</v>
+        <v>227.84</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -7556,16 +8055,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1086.21</v>
+        <v>229.93</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -17,12 +17,13 @@
     <sheet name="DT Swiss Fatbike" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="DT SWISS 350 12x148" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Canyon S14 VCLS 2.0" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="GX-T-KIT" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="GX-T-CHAIN" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Cane Creek 40 IS41-IS52" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="ROCK SHOX SID" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Lake MX242" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="SUPERLOGIC-ERGOMAX" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Canyon S14 VCLS 2.0" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="GX-T-KIT" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GX-T-CHAIN" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Cane Creek 40 IS41-IS52" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ROCK SHOX SID" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Lake MX242" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -207,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$7</f>
+              <f>'FM2797'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$7</f>
+              <f>'FM2797'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -328,12 +329,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$7</f>
+              <f>'GX-T-KIT'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$7</f>
+              <f>'GX-T-KIT'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -449,12 +450,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$7</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$7</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -570,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$7</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$7</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -691,12 +692,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$5</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$5</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -812,12 +813,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$5</f>
+              <f>'Lake MX242'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$5</f>
+              <f>'Lake MX242'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -933,12 +934,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2</f>
+              <f>'FARGO-TI'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2</f>
+              <f>'FARGO-TI'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1054,12 +1055,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2</f>
+              <f>'FARGO-STEEL'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2</f>
+              <f>'FARGO-STEEL'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1175,12 +1176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$7</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$7</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1296,12 +1297,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$7</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$7</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1417,12 +1418,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$7</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$7</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1538,12 +1539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$7</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$7</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1659,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$7</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$7</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1780,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$7</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$7</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2522,7 +2523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2590,7 +2591,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -2628,7 +2629,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -2666,7 +2667,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -2704,7 +2705,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -2742,7 +2743,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -2780,11 +2781,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>130.35</v>
+        <v>210.02</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>130.35</v>
@@ -2796,12 +2797,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2819,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -2856,166 +2857,170 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1086.21</v>
+        <v>702.37</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1073.29</v>
+        <v>702.37</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike24.pl</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>SUPERLOGIC-ERGOMAX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>738.86</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>738.86</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1299.6</v>
+        <v>738.86</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1281.42</v>
+        <v>738.86</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1281.42</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>150.31</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -3024,86 +3029,124 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1386.53</v>
+        <v>151.69</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1386.53</v>
+        <v>150.31</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>1122.7</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E16" s="2" t="n">
         <v>1112.47</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>bike-discount.de</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -3119,12 +3162,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3136,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3284,6 +3327,26 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -3299,7 +3362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3330,129 +3393,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>857.1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>857.4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>858.72</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>861.5599999999999</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>840.59</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>738.86</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3462,7 +3404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3500,16 +3442,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1281.42</v>
+        <v>857.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3520,16 +3462,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1281.87</v>
+        <v>857.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3540,16 +3482,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1283.85</v>
+        <v>858.72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3560,16 +3502,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1288.09</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3580,16 +3522,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1287.76</v>
+        <v>840.59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3600,16 +3542,36 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1299.6</v>
+        <v>848.78</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>738.86</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3663,16 +3625,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>128.53</v>
+        <v>1281.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3683,16 +3645,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>128.57</v>
+        <v>1281.87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3703,16 +3665,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>128.77</v>
+        <v>1283.85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3723,16 +3685,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>129.2</v>
+        <v>1288.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3743,16 +3705,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1287.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3763,16 +3725,36 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1299.6</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3826,16 +3808,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>239.99</v>
+        <v>128.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3846,16 +3828,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>239.99</v>
+        <v>128.57</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3866,16 +3848,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>239.99</v>
+        <v>128.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3886,16 +3868,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>239.99</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -3906,16 +3888,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>150.31</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -3926,16 +3908,36 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3985,11 +3987,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3998,18 +4000,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4018,18 +4020,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1399</v>
+        <v>239.99</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4038,27 +4040,87 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>239.99</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>150.31</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>1386.53</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>buycycle.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+      <c r="B7" s="2" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4112,16 +4174,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1288.1</v>
+        <v>1799</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -4132,16 +4194,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1292.36</v>
+        <v>1799</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
     </row>
@@ -4152,16 +4214,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1112.47</v>
+        <v>1399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -4172,6 +4234,149 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1288.1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1292.36</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
         <v>1122.7</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -4180,6 +4385,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -4197,7 +4422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4507,24 +4732,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>857.1</v>
+        <v>151.69</v>
       </c>
       <c r="E8" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -4533,22 +4758,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4562,7 +4787,7 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E9" t="n">
         <v>199.99</v>
@@ -4589,7 +4814,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4603,7 +4828,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E10" t="n">
         <v>199.99</v>
@@ -4630,7 +4855,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4644,7 +4869,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E11" t="n">
         <v>199.99</v>
@@ -4671,7 +4896,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4685,14 +4910,14 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -4702,17 +4927,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4726,14 +4951,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>738.86</v>
+        <v>840.59</v>
       </c>
       <c r="E13" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4743,75 +4968,75 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>514.24</v>
+        <v>848.78</v>
       </c>
       <c r="E14" t="n">
-        <v>119.99</v>
+        <v>179.99</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>514.42</v>
+        <v>738.86</v>
       </c>
       <c r="E15" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -4820,22 +5045,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4849,10 +5074,10 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E16" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -4861,22 +5086,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4890,10 +5115,10 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E17" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -4902,22 +5127,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -4931,10 +5156,10 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E18" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -4948,17 +5173,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4972,7 +5197,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E19" t="n">
         <v>52.9</v>
@@ -4993,30 +5218,30 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>308.53</v>
+        <v>227.84</v>
       </c>
       <c r="E20" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -5025,39 +5250,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>308.64</v>
+        <v>229.93</v>
       </c>
       <c r="E21" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5066,39 +5291,39 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>309.11</v>
+        <v>229.93</v>
       </c>
       <c r="E22" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -5107,22 +5332,22 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5136,7 +5361,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E23" t="n">
         <v>71.98999999999999</v>
@@ -5163,7 +5388,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5177,7 +5402,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E24" t="n">
         <v>71.98999999999999</v>
@@ -5198,13 +5423,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5218,10 +5443,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E25" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -5230,39 +5455,39 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>5211.45</v>
+        <v>310.13</v>
       </c>
       <c r="E26" t="n">
-        <v>1199</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5271,39 +5496,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>11731.2</v>
+        <v>310.05</v>
       </c>
       <c r="E27" t="n">
-        <v>2699</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5312,39 +5537,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>130.35</v>
       </c>
       <c r="E28" t="n">
-        <v>2317.5</v>
+        <v>29.99</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5353,39 +5578,39 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>9935.59</v>
+        <v>210.02</v>
       </c>
       <c r="E29" t="n">
-        <v>2317.5</v>
+        <v>48.32</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5394,39 +5619,39 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>5211.45</v>
       </c>
       <c r="E30" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5435,39 +5660,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>5211.45</v>
       </c>
       <c r="E31" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5476,39 +5701,39 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>9981.24</v>
+        <v>11731.2</v>
       </c>
       <c r="E32" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5517,39 +5742,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>10073.01</v>
+        <v>11731.2</v>
       </c>
       <c r="E33" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5558,12 +5783,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -5578,19 +5803,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>128.53</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5599,16 +5824,16 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -5619,19 +5844,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>128.57</v>
+        <v>9935.59</v>
       </c>
       <c r="E35" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5640,16 +5865,16 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -5660,19 +5885,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>128.77</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5681,16 +5906,16 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -5701,19 +5926,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>129.2</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5722,16 +5947,16 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -5742,19 +5967,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>9981.24</v>
       </c>
       <c r="E38" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5763,16 +5988,16 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39">
@@ -5783,19 +6008,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E39" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5804,39 +6029,39 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>1281.42</v>
+        <v>10073.01</v>
       </c>
       <c r="E40" t="n">
-        <v>299</v>
+        <v>2317.5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5845,12 +6070,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -5860,24 +6085,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1281.87</v>
+        <v>128.53</v>
       </c>
       <c r="E41" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5886,39 +6111,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1283.85</v>
+        <v>128.57</v>
       </c>
       <c r="E42" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5927,39 +6152,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1288.09</v>
+        <v>128.77</v>
       </c>
       <c r="E43" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5968,39 +6193,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>1287.76</v>
+        <v>129.2</v>
       </c>
       <c r="E44" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6009,39 +6234,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6050,285 +6275,285 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4452.98</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>1190</v>
+        <v>18.9</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>4467.26</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>1190</v>
+        <v>18.9</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>4471.19</v>
+        <v>1281.42</v>
       </c>
       <c r="E48" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>4492.85</v>
+        <v>1281.87</v>
       </c>
       <c r="E49" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4485.35</v>
+        <v>1283.85</v>
       </c>
       <c r="E50" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>4524.98</v>
+        <v>1288.09</v>
       </c>
       <c r="E51" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>707.14</v>
+        <v>1287.76</v>
       </c>
       <c r="E52" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,39 +6562,39 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>707.39</v>
+        <v>1299.6</v>
       </c>
       <c r="E53" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6378,39 +6603,39 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>708.48</v>
+        <v>1299.6</v>
       </c>
       <c r="E54" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6419,217 +6644,217 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4452.98</v>
       </c>
       <c r="E55" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>465.1</v>
+        <v>4467.26</v>
       </c>
       <c r="E56" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>469.38</v>
+        <v>4471.19</v>
       </c>
       <c r="E57" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1288.1</v>
+        <v>4492.85</v>
       </c>
       <c r="E58" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1292.36</v>
+        <v>4485.35</v>
       </c>
       <c r="E59" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -6639,229 +6864,229 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1112.47</v>
+        <v>4524.98</v>
       </c>
       <c r="E60" t="n">
-        <v>258.3</v>
+        <v>1190</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1122.7</v>
+        <v>4524.98</v>
       </c>
       <c r="E61" t="n">
-        <v>258.3</v>
+        <v>1190</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1799</v>
+        <v>707.14</v>
       </c>
       <c r="E62" t="n">
-        <v>1799</v>
+        <v>165</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1799</v>
+        <v>707.39</v>
       </c>
       <c r="E63" t="n">
-        <v>1799</v>
+        <v>165</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1399</v>
+        <v>708.48</v>
       </c>
       <c r="E64" t="n">
-        <v>1399</v>
+        <v>165</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1386.53</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>319</v>
+        <v>165</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6870,176 +7095,176 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1074.05</v>
+        <v>465.1</v>
       </c>
       <c r="E66" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1073.61</v>
+        <v>469.38</v>
       </c>
       <c r="E67" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1073.29</v>
+        <v>469.38</v>
       </c>
       <c r="E68" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1076.61</v>
+        <v>1288.1</v>
       </c>
       <c r="E69" t="n">
-        <v>230.34</v>
+        <v>299.99</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -7049,83 +7274,657 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1075.73</v>
+        <v>1292.36</v>
       </c>
       <c r="E70" t="n">
-        <v>230.34</v>
+        <v>299.99</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1112.47</v>
+      </c>
+      <c r="E71" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="E72" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="E73" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E77" t="n">
+        <v>319</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E78" t="n">
+        <v>319</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D71" s="2" t="n">
+      <c r="D79" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E79" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E80" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E81" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E82" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E83" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
         <v>1086.21</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E84" t="n">
         <v>230.34</v>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I84" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="E85" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7139,7 +7938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7285,6 +8084,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>10073.01</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -7302,7 +8121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7348,6 +8167,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>11731.2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
@@ -7365,7 +8204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7411,6 +8250,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>5211.45</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
@@ -7428,7 +8287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7574,6 +8433,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>4524.98</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
@@ -7591,7 +8470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7737,6 +8616,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>469.38</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
@@ -7754,7 +8653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7902,6 +8801,26 @@
       <c r="D7" t="inlineStr">
         <is>
           <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>210.02</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>use-elitebikes.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
     </row>
@@ -7917,7 +8836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8068,6 +8987,26 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>229.93</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -208,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$8</f>
+              <f>'FM2797'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$8</f>
+              <f>'FM2797'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -329,12 +329,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$8</f>
+              <f>'GX-T-KIT'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$8</f>
+              <f>'GX-T-KIT'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -450,12 +450,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$8</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$8</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$8</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$8</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -692,12 +692,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$6</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$6</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -813,12 +813,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$6</f>
+              <f>'Lake MX242'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$6</f>
+              <f>'Lake MX242'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -934,12 +934,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2:$A$3</f>
+              <f>'FARGO-TI'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2:$B$3</f>
+              <f>'FARGO-TI'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1055,12 +1055,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2:$A$3</f>
+              <f>'FARGO-STEEL'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2:$B$3</f>
+              <f>'FARGO-STEEL'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1176,12 +1176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$8</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$8</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1297,12 +1297,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$8</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$8</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1418,12 +1418,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$8</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$8</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1539,12 +1539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$8</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$8</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1660,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$8</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$8</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1781,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$8</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$8</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -2705,7 +2705,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -2857,11 +2857,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>702.37</v>
+        <v>1086.21</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>702.37</v>
@@ -2873,12 +2873,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -3179,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3347,6 +3347,26 @@
       <c r="D8" t="inlineStr">
         <is>
           <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3570,6 +3590,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>738.86</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
@@ -3587,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3753,6 +3793,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1299.6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -3770,7 +3830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3936,6 +3996,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
@@ -3953,7 +4033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4119,6 +4199,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
@@ -4136,7 +4236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4262,6 +4362,26 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
@@ -4279,7 +4399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4405,6 +4525,26 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -4422,7 +4562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4773,24 +4913,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>857.1</v>
+        <v>151.69</v>
       </c>
       <c r="E9" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -4799,22 +4939,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4828,7 +4968,7 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E10" t="n">
         <v>199.99</v>
@@ -4855,7 +4995,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4869,7 +5009,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E11" t="n">
         <v>199.99</v>
@@ -4896,7 +5036,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4910,7 +5050,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E12" t="n">
         <v>199.99</v>
@@ -4937,7 +5077,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -4951,14 +5091,14 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -4968,17 +5108,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -4992,7 +5132,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>848.78</v>
+        <v>840.59</v>
       </c>
       <c r="E14" t="n">
         <v>179.99</v>
@@ -5019,7 +5159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5033,14 +5173,14 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E15" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5050,34 +5190,34 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>514.24</v>
+        <v>738.86</v>
       </c>
       <c r="E16" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -5086,39 +5226,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>514.42</v>
+        <v>738.86</v>
       </c>
       <c r="E17" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -5127,22 +5267,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5156,10 +5296,10 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E18" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -5168,22 +5308,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5197,10 +5337,10 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E19" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -5209,22 +5349,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5238,10 +5378,10 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E20" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -5255,17 +5395,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5279,7 +5419,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E21" t="n">
         <v>52.9</v>
@@ -5300,13 +5440,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5320,7 +5460,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>229.93</v>
+        <v>227.84</v>
       </c>
       <c r="E22" t="n">
         <v>52.9</v>
@@ -5341,30 +5481,30 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>308.53</v>
+        <v>229.93</v>
       </c>
       <c r="E23" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -5373,39 +5513,39 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>308.64</v>
+        <v>229.93</v>
       </c>
       <c r="E24" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -5414,39 +5554,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>309.11</v>
+        <v>229.93</v>
       </c>
       <c r="E25" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -5455,22 +5595,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5484,7 +5624,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E26" t="n">
         <v>71.98999999999999</v>
@@ -5511,7 +5651,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5525,7 +5665,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E27" t="n">
         <v>71.98999999999999</v>
@@ -5546,13 +5686,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5566,10 +5706,10 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E28" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5578,22 +5718,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5607,10 +5747,10 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>210.02</v>
+        <v>310.13</v>
       </c>
       <c r="E29" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5619,39 +5759,39 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>5211.45</v>
+        <v>310.05</v>
       </c>
       <c r="E30" t="n">
-        <v>1199</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5660,39 +5800,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>5211.45</v>
+        <v>130.35</v>
       </c>
       <c r="E31" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5701,39 +5841,39 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>11731.2</v>
+        <v>210.02</v>
       </c>
       <c r="E32" t="n">
-        <v>2699</v>
+        <v>48.32</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5742,39 +5882,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>11731.2</v>
+        <v>210.02</v>
       </c>
       <c r="E33" t="n">
-        <v>2699</v>
+        <v>48.32</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5783,39 +5923,39 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>5211.45</v>
       </c>
       <c r="E34" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5824,39 +5964,39 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>9935.59</v>
+        <v>5211.45</v>
       </c>
       <c r="E35" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5865,39 +6005,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>5211.45</v>
       </c>
       <c r="E36" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5906,39 +6046,39 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E37" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5947,39 +6087,39 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>9981.24</v>
+        <v>11731.2</v>
       </c>
       <c r="E38" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5988,39 +6128,39 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>10073.01</v>
+        <v>11731.2</v>
       </c>
       <c r="E39" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6029,22 +6169,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6058,7 +6198,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>10073.01</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E40" t="n">
         <v>2317.5</v>
@@ -6079,30 +6219,30 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>128.53</v>
+        <v>9935.59</v>
       </c>
       <c r="E41" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6111,39 +6251,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>128.57</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6152,39 +6292,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>128.77</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6193,39 +6333,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>129.2</v>
+        <v>9981.24</v>
       </c>
       <c r="E44" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6234,39 +6374,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E45" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6275,39 +6415,39 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E46" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6316,39 +6456,39 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E47" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6357,16 +6497,16 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
@@ -6377,19 +6517,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1281.42</v>
+        <v>128.53</v>
       </c>
       <c r="E48" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6398,16 +6538,16 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -6418,19 +6558,19 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1281.87</v>
+        <v>128.57</v>
       </c>
       <c r="E49" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6439,16 +6579,16 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -6459,19 +6599,19 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1283.85</v>
+        <v>128.77</v>
       </c>
       <c r="E50" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6480,16 +6620,16 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51">
@@ -6500,19 +6640,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1288.09</v>
+        <v>129.2</v>
       </c>
       <c r="E51" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6521,16 +6661,16 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52">
@@ -6541,19 +6681,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1287.76</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6562,16 +6702,16 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53">
@@ -6582,19 +6722,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6603,16 +6743,16 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54">
@@ -6623,19 +6763,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6644,326 +6784,326 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4452.98</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>1190</v>
+        <v>18.9</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4467.26</v>
+        <v>1281.42</v>
       </c>
       <c r="E56" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>4471.19</v>
+        <v>1281.87</v>
       </c>
       <c r="E57" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>4492.85</v>
+        <v>1283.85</v>
       </c>
       <c r="E58" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>4485.35</v>
+        <v>1288.09</v>
       </c>
       <c r="E59" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>4524.98</v>
+        <v>1287.76</v>
       </c>
       <c r="E60" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>4524.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E61" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>707.14</v>
+        <v>1299.6</v>
       </c>
       <c r="E62" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6972,39 +7112,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>707.39</v>
+        <v>1299.6</v>
       </c>
       <c r="E63" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7013,367 +7153,367 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>708.48</v>
+        <v>4452.98</v>
       </c>
       <c r="E64" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4467.26</v>
       </c>
       <c r="E65" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>465.1</v>
+        <v>4471.19</v>
       </c>
       <c r="E66" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>469.38</v>
+        <v>4492.85</v>
       </c>
       <c r="E67" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>469.38</v>
+        <v>4485.35</v>
       </c>
       <c r="E68" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1288.1</v>
+        <v>4524.98</v>
       </c>
       <c r="E69" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1292.36</v>
+        <v>4524.98</v>
       </c>
       <c r="E70" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1112.47</v>
+        <v>4524.98</v>
       </c>
       <c r="E71" t="n">
-        <v>258.3</v>
+        <v>1190</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1122.7</v>
+        <v>707.14</v>
       </c>
       <c r="E72" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7382,39 +7522,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1122.7</v>
+        <v>707.39</v>
       </c>
       <c r="E73" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7423,16 +7563,16 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -7443,37 +7583,37 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1799</v>
+        <v>708.48</v>
       </c>
       <c r="E74" t="n">
-        <v>1799</v>
+        <v>165</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -7484,37 +7624,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1799</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>1799</v>
+        <v>165</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -7525,37 +7665,37 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1399</v>
+        <v>465.1</v>
       </c>
       <c r="E76" t="n">
-        <v>1399</v>
+        <v>107.99</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77">
@@ -7566,19 +7706,19 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1386.53</v>
+        <v>469.38</v>
       </c>
       <c r="E77" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7587,16 +7727,16 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -7607,19 +7747,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1386.53</v>
+        <v>469.38</v>
       </c>
       <c r="E78" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7628,94 +7768,94 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1074.05</v>
+        <v>469.38</v>
       </c>
       <c r="E79" t="n">
-        <v>230.34</v>
+        <v>107.99</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1073.61</v>
+        <v>1288.1</v>
       </c>
       <c r="E80" t="n">
-        <v>230.34</v>
+        <v>299.99</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -7725,206 +7865,780 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1073.29</v>
+        <v>1292.36</v>
       </c>
       <c r="E81" t="n">
-        <v>230.34</v>
+        <v>299.99</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1076.61</v>
+        <v>1112.47</v>
       </c>
       <c r="E82" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1075.73</v>
+        <v>1122.7</v>
       </c>
       <c r="E83" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1086.21</v>
+        <v>1122.7</v>
       </c>
       <c r="E84" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Lake MX242</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1122.7</v>
+      </c>
+      <c r="E85" t="n">
+        <v>258.3</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E89" t="n">
+        <v>319</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E90" t="n">
+        <v>319</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E91" t="n">
+        <v>319</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D85" s="2" t="n">
+      <c r="D92" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E92" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E93" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E94" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E95" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E96" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E97" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
         <v>702.37</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E98" t="n">
         <v>702.37</v>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>PLN</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>bike24.pl</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
-      <c r="I85" t="n">
+      <c r="I98" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E99" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7938,7 +8652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8104,6 +8818,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>10073.01</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -8121,7 +8855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8187,6 +8921,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>11731.2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
@@ -8204,7 +8958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8270,6 +9024,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>5211.45</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
@@ -8287,7 +9061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8453,6 +9227,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>4524.98</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>laufcycles.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
@@ -8470,7 +9264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8636,6 +9430,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>469.38</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
@@ -8653,7 +9467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8819,6 +9633,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>210.02</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>use-elitebikes.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
@@ -8836,7 +9670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9007,6 +9841,26 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>229.93</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -208,12 +208,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$9</f>
+              <f>'FM2797'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$9</f>
+              <f>'FM2797'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -296,7 +296,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SRAM GX Eagle Transmission Upgrade Kit - najniższa cena dzienna (PLN)</a:t>
+              <a:t>Canyon S14 VCLS 2.0 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -310,7 +310,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'GX-T-KIT'!B1</f>
+              <f>'Canyon S14 VCLS 2.0'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -329,12 +329,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$9</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$9</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -417,7 +417,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
+              <a:t>SRAM GX Eagle Transmission Upgrade Kit - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -431,7 +431,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'GX-T-CHAIN'!B1</f>
+              <f>'GX-T-KIT'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -450,12 +450,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$9</f>
+              <f>'GX-T-KIT'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$9</f>
+              <f>'GX-T-KIT'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -538,7 +538,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Cane Creek 40 IS41/IS52 - najniższa cena dzienna (PLN)</a:t>
+              <a:t>SRAM GX Eagle Transmission Łańcuch - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -552,7 +552,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Cane Creek 40 IS41-IS52'!B1</f>
+              <f>'GX-T-CHAIN'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -571,12 +571,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$9</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$9</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -659,7 +659,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>ROCK SHOX SID SL Select+ - najniższa cena dzienna (PLN)</a:t>
+              <a:t>Cane Creek 40 IS41/IS52 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -673,7 +673,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'ROCK SHOX SID'!B1</f>
+              <f>'Cane Creek 40 IS41-IS52'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -692,12 +692,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$7</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$7</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -780,6 +780,127 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>ROCK SHOX SID SL Select+ - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'ROCK SHOX SID'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'ROCK SHOX SID'!$A$2:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'ROCK SHOX SID'!$B$2:$B$8</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Lake MX242 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -813,12 +934,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$7</f>
+              <f>'Lake MX242'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$7</f>
+              <f>'Lake MX242'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -934,12 +1055,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2:$A$4</f>
+              <f>'FARGO-TI'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2:$B$4</f>
+              <f>'FARGO-TI'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1055,12 +1176,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2:$A$4</f>
+              <f>'FARGO-STEEL'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2:$B$4</f>
+              <f>'FARGO-STEEL'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1176,12 +1297,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$9</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$9</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1297,12 +1418,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$9</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$9</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1418,12 +1539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$9</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$9</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1539,12 +1660,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$9</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$9</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1660,12 +1781,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$9</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$9</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1748,7 +1869,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Canyon S14 VCLS 2.0 - najniższa cena dzienna (PLN)</a:t>
+              <a:t>Ritchey Superlogic ErgoMax 42cm - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1762,7 +1883,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Canyon S14 VCLS 2.0'!B1</f>
+              <f>'SUPERLOGIC-ERGOMAX'!B1</f>
             </strRef>
           </tx>
           <spPr>
@@ -1781,12 +1902,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$9</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$A$2</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$9</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$B$2</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1992,6 +2113,33 @@
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2591,11 +2739,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10073.01</v>
+        <v>10030.37</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2629,18 +2777,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11731.2</v>
+        <v>11681.54</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11731.2</v>
+        <v>11681.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2667,18 +2815,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5211.45</v>
+        <v>5189.39</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5211.45</v>
+        <v>5189.39</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2688,7 +2836,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.bike-packing.de/salsa-fargo-steel-frameset-rahmenkit-275-29-gunmetal-grey</t>
         </is>
       </c>
     </row>
@@ -2705,28 +2853,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4524.98</v>
+        <v>3746.75</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4452.98</v>
+        <v>3746.75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
     </row>
@@ -2743,11 +2891,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>469.38</v>
+        <v>467.39</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>465.1</v>
@@ -2781,11 +2929,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>210.02</v>
+        <v>209.13</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>130.35</v>
@@ -2819,11 +2967,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>229.93</v>
+        <v>228.96</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>227.84</v>
@@ -2857,11 +3005,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1086.21</v>
+        <v>1078.59</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>702.37</v>
@@ -2895,32 +3043,28 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>1013.92</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1013.92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>starbike.com</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.starbike.com/de/ritchey-superlogic-ergo-max-di2-drop-lenker-31-8mm-15mm-5-12-interne-zugverlegung-ud-carbon-matt/</t>
         </is>
       </c>
     </row>
@@ -2937,18 +3081,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>738.86</v>
+        <v>735.73</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>738.86</v>
+        <v>735.73</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2975,11 +3119,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1299.6</v>
+        <v>1294.1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1281.42</v>
@@ -3013,11 +3157,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>81.40000000000001</v>
@@ -3051,28 +3195,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>151.69</v>
+        <v>134.13</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>150.31</v>
+        <v>134.13</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Cane+Creek+40+Steuersatz+tapered&amp;prds=localAnnotatedOfferId:1,catalogid:3166988792593044830,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -3089,18 +3233,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1386.53</v>
+        <v>1380.66</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1386.53</v>
+        <v>1380.66</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3127,11 +3271,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1122.7</v>
+        <v>1117.95</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1112.47</v>
@@ -3162,12 +3306,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3179,7 +3324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3365,6 +3510,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -3382,7 +3547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3413,8 +3578,29 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1013.92</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>starbike.com</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.starbike.com/de/ritchey-superlogic-ergo-max-di2-drop-lenker-31-8mm-15mm-5-12-interne-zugverlegung-ud-carbon-matt/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3424,7 +3610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3610,6 +3796,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>735.73</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
@@ -3627,7 +3833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3813,6 +4019,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1294.1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -3830,7 +4056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4016,6 +4242,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
@@ -4033,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4221,6 +4467,26 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>134.13</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bike24.de</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Cane+Creek+40+Steuersatz+tapered&amp;prds=localAnnotatedOfferId:1,catalogid:3166988792593044830,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4382,6 +4648,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
@@ -4399,7 +4685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4545,6 +4831,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1117.95</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -4562,7 +4868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I99"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4954,24 +5260,24 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>857.1</v>
+        <v>134.13</v>
       </c>
       <c r="E10" t="n">
-        <v>199.99</v>
+        <v>30.99</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -4980,22 +5286,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Cane+Creek+40+Steuersatz+tapered&amp;prds=localAnnotatedOfferId:1,catalogid:3166988792593044830,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5009,7 +5315,7 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E11" t="n">
         <v>199.99</v>
@@ -5036,7 +5342,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5050,7 +5356,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E12" t="n">
         <v>199.99</v>
@@ -5077,7 +5383,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5091,7 +5397,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E13" t="n">
         <v>199.99</v>
@@ -5118,7 +5424,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5132,14 +5438,14 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5149,17 +5455,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5173,7 +5479,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>848.78</v>
+        <v>840.59</v>
       </c>
       <c r="E15" t="n">
         <v>179.99</v>
@@ -5200,7 +5506,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5214,14 +5520,14 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E16" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5231,17 +5537,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5282,24 +5588,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>514.24</v>
+        <v>738.86</v>
       </c>
       <c r="E18" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -5308,39 +5614,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>514.42</v>
+        <v>735.73</v>
       </c>
       <c r="E19" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -5349,22 +5655,22 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5378,10 +5684,10 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E20" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -5390,22 +5696,22 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5419,10 +5725,10 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E21" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -5431,22 +5737,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5460,10 +5766,10 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E22" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -5477,17 +5783,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5501,7 +5807,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E23" t="n">
         <v>52.9</v>
@@ -5522,13 +5828,13 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5542,7 +5848,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>229.93</v>
+        <v>227.84</v>
       </c>
       <c r="E24" t="n">
         <v>52.9</v>
@@ -5563,13 +5869,13 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5604,30 +5910,30 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>308.53</v>
+        <v>229.93</v>
       </c>
       <c r="E26" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5636,39 +5942,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>308.64</v>
+        <v>229.93</v>
       </c>
       <c r="E27" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5677,39 +5983,39 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>309.11</v>
+        <v>228.96</v>
       </c>
       <c r="E28" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5718,22 +6024,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5747,7 +6053,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E29" t="n">
         <v>71.98999999999999</v>
@@ -5774,7 +6080,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5788,7 +6094,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E30" t="n">
         <v>71.98999999999999</v>
@@ -5809,13 +6115,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5829,10 +6135,10 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E31" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5841,22 +6147,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5870,10 +6176,10 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>210.02</v>
+        <v>310.13</v>
       </c>
       <c r="E32" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5882,22 +6188,22 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5911,10 +6217,10 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>210.02</v>
+        <v>310.05</v>
       </c>
       <c r="E33" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5923,16 +6229,16 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
@@ -5943,19 +6249,19 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>5211.45</v>
+        <v>130.35</v>
       </c>
       <c r="E34" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5964,16 +6270,16 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -5984,19 +6290,19 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>5211.45</v>
+        <v>210.02</v>
       </c>
       <c r="E35" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -6005,16 +6311,16 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36">
@@ -6025,19 +6331,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>5211.45</v>
+        <v>210.02</v>
       </c>
       <c r="E36" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6046,39 +6352,39 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>11731.2</v>
+        <v>209.13</v>
       </c>
       <c r="E37" t="n">
-        <v>2699</v>
+        <v>48.32</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6087,39 +6393,39 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E38" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6133,34 +6439,34 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E39" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6174,34 +6480,34 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>5211.45</v>
       </c>
       <c r="E40" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6210,39 +6516,39 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>9935.59</v>
+        <v>5189.39</v>
       </c>
       <c r="E41" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6251,39 +6557,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-steel-frameset-rahmenkit-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>11731.2</v>
       </c>
       <c r="E42" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6292,39 +6598,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E43" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6333,39 +6639,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>9981.24</v>
+        <v>11731.2</v>
       </c>
       <c r="E44" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6374,39 +6680,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>10073.01</v>
+        <v>11681.54</v>
       </c>
       <c r="E45" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6415,22 +6721,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6444,7 +6750,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>10073.01</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E46" t="n">
         <v>2317.5</v>
@@ -6465,13 +6771,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6485,7 +6791,7 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>10073.01</v>
+        <v>9935.59</v>
       </c>
       <c r="E47" t="n">
         <v>2317.5</v>
@@ -6506,30 +6812,30 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>128.53</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6538,39 +6844,39 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>128.57</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6579,39 +6885,39 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>128.77</v>
+        <v>9981.24</v>
       </c>
       <c r="E50" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6620,39 +6926,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>129.2</v>
+        <v>10073.01</v>
       </c>
       <c r="E51" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6661,39 +6967,39 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E52" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6702,39 +7008,39 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E53" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6743,39 +7049,39 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10030.37</v>
       </c>
       <c r="E54" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6784,22 +7090,22 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>77</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6813,10 +7119,10 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>128.53</v>
       </c>
       <c r="E55" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6825,39 +7131,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1281.42</v>
+        <v>128.57</v>
       </c>
       <c r="E56" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6866,39 +7172,39 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1281.87</v>
+        <v>128.77</v>
       </c>
       <c r="E57" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6907,39 +7213,39 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1283.85</v>
+        <v>129.2</v>
       </c>
       <c r="E58" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6948,39 +7254,39 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1288.09</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6989,39 +7295,39 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1287.76</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7030,39 +7336,39 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7071,39 +7377,39 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7112,39 +7418,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.8</v>
       </c>
       <c r="E63" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7153,16 +7459,16 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64">
@@ -7173,37 +7479,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>4452.98</v>
+        <v>1281.42</v>
       </c>
       <c r="E64" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
@@ -7214,37 +7520,37 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>4467.26</v>
+        <v>1281.87</v>
       </c>
       <c r="E65" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
@@ -7255,37 +7561,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>4471.19</v>
+        <v>1283.85</v>
       </c>
       <c r="E66" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -7296,37 +7602,37 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>4492.85</v>
+        <v>1288.09</v>
       </c>
       <c r="E67" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
@@ -7337,37 +7643,37 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>4485.35</v>
+        <v>1287.76</v>
       </c>
       <c r="E68" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -7378,37 +7684,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>4524.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E69" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
@@ -7419,37 +7725,37 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>4524.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E70" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
     </row>
     <row r="71">
@@ -7460,60 +7766,60 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>4524.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E71" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>707.14</v>
+        <v>1294.1</v>
       </c>
       <c r="E72" t="n">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7522,408 +7828,408 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>707.39</v>
+        <v>4452.98</v>
       </c>
       <c r="E73" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>708.48</v>
+        <v>4467.26</v>
       </c>
       <c r="E74" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4471.19</v>
       </c>
       <c r="E75" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>465.1</v>
+        <v>4492.85</v>
       </c>
       <c r="E76" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>469.38</v>
+        <v>4485.35</v>
       </c>
       <c r="E77" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E78" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E79" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1288.1</v>
+        <v>4524.98</v>
       </c>
       <c r="E80" t="n">
-        <v>299.99</v>
+        <v>1190</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1292.36</v>
+        <v>3746.75</v>
       </c>
       <c r="E81" t="n">
-        <v>299.99</v>
+        <v>990</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1112.47</v>
+        <v>707.14</v>
       </c>
       <c r="E82" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7932,39 +8238,39 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1122.7</v>
+        <v>707.39</v>
       </c>
       <c r="E83" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7973,39 +8279,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1122.7</v>
+        <v>708.48</v>
       </c>
       <c r="E84" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8014,39 +8320,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1122.7</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E85" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8055,162 +8361,162 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1799</v>
+        <v>465.1</v>
       </c>
       <c r="E86" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1799</v>
+        <v>469.38</v>
       </c>
       <c r="E87" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1399</v>
+        <v>469.38</v>
       </c>
       <c r="E88" t="n">
-        <v>1399</v>
+        <v>107.99</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1386.53</v>
+        <v>469.38</v>
       </c>
       <c r="E89" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8219,39 +8525,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1386.53</v>
+        <v>467.39</v>
       </c>
       <c r="E90" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8260,39 +8566,39 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1386.53</v>
+        <v>1288.1</v>
       </c>
       <c r="E91" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8301,285 +8607,285 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1074.05</v>
+        <v>1292.36</v>
       </c>
       <c r="E92" t="n">
-        <v>230.34</v>
+        <v>299.99</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1073.61</v>
+        <v>1112.47</v>
       </c>
       <c r="E93" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1073.29</v>
+        <v>1122.7</v>
       </c>
       <c r="E94" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1076.61</v>
+        <v>1122.7</v>
       </c>
       <c r="E95" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1075.73</v>
+        <v>1122.7</v>
       </c>
       <c r="E96" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1086.21</v>
+        <v>1117.95</v>
       </c>
       <c r="E97" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>702.37</v>
+        <v>1799</v>
       </c>
       <c r="E98" t="n">
-        <v>702.37</v>
+        <v>1799</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8588,57 +8894,672 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1799</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E101" t="n">
+        <v>319</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E102" t="n">
+        <v>319</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E103" t="n">
+        <v>319</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="E104" t="n">
+        <v>319</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
-      <c r="D99" s="2" t="n">
+      <c r="D105" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E105" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E106" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E107" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E108" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E109" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
         <v>1086.21</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E110" t="n">
         <v>230.34</v>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>bikeshopzizers.ch</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
-      <c r="I99" t="n">
+      <c r="I110" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="E111" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E112" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="E113" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1013.92</v>
+      </c>
+      <c r="E114" t="n">
+        <v>216.53</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>starbike.com</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://www.starbike.com/de/ritchey-superlogic-ergo-max-di2-drop-lenker-31-8mm-15mm-5-12-interne-zugverlegung-ud-carbon-matt/</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -8652,7 +9573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8838,6 +9759,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>10030.37</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -8855,7 +9796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8941,6 +9882,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>11681.54</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
@@ -8958,7 +9919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9046,6 +10007,26 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>5189.39</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-steel-frameset-rahmenkit-275-29-gunmetal-grey</t>
         </is>
       </c>
     </row>
@@ -9061,7 +10042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9249,6 +10230,26 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>3746.75</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>fullsusbikes.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
     </row>
@@ -9264,7 +10265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9450,6 +10451,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>467.39</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
@@ -9467,7 +10488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9653,6 +10674,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>209.13</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>use-elitebikes.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
@@ -9670,7 +10711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9861,6 +10902,26 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>228.96</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -2836,7 +2836,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-steel-frameset-rahmenkit-275-29-gunmetal-grey</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
     </row>
@@ -2857,24 +2857,24 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3746.75</v>
+        <v>4503.67</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3746.75</v>
+        <v>4452.98</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>
@@ -3047,10 +3047,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1013.92</v>
+        <v>860.86</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1013.92</v>
+        <v>860.86</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -3059,12 +3059,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>starbike.com</t>
+          <t>actionsports.de</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.starbike.com/de/ritchey-superlogic-ergo-max-di2-drop-lenker-31-8mm-15mm-5-12-interne-zugverlegung-ud-carbon-matt/</t>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
     </row>
@@ -3585,16 +3585,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1013.92</v>
+        <v>860.86</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>starbike.com</t>
+          <t>actionsports.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.starbike.com/de/ritchey-superlogic-ergo-max-di2-drop-lenker-31-8mm-15mm-5-12-interne-zugverlegung-ud-carbon-matt/</t>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
     </row>
@@ -5295,7 +5295,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
@@ -6402,7 +6402,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
@@ -6562,11 +6562,11 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-steel-frameset-rahmenkit-275-29-gunmetal-grey</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64">
@@ -7837,7 +7837,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
@@ -8185,10 +8185,10 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3746.75</v>
+        <v>4503.67</v>
       </c>
       <c r="E81" t="n">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8197,16 +8197,16 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="91">
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105">
@@ -9538,28 +9538,28 @@
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1013.92</v>
+        <v>860.86</v>
       </c>
       <c r="E114" t="n">
-        <v>216.53</v>
+        <v>198.9</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>starbike.com</t>
+          <t>actionsports.de</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.starbike.com/de/ritchey-superlogic-ergo-max-di2-drop-lenker-31-8mm-15mm-5-12-interne-zugverlegung-ud-carbon-matt/</t>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-steel-frameset-rahmenkit-275-29-gunmetal-grey</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
     </row>
@@ -10240,16 +10240,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>3746.75</v>
+        <v>4503.67</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -13,17 +13,18 @@
     <sheet name="FARGO-TI" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="FARGO-STEEL" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="LAUF-CARBONARA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Lake MX190-X Wide" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DT Swiss Fatbike" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="DT SWISS 350 12x148" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="SUPERLOGIC-ERGOMAX" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Canyon S14 VCLS 2.0" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="GX-T-KIT" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="GX-T-CHAIN" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Cane Creek 40 IS41-IS52" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="ROCK SHOX SID" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Lake MX242" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="IBS-V1X" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Lake MX190-X Wide" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DT Swiss Fatbike" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DT SWISS 350 12x148" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Ritchey WCS Carbon ErgoMax" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="SUPERLOGIC-ERGOMAX" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Canyon S14 VCLS 2.0" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="GX-T-KIT" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="GX-T-CHAIN" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Cane Creek 40 IS41-IS52" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ROCK SHOX SID" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Lake MX242" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -296,6 +297,127 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Ritchey Superlogic ErgoMax 42cm - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'SUPERLOGIC-ERGOMAX'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'SUPERLOGIC-ERGOMAX'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'SUPERLOGIC-ERGOMAX'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Canyon S14 VCLS 2.0 - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -404,7 +526,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -525,7 +647,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -646,7 +768,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -767,7 +889,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -888,7 +1010,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1385,6 +1507,127 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Infinity Bike Seat V1X - najniższa cena dzienna (PLN)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'IBS-V1X'!B1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'IBS-V1X'!$A$2</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'IBS-V1X'!$B$2</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Data</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>PLN</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Lake MX190-X Wide - najniższa cena dzienna (PLN)</a:t>
             </a:r>
           </a:p>
@@ -1493,7 +1736,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1614,7 +1857,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1735,7 +1978,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="12"/>
   <chart>
@@ -1787,127 +2030,6 @@
           <val>
             <numRef>
               <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$10</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>Data</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>PLN</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Ritchey Superlogic ErgoMax 42cm - najniższa cena dzienna (PLN)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'SUPERLOGIC-ERGOMAX'!B1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="6"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$A$2</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$B$2</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2140,6 +2262,33 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7920000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2671,7 +2820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2857,36 +3006,36 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>4503.67</v>
+        <v>3746.75</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4452.98</v>
+        <v>3746.75</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2895,36 +3044,36 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>467.39</v>
+        <v>1464.64</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>465.1</v>
+        <v>1464.64</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2933,36 +3082,36 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>209.13</v>
+        <v>467.39</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>130.35</v>
+        <v>465.1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2971,36 +3120,36 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>228.96</v>
+        <v>129.8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>227.84</v>
+        <v>129.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3009,36 +3158,36 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1078.59</v>
+        <v>228.96</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>702.37</v>
+        <v>227.84</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SUPERLOGIC-ERGOMAX</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ritchey Superlogic ErgoMax 42cm</t>
+          <t>Ritchey WCS Carbon ErgoMax</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3047,36 +3196,36 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>860.86</v>
+        <v>1078.59</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>860.86</v>
+        <v>702.37</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>actionsports.de</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>SUPERLOGIC-ERGOMAX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3085,10 +3234,10 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>735.73</v>
+        <v>860.86</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>735.73</v>
+        <v>860.86</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -3097,24 +3246,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>actionsports.de</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3123,36 +3272,36 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1294.1</v>
+        <v>735.73</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1281.42</v>
+        <v>735.73</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3161,36 +3310,36 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>81.8</v>
+        <v>1294.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1281.42</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cane Creek 40 IS41/IS52</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3199,36 +3348,36 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>134.13</v>
+        <v>81.8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>134.13</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Cane+Creek+40+Steuersatz+tapered&amp;prds=localAnnotatedOfferId:1,catalogid:3166988792593044830,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3237,60 +3386,98 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1380.66</v>
+        <v>151.05</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1380.66</v>
+        <v>150.31</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Lake MX242</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D16" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>1117.95</v>
       </c>
-      <c r="E16" s="2" t="n">
+      <c r="E17" s="2" t="n">
         <v>1112.47</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>bike-discount.de</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H17" s="3" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -3313,6 +3500,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3362,16 +3550,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1074.05</v>
+        <v>514.24</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
     </row>
@@ -3382,16 +3570,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1073.61</v>
+        <v>514.42</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
     </row>
@@ -3402,16 +3590,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1073.29</v>
+        <v>398.89</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
     </row>
@@ -3422,16 +3610,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1076.61</v>
+        <v>227.89</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -3442,16 +3630,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1075.73</v>
+        <v>227.84</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -3462,16 +3650,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1086.21</v>
+        <v>229.93</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -3482,16 +3670,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>702.37</v>
+        <v>229.93</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -3502,16 +3690,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1086.21</v>
+        <v>229.93</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -3522,16 +3710,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1078.59</v>
+        <v>228.96</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
     </row>
@@ -3542,6 +3730,229 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3595,229 +4006,6 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Najniższa cena (PLN)</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sklep</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-07-05</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>857.1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>857.4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>858.72</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>861.5599999999999</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>840.59</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>848.78</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>738.86</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>738.86</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>735.73</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>canyon.com</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3871,16 +4059,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1281.42</v>
+        <v>857.1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3891,16 +4079,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1281.87</v>
+        <v>857.4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3911,16 +4099,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1283.85</v>
+        <v>858.72</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3931,16 +4119,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1288.09</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
     </row>
@@ -3951,16 +4139,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1287.76</v>
+        <v>840.59</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3971,16 +4159,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1299.6</v>
+        <v>848.78</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -3991,16 +4179,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1299.6</v>
+        <v>738.86</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -4011,16 +4199,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1299.6</v>
+        <v>738.86</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -4031,16 +4219,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1294.1</v>
+        <v>735.73</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
     </row>
@@ -4094,16 +4282,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>128.53</v>
+        <v>1281.42</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4114,16 +4302,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>128.57</v>
+        <v>1281.87</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4134,16 +4322,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>128.77</v>
+        <v>1283.85</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4154,16 +4342,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>129.2</v>
+        <v>1288.09</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4174,16 +4362,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>1287.76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4194,16 +4382,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4214,16 +4402,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4234,16 +4422,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>1299.6</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4254,16 +4442,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>81.8</v>
+        <v>1294.1</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
     </row>
@@ -4317,16 +4505,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>239.99</v>
+        <v>128.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -4337,16 +4525,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>239.99</v>
+        <v>128.57</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -4357,16 +4545,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>239.99</v>
+        <v>128.77</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -4377,16 +4565,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>239.99</v>
+        <v>129.2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
     </row>
@@ -4397,16 +4585,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>150.31</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -4417,16 +4605,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -4437,16 +4625,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -4457,16 +4645,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>151.69</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>last-bikes.com</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -4477,16 +4665,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>134.13</v>
+        <v>81.8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Cane+Creek+40+Steuersatz+tapered&amp;prds=localAnnotatedOfferId:1,catalogid:3166988792593044830,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4536,11 +4724,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4549,18 +4737,18 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1799</v>
+        <v>239.99</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4569,18 +4757,18 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1399</v>
+        <v>239.99</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4589,87 +4777,127 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>1386.53</v>
+        <v>239.99</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.centrumrowerowe.pl/stery-zintegrowane-1-1-8-1-1-2-tapered-cane-creek-40-series-is42-is52-short-pd10206/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1386.53</v>
+        <v>150.31</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1386.53</v>
+        <v>151.69</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>151.69</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>1380.66</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>buycycle.com</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+      <c r="B10" s="2" t="n">
+        <v>151.05</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
     </row>
@@ -4723,6 +4951,189 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Najniższa cena (PLN)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sklep</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
         <v>1288.1</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -4868,7 +5279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5274,10 +5685,10 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>134.13</v>
+        <v>151.05</v>
       </c>
       <c r="E10" t="n">
-        <v>30.99</v>
+        <v>34.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -5286,16 +5697,16 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Cane+Creek+40+Steuersatz+tapered&amp;prds=localAnnotatedOfferId:1,catalogid:3166988792593044830,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -6033,7 +6444,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29">
@@ -6381,10 +6792,10 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>209.13</v>
+        <v>129.8</v>
       </c>
       <c r="E37" t="n">
-        <v>48.32</v>
+        <v>29.99</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6393,16 +6804,16 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -7468,7 +7879,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64">
@@ -7837,30 +8248,30 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>4452.98</v>
+        <v>1464.64</v>
       </c>
       <c r="E73" t="n">
-        <v>1190</v>
+        <v>387</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7869,22 +8280,22 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7898,7 +8309,7 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>4467.26</v>
+        <v>4452.98</v>
       </c>
       <c r="E74" t="n">
         <v>1190</v>
@@ -7925,7 +8336,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7939,7 +8350,7 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4471.19</v>
+        <v>4467.26</v>
       </c>
       <c r="E75" t="n">
         <v>1190</v>
@@ -7966,7 +8377,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7980,7 +8391,7 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>4492.85</v>
+        <v>4471.19</v>
       </c>
       <c r="E76" t="n">
         <v>1190</v>
@@ -8001,13 +8412,13 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8021,7 +8432,7 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>4485.35</v>
+        <v>4492.85</v>
       </c>
       <c r="E77" t="n">
         <v>1190</v>
@@ -8048,7 +8459,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8062,7 +8473,7 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4524.98</v>
+        <v>4485.35</v>
       </c>
       <c r="E78" t="n">
         <v>1190</v>
@@ -8089,7 +8500,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8124,13 +8535,13 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8171,7 +8582,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8185,7 +8596,7 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4503.67</v>
+        <v>4524.98</v>
       </c>
       <c r="E81" t="n">
         <v>1190</v>
@@ -8212,48 +8623,48 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>707.14</v>
+        <v>3746.75</v>
       </c>
       <c r="E82" t="n">
-        <v>165</v>
+        <v>990</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8267,7 +8678,7 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>707.39</v>
+        <v>707.14</v>
       </c>
       <c r="E83" t="n">
         <v>165</v>
@@ -8294,7 +8705,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8308,7 +8719,7 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>708.48</v>
+        <v>707.39</v>
       </c>
       <c r="E84" t="n">
         <v>165</v>
@@ -8329,13 +8740,13 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8349,7 +8760,7 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>708.48</v>
       </c>
       <c r="E85" t="n">
         <v>165</v>
@@ -8376,7 +8787,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8390,10 +8801,10 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>465.1</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E86" t="n">
-        <v>107.99</v>
+        <v>165</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8402,22 +8813,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8431,7 +8842,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>469.38</v>
+        <v>465.1</v>
       </c>
       <c r="E87" t="n">
         <v>107.99</v>
@@ -8452,13 +8863,13 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8493,13 +8904,13 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8540,7 +8951,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8554,7 +8965,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>467.39</v>
+        <v>469.38</v>
       </c>
       <c r="E90" t="n">
         <v>107.99</v>
@@ -8575,30 +8986,30 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1288.1</v>
+        <v>467.39</v>
       </c>
       <c r="E91" t="n">
-        <v>299.99</v>
+        <v>107.99</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8607,22 +9018,22 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8636,7 +9047,7 @@
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1292.36</v>
+        <v>1288.1</v>
       </c>
       <c r="E92" t="n">
         <v>299.99</v>
@@ -8653,17 +9064,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8677,10 +9088,10 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1112.47</v>
+        <v>1292.36</v>
       </c>
       <c r="E93" t="n">
-        <v>258.3</v>
+        <v>299.99</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8698,13 +9109,13 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8718,7 +9129,7 @@
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1122.7</v>
+        <v>1112.47</v>
       </c>
       <c r="E94" t="n">
         <v>258.3</v>
@@ -8739,13 +9150,13 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8780,13 +9191,13 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8827,7 +9238,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8841,7 +9252,7 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1117.95</v>
+        <v>1122.7</v>
       </c>
       <c r="E97" t="n">
         <v>258.3</v>
@@ -8862,54 +9273,54 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1799</v>
+        <v>1117.95</v>
       </c>
       <c r="E98" t="n">
-        <v>1799</v>
+        <v>258.3</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8944,13 +9355,13 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8964,10 +9375,10 @@
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="E100" t="n">
-        <v>1399</v>
+        <v>1799</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8981,17 +9392,17 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9005,34 +9416,34 @@
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1386.53</v>
+        <v>1399</v>
       </c>
       <c r="E101" t="n">
-        <v>319</v>
+        <v>1399</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9067,13 +9478,13 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9114,7 +9525,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9128,7 +9539,7 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1380.66</v>
+        <v>1386.53</v>
       </c>
       <c r="E104" t="n">
         <v>319</v>
@@ -9149,54 +9560,54 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1074.05</v>
+        <v>1380.66</v>
       </c>
       <c r="E105" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9210,7 +9621,7 @@
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1073.61</v>
+        <v>1074.05</v>
       </c>
       <c r="E106" t="n">
         <v>230.34</v>
@@ -9237,7 +9648,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9251,7 +9662,7 @@
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1073.29</v>
+        <v>1073.61</v>
       </c>
       <c r="E107" t="n">
         <v>230.34</v>
@@ -9278,7 +9689,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9292,7 +9703,7 @@
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1076.61</v>
+        <v>1073.29</v>
       </c>
       <c r="E108" t="n">
         <v>230.34</v>
@@ -9319,7 +9730,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9333,7 +9744,7 @@
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1075.73</v>
+        <v>1076.61</v>
       </c>
       <c r="E109" t="n">
         <v>230.34</v>
@@ -9360,7 +9771,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9374,7 +9785,7 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1086.21</v>
+        <v>1075.73</v>
       </c>
       <c r="E110" t="n">
         <v>230.34</v>
@@ -9401,7 +9812,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9415,34 +9826,34 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>702.37</v>
+        <v>1086.21</v>
       </c>
       <c r="E111" t="n">
-        <v>702.37</v>
+        <v>230.34</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>bikeshopzizers.ch</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9456,34 +9867,34 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1086.21</v>
+        <v>702.37</v>
       </c>
       <c r="E112" t="n">
-        <v>230.34</v>
+        <v>702.37</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike24.pl</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9497,7 +9908,7 @@
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1078.59</v>
+        <v>1086.21</v>
       </c>
       <c r="E113" t="n">
         <v>230.34</v>
@@ -9529,37 +9940,78 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="E114" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>SUPERLOGIC-ERGOMAX</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Ritchey Superlogic ErgoMax 42cm</t>
         </is>
       </c>
-      <c r="D114" s="2" t="n">
+      <c r="D115" s="2" t="n">
         <v>860.86</v>
       </c>
-      <c r="E114" t="n">
+      <c r="E115" t="n">
         <v>198.9</v>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>actionsports.de</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
-      <c r="I114" t="n">
-        <v>20</v>
+      <c r="I115" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -10240,16 +10692,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>4503.67</v>
+        <v>3746.75</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
     </row>
@@ -10265,7 +10717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10299,180 +10751,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>707.14</v>
+        <v>1464.64</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-07-06</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>707.39</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>sport-bittl.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>708.48</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>sport-bittl.com</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>710.8200000000001</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>sport-bittl.com</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>465.1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>alltricks.nl</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>469.38</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>alltricks.nl</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>469.38</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>alltricks.nl</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>469.38</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>alltricks.nl</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>467.39</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>alltricks.nl</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
     </row>
@@ -10526,16 +10818,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>308.53</v>
+        <v>707.14</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -10546,16 +10838,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>308.64</v>
+        <v>707.39</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -10566,16 +10858,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>309.11</v>
+        <v>708.48</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -10586,16 +10878,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>310.13</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
     </row>
@@ -10606,16 +10898,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>310.05</v>
+        <v>465.1</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -10626,16 +10918,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>130.35</v>
+        <v>469.38</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -10646,16 +10938,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>210.02</v>
+        <v>469.38</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -10666,16 +10958,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>210.02</v>
+        <v>469.38</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -10686,16 +10978,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>209.13</v>
+        <v>467.39</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
     </row>
@@ -10749,16 +11041,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>514.24</v>
+        <v>308.53</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -10769,16 +11061,16 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>514.42</v>
+        <v>308.64</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -10789,16 +11081,16 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>398.89</v>
+        <v>309.11</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -10809,16 +11101,16 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>227.89</v>
+        <v>310.13</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -10829,16 +11121,16 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>227.84</v>
+        <v>310.05</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
     </row>
@@ -10849,16 +11141,16 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>229.93</v>
+        <v>130.35</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -10869,16 +11161,16 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>229.93</v>
+        <v>210.02</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
     </row>
@@ -10889,16 +11181,16 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>229.93</v>
+        <v>210.02</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
     </row>
@@ -10909,16 +11201,16 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>228.96</v>
+        <v>129.8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$10</f>
+              <f>'FM2797'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$10</f>
+              <f>'FM2797'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -330,12 +330,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$A$2</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$B$2</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -451,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$10</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$10</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -572,12 +572,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$10</f>
+              <f>'GX-T-KIT'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$10</f>
+              <f>'GX-T-KIT'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,12 +693,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$10</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$10</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -814,12 +814,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$10</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$10</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -935,12 +935,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$8</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$8</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1056,12 +1056,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$8</f>
+              <f>'Lake MX242'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$8</f>
+              <f>'Lake MX242'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1177,12 +1177,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2:$A$5</f>
+              <f>'FARGO-TI'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2:$B$5</f>
+              <f>'FARGO-TI'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1298,12 +1298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2:$A$5</f>
+              <f>'FARGO-STEEL'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2:$B$5</f>
+              <f>'FARGO-STEEL'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,12 +1419,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$10</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$10</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1540,12 +1540,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'IBS-V1X'!$A$2</f>
+              <f>'IBS-V1X'!$A$2:$A$3</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'IBS-V1X'!$B$2</f>
+              <f>'IBS-V1X'!$B$2:$B$3</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1661,12 +1661,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$10</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$10</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1782,12 +1782,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$10</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$10</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1903,12 +1903,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$10</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$10</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$10</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$10</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2888,11 +2888,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10030.37</v>
+        <v>10059.57</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2926,11 +2926,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11681.54</v>
+        <v>11715.55</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11681.54</v>
@@ -2964,11 +2964,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5189.39</v>
+        <v>5204.5</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>5189.39</v>
@@ -3002,11 +3002,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3746.75</v>
+        <v>3769.52</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>3746.75</v>
@@ -3040,11 +3040,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1464.64</v>
+        <v>1473.54</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1464.64</v>
@@ -3078,11 +3078,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>467.39</v>
+        <v>468.75</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>465.1</v>
@@ -3116,11 +3116,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>129.8</v>
+        <v>130.18</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>129.8</v>
@@ -3154,11 +3154,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>228.96</v>
+        <v>229.62</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>227.84</v>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1078.59</v>
+        <v>1079.4</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>702.37</v>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>860.86</v>
+        <v>863.37</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>860.86</v>
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>735.73</v>
+        <v>737.88</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>735.73</v>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1294.1</v>
+        <v>1297.87</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1281.42</v>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>81.8</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>81.40000000000001</v>
@@ -3382,11 +3382,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>151.05</v>
+        <v>151.49</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>150.31</v>
@@ -3420,11 +3420,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1380.66</v>
+        <v>1384.68</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1380.66</v>
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1117.95</v>
+        <v>1121.2</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1112.47</v>
@@ -3512,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3718,6 +3718,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>229.62</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
@@ -3735,7 +3755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3941,6 +3961,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1079.4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -3958,7 +3998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4004,6 +4044,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>863.37</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
@@ -4021,7 +4081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4227,6 +4287,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>737.88</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
@@ -4244,7 +4324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4450,6 +4530,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1297.87</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -4467,7 +4567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4673,6 +4773,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>82.04000000000001</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
@@ -4690,7 +4810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4896,6 +5016,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>151.49</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
@@ -4913,7 +5053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5079,6 +5219,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1384.68</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
@@ -5096,7 +5256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5262,6 +5422,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1121.2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -5279,7 +5459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5712,24 +5892,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>857.1</v>
+        <v>151.49</v>
       </c>
       <c r="E11" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -5738,22 +5918,22 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5767,7 +5947,7 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E12" t="n">
         <v>199.99</v>
@@ -5794,7 +5974,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5808,7 +5988,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E13" t="n">
         <v>199.99</v>
@@ -5835,7 +6015,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5849,7 +6029,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E14" t="n">
         <v>199.99</v>
@@ -5876,7 +6056,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5890,14 +6070,14 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5907,17 +6087,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5931,7 +6111,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>848.78</v>
+        <v>840.59</v>
       </c>
       <c r="E16" t="n">
         <v>179.99</v>
@@ -5958,7 +6138,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5972,14 +6152,14 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E17" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -5989,17 +6169,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6040,7 +6220,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6054,7 +6234,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>735.73</v>
+        <v>738.86</v>
       </c>
       <c r="E19" t="n">
         <v>169.99</v>
@@ -6075,30 +6255,30 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>514.24</v>
+        <v>735.73</v>
       </c>
       <c r="E20" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -6107,39 +6287,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>514.42</v>
+        <v>737.88</v>
       </c>
       <c r="E21" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -6148,22 +6328,22 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6177,10 +6357,10 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E22" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -6189,22 +6369,22 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6218,10 +6398,10 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E23" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -6230,22 +6410,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6259,10 +6439,10 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E24" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -6276,17 +6456,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6300,7 +6480,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E25" t="n">
         <v>52.9</v>
@@ -6321,13 +6501,13 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6341,7 +6521,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>229.93</v>
+        <v>227.84</v>
       </c>
       <c r="E26" t="n">
         <v>52.9</v>
@@ -6362,13 +6542,13 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6403,13 +6583,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6423,7 +6603,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>228.96</v>
+        <v>229.93</v>
       </c>
       <c r="E28" t="n">
         <v>52.9</v>
@@ -6444,30 +6624,30 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>308.53</v>
+        <v>229.93</v>
       </c>
       <c r="E29" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -6476,39 +6656,39 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>308.64</v>
+        <v>228.96</v>
       </c>
       <c r="E30" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -6517,39 +6697,39 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>309.11</v>
+        <v>229.62</v>
       </c>
       <c r="E31" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -6558,22 +6738,22 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6587,7 +6767,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E32" t="n">
         <v>71.98999999999999</v>
@@ -6614,7 +6794,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6628,7 +6808,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E33" t="n">
         <v>71.98999999999999</v>
@@ -6649,13 +6829,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6669,10 +6849,10 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E34" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -6681,22 +6861,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6710,10 +6890,10 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>210.02</v>
+        <v>310.13</v>
       </c>
       <c r="E35" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -6722,22 +6902,22 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6751,10 +6931,10 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>210.02</v>
+        <v>310.05</v>
       </c>
       <c r="E36" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -6763,22 +6943,22 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6792,7 +6972,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>129.8</v>
+        <v>130.35</v>
       </c>
       <c r="E37" t="n">
         <v>29.99</v>
@@ -6813,30 +6993,30 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>5211.45</v>
+        <v>210.02</v>
       </c>
       <c r="E38" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -6845,39 +7025,39 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>5211.45</v>
+        <v>210.02</v>
       </c>
       <c r="E39" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -6886,39 +7066,39 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>5211.45</v>
+        <v>129.8</v>
       </c>
       <c r="E40" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -6927,39 +7107,39 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>5189.39</v>
+        <v>130.18</v>
       </c>
       <c r="E41" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6968,16 +7148,16 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
@@ -6988,19 +7168,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E42" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -7014,11 +7194,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -7029,19 +7209,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E43" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -7055,11 +7235,11 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -7070,19 +7250,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E44" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -7096,11 +7276,11 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -7111,19 +7291,19 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>11681.54</v>
+        <v>5189.39</v>
       </c>
       <c r="E45" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -7137,34 +7317,34 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>5204.5</v>
       </c>
       <c r="E46" t="n">
-        <v>2317.5</v>
+        <v>1199</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -7173,39 +7353,39 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>9935.59</v>
+        <v>11731.2</v>
       </c>
       <c r="E47" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7214,39 +7394,39 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>11731.2</v>
       </c>
       <c r="E48" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7255,39 +7435,39 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E49" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7296,39 +7476,39 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>9981.24</v>
+        <v>11681.54</v>
       </c>
       <c r="E50" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7337,39 +7517,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>10073.01</v>
+        <v>11715.55</v>
       </c>
       <c r="E51" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7378,22 +7558,22 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7407,7 +7587,7 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>10073.01</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E52" t="n">
         <v>2317.5</v>
@@ -7428,13 +7608,13 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7448,7 +7628,7 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>10073.01</v>
+        <v>9935.59</v>
       </c>
       <c r="E53" t="n">
         <v>2317.5</v>
@@ -7469,13 +7649,13 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7489,7 +7669,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>10030.37</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E54" t="n">
         <v>2317.5</v>
@@ -7510,30 +7690,30 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>128.53</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7542,39 +7722,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>128.57</v>
+        <v>9981.24</v>
       </c>
       <c r="E56" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7583,39 +7763,39 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>128.77</v>
+        <v>10073.01</v>
       </c>
       <c r="E57" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7624,39 +7804,39 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>129.2</v>
+        <v>10073.01</v>
       </c>
       <c r="E58" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7665,39 +7845,39 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>10073.01</v>
       </c>
       <c r="E59" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7706,39 +7886,39 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10030.37</v>
       </c>
       <c r="E60" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7747,39 +7927,39 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10059.57</v>
       </c>
       <c r="E61" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7788,22 +7968,22 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7817,10 +7997,10 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>128.53</v>
       </c>
       <c r="E62" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7829,22 +8009,22 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7858,10 +8038,10 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>81.8</v>
+        <v>128.57</v>
       </c>
       <c r="E63" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7870,39 +8050,39 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1281.42</v>
+        <v>128.77</v>
       </c>
       <c r="E64" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7911,39 +8091,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1281.87</v>
+        <v>129.2</v>
       </c>
       <c r="E65" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7952,39 +8132,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1283.85</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7993,39 +8173,39 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>1288.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E67" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8034,39 +8214,39 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1287.76</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E68" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8075,39 +8255,39 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8116,39 +8296,39 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.8</v>
       </c>
       <c r="E70" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8157,39 +8337,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8198,22 +8378,22 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>35</v>
+        <v>83</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8227,7 +8407,7 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1294.1</v>
+        <v>1281.42</v>
       </c>
       <c r="E72" t="n">
         <v>299</v>
@@ -8248,376 +8428,376 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1464.64</v>
+        <v>1281.87</v>
       </c>
       <c r="E73" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>4452.98</v>
+        <v>1283.85</v>
       </c>
       <c r="E74" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>4467.26</v>
+        <v>1288.09</v>
       </c>
       <c r="E75" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>4471.19</v>
+        <v>1287.76</v>
       </c>
       <c r="E76" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>4492.85</v>
+        <v>1299.6</v>
       </c>
       <c r="E77" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>4485.35</v>
+        <v>1299.6</v>
       </c>
       <c r="E78" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>4524.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E79" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>4524.98</v>
+        <v>1294.1</v>
       </c>
       <c r="E80" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>4524.98</v>
+        <v>1297.87</v>
       </c>
       <c r="E81" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82">
@@ -8628,19 +8808,19 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>3746.75</v>
+        <v>1464.64</v>
       </c>
       <c r="E82" t="n">
-        <v>990</v>
+        <v>387</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8649,490 +8829,490 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>707.14</v>
+        <v>1473.54</v>
       </c>
       <c r="E83" t="n">
-        <v>165</v>
+        <v>387</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>707.39</v>
+        <v>4452.98</v>
       </c>
       <c r="E84" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>708.48</v>
+        <v>4467.26</v>
       </c>
       <c r="E85" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4471.19</v>
       </c>
       <c r="E86" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>465.1</v>
+        <v>4492.85</v>
       </c>
       <c r="E87" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>469.38</v>
+        <v>4485.35</v>
       </c>
       <c r="E88" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E89" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E90" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>467.39</v>
+        <v>4524.98</v>
       </c>
       <c r="E91" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1288.1</v>
+        <v>3746.75</v>
       </c>
       <c r="E92" t="n">
-        <v>299.99</v>
+        <v>990</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1292.36</v>
+        <v>3769.52</v>
       </c>
       <c r="E93" t="n">
-        <v>299.99</v>
+        <v>990</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1112.47</v>
+        <v>707.14</v>
       </c>
       <c r="E94" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9141,39 +9321,39 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1122.7</v>
+        <v>707.39</v>
       </c>
       <c r="E95" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9182,39 +9362,39 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1122.7</v>
+        <v>708.48</v>
       </c>
       <c r="E96" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9223,39 +9403,39 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1122.7</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E97" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9264,39 +9444,39 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1117.95</v>
+        <v>465.1</v>
       </c>
       <c r="E98" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9305,162 +9485,162 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1799</v>
+        <v>469.38</v>
       </c>
       <c r="E99" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1799</v>
+        <v>469.38</v>
       </c>
       <c r="E100" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1399</v>
+        <v>469.38</v>
       </c>
       <c r="E101" t="n">
-        <v>1399</v>
+        <v>107.99</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1386.53</v>
+        <v>467.39</v>
       </c>
       <c r="E102" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9469,39 +9649,39 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1386.53</v>
+        <v>468.75</v>
       </c>
       <c r="E103" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9510,39 +9690,39 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1386.53</v>
+        <v>1288.1</v>
       </c>
       <c r="E104" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9551,39 +9731,39 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1380.66</v>
+        <v>1292.36</v>
       </c>
       <c r="E105" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9592,285 +9772,285 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1074.05</v>
+        <v>1112.47</v>
       </c>
       <c r="E106" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1073.61</v>
+        <v>1122.7</v>
       </c>
       <c r="E107" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1073.29</v>
+        <v>1122.7</v>
       </c>
       <c r="E108" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1076.61</v>
+        <v>1122.7</v>
       </c>
       <c r="E109" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1075.73</v>
+        <v>1117.95</v>
       </c>
       <c r="E110" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1086.21</v>
+        <v>1121.2</v>
       </c>
       <c r="E111" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>702.37</v>
+        <v>1799</v>
       </c>
       <c r="E112" t="n">
-        <v>702.37</v>
+        <v>1799</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9879,138 +10059,794 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1086.21</v>
+        <v>1799</v>
       </c>
       <c r="E113" t="n">
-        <v>230.34</v>
+        <v>1799</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1078.59</v>
+        <v>1399</v>
       </c>
       <c r="E114" t="n">
-        <v>230.34</v>
+        <v>1399</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E115" t="n">
+        <v>319</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E116" t="n">
+        <v>319</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1386.53</v>
+      </c>
+      <c r="E117" t="n">
+        <v>319</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="E118" t="n">
+        <v>319</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>1384.68</v>
+      </c>
+      <c r="E119" t="n">
+        <v>319</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E120" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E121" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E122" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E123" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E124" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E125" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="E126" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E127" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="E128" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>1079.4</v>
+      </c>
+      <c r="E129" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
         <is>
           <t>SUPERLOGIC-ERGOMAX</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>Ritchey Superlogic ErgoMax 42cm</t>
         </is>
       </c>
-      <c r="D115" s="2" t="n">
+      <c r="D130" s="2" t="n">
         <v>860.86</v>
       </c>
-      <c r="E115" t="n">
+      <c r="E130" t="n">
         <v>198.9</v>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>actionsports.de</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
-      <c r="I115" t="n">
+      <c r="I130" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>863.37</v>
+      </c>
+      <c r="E131" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
         <v>19</v>
       </c>
     </row>
@@ -10025,7 +10861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10231,6 +11067,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>10059.57</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>imfixies.it</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
@@ -10248,7 +11104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10354,6 +11210,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>11715.55</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
@@ -10371,7 +11247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10477,6 +11353,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>5204.5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
@@ -10494,7 +11390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10700,6 +11596,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>3769.52</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fullsusbikes.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
@@ -10717,7 +11633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10763,6 +11679,26 @@
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>1473.54</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cyclingupgrades.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
@@ -10780,7 +11716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10986,6 +11922,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>468.75</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
@@ -11003,7 +11959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11214,6 +12170,26 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>130.18</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bike24.de</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$11</f>
+              <f>'FM2797'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$11</f>
+              <f>'FM2797'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -330,12 +330,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$3</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$3</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -451,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$11</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$11</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -572,12 +572,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$11</f>
+              <f>'GX-T-KIT'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$11</f>
+              <f>'GX-T-KIT'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,12 +693,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$11</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$11</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -814,12 +814,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$11</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$11</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -935,12 +935,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$9</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$9</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1056,12 +1056,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$9</f>
+              <f>'Lake MX242'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$9</f>
+              <f>'Lake MX242'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1177,12 +1177,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2:$A$6</f>
+              <f>'FARGO-TI'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2:$B$6</f>
+              <f>'FARGO-TI'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1298,12 +1298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2:$A$6</f>
+              <f>'FARGO-STEEL'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2:$B$6</f>
+              <f>'FARGO-STEEL'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,12 +1419,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$11</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$11</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1540,12 +1540,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'IBS-V1X'!$A$2:$A$3</f>
+              <f>'IBS-V1X'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'IBS-V1X'!$B$2:$B$3</f>
+              <f>'IBS-V1X'!$B$2:$B$4</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1661,12 +1661,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$11</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$11</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1782,12 +1782,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$11</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$11</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1903,12 +1903,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$11</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$11</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$11</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$11</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2888,11 +2888,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10059.57</v>
+        <v>10814.42</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
     </row>
@@ -2926,18 +2926,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11715.55</v>
+        <v>11679.92</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11681.54</v>
+        <v>11679.92</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2964,18 +2964,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5204.5</v>
+        <v>5188.67</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5189.39</v>
+        <v>5188.67</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3002,11 +3002,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3769.52</v>
+        <v>3750.02</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>3746.75</v>
@@ -3040,11 +3040,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1473.54</v>
+        <v>1465.92</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1464.64</v>
@@ -3078,11 +3078,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>468.75</v>
+        <v>467.33</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>465.1</v>
@@ -3116,18 +3116,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>130.18</v>
+        <v>129.78</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>129.8</v>
+        <v>129.78</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3154,11 +3154,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>229.62</v>
+        <v>228.92</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>227.84</v>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1079.4</v>
+        <v>1077.16</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>702.37</v>
@@ -3230,18 +3230,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>863.37</v>
+        <v>860.74</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>860.86</v>
+        <v>860.74</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3268,18 +3268,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>737.88</v>
+        <v>735.63</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>735.73</v>
+        <v>735.63</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1297.87</v>
+        <v>1293.92</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1281.42</v>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>81.40000000000001</v>
@@ -3382,11 +3382,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>151.49</v>
+        <v>151.03</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>150.31</v>
@@ -3420,11 +3420,11 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1384.68</v>
+        <v>1399</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1380.66</v>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1121.2</v>
+        <v>1117.79</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1112.47</v>
@@ -3512,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3738,6 +3738,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>228.92</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
@@ -3755,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3981,6 +4001,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1077.16</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -3998,7 +4038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4064,6 +4104,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>860.74</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
@@ -4081,7 +4141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4307,6 +4367,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>735.63</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
@@ -4324,7 +4404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4550,6 +4630,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1293.92</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -4567,7 +4667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4793,6 +4893,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
@@ -4810,7 +4930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5036,6 +5156,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>151.03</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
@@ -5053,7 +5193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5241,6 +5381,26 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5442,6 +5602,26 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1117.79</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -5459,7 +5639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I131"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5933,24 +6113,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>857.1</v>
+        <v>151.03</v>
       </c>
       <c r="E12" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -5959,22 +6139,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5988,7 +6168,7 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E13" t="n">
         <v>199.99</v>
@@ -6015,7 +6195,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6029,7 +6209,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E14" t="n">
         <v>199.99</v>
@@ -6056,7 +6236,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6070,7 +6250,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E15" t="n">
         <v>199.99</v>
@@ -6097,7 +6277,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6111,14 +6291,14 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6128,17 +6308,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6152,7 +6332,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>848.78</v>
+        <v>840.59</v>
       </c>
       <c r="E17" t="n">
         <v>179.99</v>
@@ -6179,7 +6359,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6193,14 +6373,14 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E18" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6210,17 +6390,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6261,7 +6441,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6275,7 +6455,7 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>735.73</v>
+        <v>738.86</v>
       </c>
       <c r="E20" t="n">
         <v>169.99</v>
@@ -6296,13 +6476,13 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6316,7 +6496,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>737.88</v>
+        <v>735.73</v>
       </c>
       <c r="E21" t="n">
         <v>169.99</v>
@@ -6343,24 +6523,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>514.24</v>
+        <v>737.88</v>
       </c>
       <c r="E22" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -6369,39 +6549,39 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>514.42</v>
+        <v>735.63</v>
       </c>
       <c r="E23" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -6410,22 +6590,22 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6439,10 +6619,10 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E24" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -6451,22 +6631,22 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6480,10 +6660,10 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E25" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -6492,22 +6672,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6521,10 +6701,10 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E26" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -6538,17 +6718,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6562,7 +6742,7 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E27" t="n">
         <v>52.9</v>
@@ -6583,13 +6763,13 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6603,7 +6783,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>229.93</v>
+        <v>227.84</v>
       </c>
       <c r="E28" t="n">
         <v>52.9</v>
@@ -6624,13 +6804,13 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6665,13 +6845,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6685,7 +6865,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>228.96</v>
+        <v>229.93</v>
       </c>
       <c r="E30" t="n">
         <v>52.9</v>
@@ -6706,13 +6886,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6726,7 +6906,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>229.62</v>
+        <v>229.93</v>
       </c>
       <c r="E31" t="n">
         <v>52.9</v>
@@ -6747,30 +6927,30 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>308.53</v>
+        <v>228.96</v>
       </c>
       <c r="E32" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -6779,39 +6959,39 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>308.64</v>
+        <v>229.62</v>
       </c>
       <c r="E33" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -6820,39 +7000,39 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>309.11</v>
+        <v>228.92</v>
       </c>
       <c r="E34" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -6861,22 +7041,22 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -6890,7 +7070,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E35" t="n">
         <v>71.98999999999999</v>
@@ -6917,7 +7097,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6931,7 +7111,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E36" t="n">
         <v>71.98999999999999</v>
@@ -6952,13 +7132,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6972,10 +7152,10 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E37" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -6984,22 +7164,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7013,10 +7193,10 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>210.02</v>
+        <v>310.13</v>
       </c>
       <c r="E38" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -7025,22 +7205,22 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7054,10 +7234,10 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>210.02</v>
+        <v>310.05</v>
       </c>
       <c r="E39" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -7066,22 +7246,22 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7095,7 +7275,7 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>129.8</v>
+        <v>130.35</v>
       </c>
       <c r="E40" t="n">
         <v>29.99</v>
@@ -7116,13 +7296,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7136,10 +7316,10 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>130.18</v>
+        <v>210.02</v>
       </c>
       <c r="E41" t="n">
-        <v>29.99</v>
+        <v>48.32</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -7148,39 +7328,39 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>5211.45</v>
+        <v>210.02</v>
       </c>
       <c r="E42" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -7189,39 +7369,39 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>5211.45</v>
+        <v>129.8</v>
       </c>
       <c r="E43" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -7230,39 +7410,39 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>5211.45</v>
+        <v>130.18</v>
       </c>
       <c r="E44" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -7271,39 +7451,39 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>5189.39</v>
+        <v>129.78</v>
       </c>
       <c r="E45" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -7312,22 +7492,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7341,7 +7521,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5204.5</v>
+        <v>5211.45</v>
       </c>
       <c r="E46" t="n">
         <v>1199</v>
@@ -7362,30 +7542,30 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E47" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7399,34 +7579,34 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E48" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7440,34 +7620,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>11731.2</v>
+        <v>5189.39</v>
       </c>
       <c r="E49" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7481,34 +7661,34 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>11681.54</v>
+        <v>5204.5</v>
       </c>
       <c r="E50" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7522,34 +7702,34 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>11715.55</v>
+        <v>5188.67</v>
       </c>
       <c r="E51" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7563,34 +7743,34 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E52" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7599,39 +7779,39 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>9935.59</v>
+        <v>11731.2</v>
       </c>
       <c r="E53" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7640,39 +7820,39 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>11731.2</v>
       </c>
       <c r="E54" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7681,39 +7861,39 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>11681.54</v>
       </c>
       <c r="E55" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7722,39 +7902,39 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>9981.24</v>
+        <v>11715.55</v>
       </c>
       <c r="E56" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7763,39 +7943,39 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>10073.01</v>
+        <v>11679.92</v>
       </c>
       <c r="E57" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7804,22 +7984,22 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -7833,7 +8013,7 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>10073.01</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E58" t="n">
         <v>2317.5</v>
@@ -7854,13 +8034,13 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7874,7 +8054,7 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>10073.01</v>
+        <v>9935.59</v>
       </c>
       <c r="E59" t="n">
         <v>2317.5</v>
@@ -7895,13 +8075,13 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -7915,7 +8095,7 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>10030.37</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E60" t="n">
         <v>2317.5</v>
@@ -7936,13 +8116,13 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7956,7 +8136,7 @@
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>10059.57</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E61" t="n">
         <v>2317.5</v>
@@ -7977,30 +8157,30 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>128.53</v>
+        <v>9981.24</v>
       </c>
       <c r="E62" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8009,39 +8189,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>128.57</v>
+        <v>10073.01</v>
       </c>
       <c r="E63" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8050,39 +8230,39 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>128.77</v>
+        <v>10073.01</v>
       </c>
       <c r="E64" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8091,39 +8271,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>129.2</v>
+        <v>10073.01</v>
       </c>
       <c r="E65" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8132,39 +8312,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>10030.37</v>
       </c>
       <c r="E66" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8173,39 +8353,39 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10059.57</v>
       </c>
       <c r="E67" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8214,39 +8394,39 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10814.42</v>
       </c>
       <c r="E68" t="n">
-        <v>18.9</v>
+        <v>2499</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8255,22 +8435,22 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8284,10 +8464,10 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>128.53</v>
       </c>
       <c r="E69" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8296,22 +8476,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8325,10 +8505,10 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>81.8</v>
+        <v>128.57</v>
       </c>
       <c r="E70" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8337,22 +8517,22 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8366,10 +8546,10 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>128.77</v>
       </c>
       <c r="E71" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8378,39 +8558,39 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1281.42</v>
+        <v>129.2</v>
       </c>
       <c r="E72" t="n">
-        <v>299</v>
+        <v>29.99</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8419,39 +8599,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1281.87</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E73" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8460,39 +8640,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1283.85</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E74" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8501,39 +8681,39 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1288.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8542,39 +8722,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1287.76</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E76" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8583,39 +8763,39 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.8</v>
       </c>
       <c r="E77" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8624,39 +8804,39 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8665,39 +8845,39 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8706,22 +8886,22 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8735,7 +8915,7 @@
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1294.1</v>
+        <v>1281.42</v>
       </c>
       <c r="E80" t="n">
         <v>299</v>
@@ -8756,13 +8936,13 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8776,7 +8956,7 @@
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1297.87</v>
+        <v>1281.87</v>
       </c>
       <c r="E81" t="n">
         <v>299</v>
@@ -8797,399 +8977,399 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1464.64</v>
+        <v>1283.85</v>
       </c>
       <c r="E82" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1473.54</v>
+        <v>1288.09</v>
       </c>
       <c r="E83" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4452.98</v>
+        <v>1287.76</v>
       </c>
       <c r="E84" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>4467.26</v>
+        <v>1299.6</v>
       </c>
       <c r="E85" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>4471.19</v>
+        <v>1299.6</v>
       </c>
       <c r="E86" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>4492.85</v>
+        <v>1299.6</v>
       </c>
       <c r="E87" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>4485.35</v>
+        <v>1294.1</v>
       </c>
       <c r="E88" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4524.98</v>
+        <v>1297.87</v>
       </c>
       <c r="E89" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>4524.98</v>
+        <v>1293.92</v>
       </c>
       <c r="E90" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>4524.98</v>
+        <v>1464.64</v>
       </c>
       <c r="E91" t="n">
-        <v>1190</v>
+        <v>387</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9198,39 +9378,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>3746.75</v>
+        <v>1473.54</v>
       </c>
       <c r="E92" t="n">
-        <v>990</v>
+        <v>387</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9239,39 +9419,39 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>3769.52</v>
+        <v>1465.92</v>
       </c>
       <c r="E93" t="n">
-        <v>990</v>
+        <v>387</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9280,16 +9460,16 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -9300,37 +9480,37 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>707.14</v>
+        <v>4452.98</v>
       </c>
       <c r="E94" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -9341,37 +9521,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>707.39</v>
+        <v>4467.26</v>
       </c>
       <c r="E95" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -9382,37 +9562,37 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>708.48</v>
+        <v>4471.19</v>
       </c>
       <c r="E96" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -9423,37 +9603,37 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4492.85</v>
       </c>
       <c r="E97" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
@@ -9464,37 +9644,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>465.1</v>
+        <v>4485.35</v>
       </c>
       <c r="E98" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -9505,37 +9685,37 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E99" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100">
@@ -9546,37 +9726,37 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E100" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -9587,37 +9767,37 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E101" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -9628,37 +9808,37 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>467.39</v>
+        <v>3746.75</v>
       </c>
       <c r="E102" t="n">
-        <v>107.99</v>
+        <v>990</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
@@ -9669,101 +9849,101 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>468.75</v>
+        <v>3769.52</v>
       </c>
       <c r="E103" t="n">
-        <v>107.99</v>
+        <v>990</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1288.1</v>
+        <v>3750.02</v>
       </c>
       <c r="E104" t="n">
-        <v>299.99</v>
+        <v>990</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1292.36</v>
+        <v>707.14</v>
       </c>
       <c r="E105" t="n">
-        <v>299.99</v>
+        <v>165</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9772,39 +9952,39 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1112.47</v>
+        <v>707.39</v>
       </c>
       <c r="E106" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9813,39 +9993,39 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1122.7</v>
+        <v>708.48</v>
       </c>
       <c r="E107" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9854,39 +10034,39 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1122.7</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E108" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9895,39 +10075,39 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1122.7</v>
+        <v>465.1</v>
       </c>
       <c r="E109" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9936,39 +10116,39 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1117.95</v>
+        <v>469.38</v>
       </c>
       <c r="E110" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9977,39 +10157,39 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1121.2</v>
+        <v>469.38</v>
       </c>
       <c r="E111" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10018,162 +10198,162 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1799</v>
+        <v>469.38</v>
       </c>
       <c r="E112" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1799</v>
+        <v>467.39</v>
       </c>
       <c r="E113" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1399</v>
+        <v>468.75</v>
       </c>
       <c r="E114" t="n">
-        <v>1399</v>
+        <v>107.99</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1386.53</v>
+        <v>467.33</v>
       </c>
       <c r="E115" t="n">
-        <v>319</v>
+        <v>107.99</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10182,39 +10362,39 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1386.53</v>
+        <v>1288.1</v>
       </c>
       <c r="E116" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10223,39 +10403,39 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1386.53</v>
+        <v>1292.36</v>
       </c>
       <c r="E117" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10264,39 +10444,39 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1380.66</v>
+        <v>1112.47</v>
       </c>
       <c r="E118" t="n">
-        <v>319</v>
+        <v>258.3</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10305,39 +10485,39 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1384.68</v>
+        <v>1122.7</v>
       </c>
       <c r="E119" t="n">
-        <v>319</v>
+        <v>258.3</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10346,258 +10526,258 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1074.05</v>
+        <v>1122.7</v>
       </c>
       <c r="E120" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1073.61</v>
+        <v>1122.7</v>
       </c>
       <c r="E121" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1073.29</v>
+        <v>1117.95</v>
       </c>
       <c r="E122" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1076.61</v>
+        <v>1121.2</v>
       </c>
       <c r="E123" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1075.73</v>
+        <v>1117.79</v>
       </c>
       <c r="E124" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1086.21</v>
+        <v>1799</v>
       </c>
       <c r="E125" t="n">
-        <v>230.34</v>
+        <v>1799</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -10607,24 +10787,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>702.37</v>
+        <v>1799</v>
       </c>
       <c r="E126" t="n">
-        <v>702.37</v>
+        <v>1799</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10633,162 +10813,162 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1086.21</v>
+        <v>1399</v>
       </c>
       <c r="E127" t="n">
-        <v>230.34</v>
+        <v>1399</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1078.59</v>
+        <v>1386.53</v>
       </c>
       <c r="E128" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1079.4</v>
+        <v>1386.53</v>
       </c>
       <c r="E129" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>SUPERLOGIC-ERGOMAX</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ritchey Superlogic ErgoMax 42cm</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>860.86</v>
+        <v>1386.53</v>
       </c>
       <c r="E130" t="n">
-        <v>198.9</v>
+        <v>319</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10797,56 +10977,712 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>actionsports.de</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>1380.66</v>
+      </c>
+      <c r="E131" t="n">
+        <v>319</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>1384.68</v>
+      </c>
+      <c r="E132" t="n">
+        <v>319</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>buycycle.com</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E134" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E135" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E136" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E137" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E138" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E139" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="E140" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E141" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="E142" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1079.4</v>
+      </c>
+      <c r="E143" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>1077.16</v>
+      </c>
+      <c r="E144" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
         <is>
           <t>SUPERLOGIC-ERGOMAX</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C145" t="inlineStr">
         <is>
           <t>Ritchey Superlogic ErgoMax 42cm</t>
         </is>
       </c>
-      <c r="D131" s="2" t="n">
+      <c r="D145" s="2" t="n">
+        <v>860.86</v>
+      </c>
+      <c r="E145" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
         <v>863.37</v>
       </c>
-      <c r="E131" t="n">
+      <c r="E146" t="n">
         <v>198.9</v>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F146" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="G146" t="inlineStr">
         <is>
           <t>actionsports.de</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
-      <c r="I131" t="n">
+      <c r="I146" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>860.74</v>
+      </c>
+      <c r="E147" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
         <v>19</v>
       </c>
     </row>
@@ -10861,7 +11697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11089,6 +11925,26 @@
       <c r="D11" t="inlineStr">
         <is>
           <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>10814.42</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>justpedal.nl</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11230,6 +12086,26 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>11679.92</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
@@ -11247,7 +12123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11373,6 +12249,26 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>5188.67</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
@@ -11390,7 +12286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11616,6 +12512,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>3750.02</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>fullsusbikes.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
@@ -11633,7 +12549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11699,6 +12615,26 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>1465.92</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cyclingupgrades.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
@@ -11716,7 +12652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11942,6 +12878,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>467.33</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
@@ -11959,7 +12915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12190,6 +13146,26 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>129.78</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bike24.de</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$12</f>
+              <f>'FM2797'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$12</f>
+              <f>'FM2797'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -330,12 +330,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$4</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$4</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -451,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$12</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$12</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -572,12 +572,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$12</f>
+              <f>'GX-T-KIT'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$12</f>
+              <f>'GX-T-KIT'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,12 +693,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$12</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$12</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -814,12 +814,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$12</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$12</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -935,12 +935,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$10</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$10</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1056,12 +1056,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$10</f>
+              <f>'Lake MX242'!$A$2:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$10</f>
+              <f>'Lake MX242'!$B$2:$B$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1177,12 +1177,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2:$A$7</f>
+              <f>'FARGO-TI'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2:$B$7</f>
+              <f>'FARGO-TI'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1298,12 +1298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2:$A$7</f>
+              <f>'FARGO-STEEL'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2:$B$7</f>
+              <f>'FARGO-STEEL'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,12 +1419,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$12</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$12</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1540,12 +1540,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'IBS-V1X'!$A$2:$A$4</f>
+              <f>'IBS-V1X'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'IBS-V1X'!$B$2:$B$4</f>
+              <f>'IBS-V1X'!$B$2:$B$5</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1661,12 +1661,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$12</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$12</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1782,12 +1782,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$12</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$12</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1903,12 +1903,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$12</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$12</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$12</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$12</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$13</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2888,11 +2888,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10814.42</v>
+        <v>10811.17</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2926,18 +2926,18 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11679.92</v>
+        <v>11676.41</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11679.92</v>
+        <v>11676.41</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2964,18 +2964,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5188.67</v>
+        <v>5187.11</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5188.67</v>
+        <v>5187.11</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3002,18 +3002,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3750.02</v>
+        <v>3735.37</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>3746.75</v>
+        <v>3735.37</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3040,18 +3040,18 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1465.92</v>
+        <v>1460.19</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1464.64</v>
+        <v>1460.19</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3078,11 +3078,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>467.33</v>
+        <v>467.19</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>465.1</v>
@@ -3116,11 +3116,11 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>129.78</v>
+        <v>209.04</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>129.78</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
     </row>
@@ -3154,11 +3154,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>228.92</v>
+        <v>228.86</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>227.84</v>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1077.16</v>
+        <v>1077.07</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>702.37</v>
@@ -3230,18 +3230,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>860.74</v>
+        <v>860.48</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>860.74</v>
+        <v>860.48</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3268,18 +3268,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>735.63</v>
+        <v>735.41</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>735.63</v>
+        <v>735.41</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3306,11 +3306,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1293.92</v>
+        <v>1293.53</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1281.42</v>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>81.79000000000001</v>
+        <v>81.77</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>81.40000000000001</v>
@@ -3382,11 +3382,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>151.03</v>
+        <v>150.98</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>150.31</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1117.79</v>
+        <v>1117.46</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1112.47</v>
@@ -3512,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3758,6 +3758,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>228.86</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
@@ -3775,7 +3795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4021,6 +4041,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1077.07</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -4038,7 +4078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4124,6 +4164,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>860.48</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
@@ -4141,7 +4201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4387,6 +4447,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>735.41</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
@@ -4404,7 +4484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4650,6 +4730,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1293.53</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -4667,7 +4767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4913,6 +5013,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>81.77</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
@@ -4930,7 +5050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5176,6 +5296,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>150.98</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
@@ -5193,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5399,6 +5539,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
@@ -5416,7 +5576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5622,6 +5782,26 @@
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1117.46</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -5639,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6154,24 +6334,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>857.1</v>
+        <v>150.98</v>
       </c>
       <c r="E13" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -6180,22 +6360,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6209,7 +6389,7 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E14" t="n">
         <v>199.99</v>
@@ -6236,7 +6416,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6250,7 +6430,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E15" t="n">
         <v>199.99</v>
@@ -6277,7 +6457,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6291,7 +6471,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E16" t="n">
         <v>199.99</v>
@@ -6318,7 +6498,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6332,14 +6512,14 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6349,17 +6529,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6373,7 +6553,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>848.78</v>
+        <v>840.59</v>
       </c>
       <c r="E18" t="n">
         <v>179.99</v>
@@ -6400,7 +6580,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6414,14 +6594,14 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E19" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6431,17 +6611,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6482,7 +6662,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6496,7 +6676,7 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>735.73</v>
+        <v>738.86</v>
       </c>
       <c r="E21" t="n">
         <v>169.99</v>
@@ -6517,13 +6697,13 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6537,7 +6717,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>737.88</v>
+        <v>735.73</v>
       </c>
       <c r="E22" t="n">
         <v>169.99</v>
@@ -6564,7 +6744,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6578,7 +6758,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>735.63</v>
+        <v>737.88</v>
       </c>
       <c r="E23" t="n">
         <v>169.99</v>
@@ -6605,24 +6785,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>514.24</v>
+        <v>735.63</v>
       </c>
       <c r="E24" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -6631,39 +6811,39 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>514.42</v>
+        <v>735.41</v>
       </c>
       <c r="E25" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -6672,22 +6852,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -6701,10 +6881,10 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E26" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -6713,22 +6893,22 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6742,10 +6922,10 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E27" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -6754,22 +6934,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6783,10 +6963,10 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E28" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -6800,17 +6980,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -6824,7 +7004,7 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E29" t="n">
         <v>52.9</v>
@@ -6845,13 +7025,13 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6865,7 +7045,7 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>229.93</v>
+        <v>227.84</v>
       </c>
       <c r="E30" t="n">
         <v>52.9</v>
@@ -6886,13 +7066,13 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6927,13 +7107,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6947,7 +7127,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>228.96</v>
+        <v>229.93</v>
       </c>
       <c r="E32" t="n">
         <v>52.9</v>
@@ -6968,13 +7148,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6988,7 +7168,7 @@
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>229.62</v>
+        <v>229.93</v>
       </c>
       <c r="E33" t="n">
         <v>52.9</v>
@@ -7009,13 +7189,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7029,7 +7209,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>228.92</v>
+        <v>228.96</v>
       </c>
       <c r="E34" t="n">
         <v>52.9</v>
@@ -7050,30 +7230,30 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>308.53</v>
+        <v>229.62</v>
       </c>
       <c r="E35" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -7082,39 +7262,39 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>308.64</v>
+        <v>228.92</v>
       </c>
       <c r="E36" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -7123,39 +7303,39 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>309.11</v>
+        <v>228.86</v>
       </c>
       <c r="E37" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -7164,22 +7344,22 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7193,7 +7373,7 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E38" t="n">
         <v>71.98999999999999</v>
@@ -7220,7 +7400,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7234,7 +7414,7 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E39" t="n">
         <v>71.98999999999999</v>
@@ -7255,13 +7435,13 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -7275,10 +7455,10 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E40" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -7287,22 +7467,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7316,10 +7496,10 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>210.02</v>
+        <v>310.13</v>
       </c>
       <c r="E41" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -7328,22 +7508,22 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7357,10 +7537,10 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>210.02</v>
+        <v>310.05</v>
       </c>
       <c r="E42" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -7369,22 +7549,22 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7398,7 +7578,7 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>129.8</v>
+        <v>130.35</v>
       </c>
       <c r="E43" t="n">
         <v>29.99</v>
@@ -7419,13 +7599,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7439,10 +7619,10 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>130.18</v>
+        <v>210.02</v>
       </c>
       <c r="E44" t="n">
-        <v>29.99</v>
+        <v>48.32</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -7451,22 +7631,22 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7480,10 +7660,10 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>129.78</v>
+        <v>210.02</v>
       </c>
       <c r="E45" t="n">
-        <v>29.99</v>
+        <v>48.32</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -7492,39 +7672,39 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>5211.45</v>
+        <v>129.8</v>
       </c>
       <c r="E46" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -7533,39 +7713,39 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>5211.45</v>
+        <v>130.18</v>
       </c>
       <c r="E47" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7574,39 +7754,39 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5211.45</v>
+        <v>129.78</v>
       </c>
       <c r="E48" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7615,39 +7795,39 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5189.39</v>
+        <v>209.04</v>
       </c>
       <c r="E49" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7656,22 +7836,22 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7685,7 +7865,7 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5204.5</v>
+        <v>5211.45</v>
       </c>
       <c r="E50" t="n">
         <v>1199</v>
@@ -7706,13 +7886,13 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7726,7 +7906,7 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5188.67</v>
+        <v>5211.45</v>
       </c>
       <c r="E51" t="n">
         <v>1199</v>
@@ -7747,30 +7927,30 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>11731.2</v>
+        <v>5211.45</v>
       </c>
       <c r="E52" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7784,34 +7964,34 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>11731.2</v>
+        <v>5189.39</v>
       </c>
       <c r="E53" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -7825,34 +8005,34 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>11731.2</v>
+        <v>5204.5</v>
       </c>
       <c r="E54" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7866,34 +8046,34 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>11681.54</v>
+        <v>5188.67</v>
       </c>
       <c r="E55" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7907,34 +8087,34 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>11715.55</v>
+        <v>5187.11</v>
       </c>
       <c r="E56" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7948,17 +8128,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7972,7 +8152,7 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11679.92</v>
+        <v>11731.2</v>
       </c>
       <c r="E57" t="n">
         <v>2699</v>
@@ -7999,24 +8179,24 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E58" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8025,39 +8205,39 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>9935.59</v>
+        <v>11731.2</v>
       </c>
       <c r="E59" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8066,39 +8246,39 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>11681.54</v>
       </c>
       <c r="E60" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8107,39 +8287,39 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>11715.55</v>
       </c>
       <c r="E61" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8148,39 +8328,39 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>9981.24</v>
+        <v>11679.92</v>
       </c>
       <c r="E62" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -8189,39 +8369,39 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>10073.01</v>
+        <v>11676.41</v>
       </c>
       <c r="E63" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -8230,22 +8410,22 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -8259,7 +8439,7 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>10073.01</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E64" t="n">
         <v>2317.5</v>
@@ -8280,13 +8460,13 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -8300,7 +8480,7 @@
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>10073.01</v>
+        <v>9935.59</v>
       </c>
       <c r="E65" t="n">
         <v>2317.5</v>
@@ -8321,13 +8501,13 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -8341,7 +8521,7 @@
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>10030.37</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E66" t="n">
         <v>2317.5</v>
@@ -8362,13 +8542,13 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8382,7 +8562,7 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>10059.57</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E67" t="n">
         <v>2317.5</v>
@@ -8403,13 +8583,13 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8423,10 +8603,10 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>10814.42</v>
+        <v>9981.24</v>
       </c>
       <c r="E68" t="n">
-        <v>2499</v>
+        <v>2317.5</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8435,39 +8615,39 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>justpedal.nl</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>128.53</v>
+        <v>10073.01</v>
       </c>
       <c r="E69" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8476,39 +8656,39 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>128.57</v>
+        <v>10073.01</v>
       </c>
       <c r="E70" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8517,39 +8697,39 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>128.77</v>
+        <v>10073.01</v>
       </c>
       <c r="E71" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8558,39 +8738,39 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>129.2</v>
+        <v>10030.37</v>
       </c>
       <c r="E72" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8599,39 +8779,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>10059.57</v>
       </c>
       <c r="E73" t="n">
-        <v>18.9</v>
+        <v>2317.5</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8640,39 +8820,39 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10814.42</v>
       </c>
       <c r="E74" t="n">
-        <v>18.9</v>
+        <v>2499</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8681,39 +8861,39 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10811.17</v>
       </c>
       <c r="E75" t="n">
-        <v>18.9</v>
+        <v>2499</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8722,22 +8902,22 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8751,10 +8931,10 @@
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>128.53</v>
       </c>
       <c r="E76" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8763,22 +8943,22 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8792,10 +8972,10 @@
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>81.8</v>
+        <v>128.57</v>
       </c>
       <c r="E77" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8804,22 +8984,22 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8833,10 +9013,10 @@
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>128.77</v>
       </c>
       <c r="E78" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8845,22 +9025,22 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8874,10 +9054,10 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>81.79000000000001</v>
+        <v>129.2</v>
       </c>
       <c r="E79" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8886,39 +9066,39 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1281.42</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E80" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8927,39 +9107,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1281.87</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8968,39 +9148,39 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1283.85</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9009,39 +9189,39 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1288.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E83" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9050,39 +9230,39 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1287.76</v>
+        <v>81.8</v>
       </c>
       <c r="E84" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9091,39 +9271,39 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E85" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9132,39 +9312,39 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="E86" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9173,39 +9353,39 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.77</v>
       </c>
       <c r="E87" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9214,22 +9394,22 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9243,7 +9423,7 @@
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1294.1</v>
+        <v>1281.42</v>
       </c>
       <c r="E88" t="n">
         <v>299</v>
@@ -9264,13 +9444,13 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9284,7 +9464,7 @@
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1297.87</v>
+        <v>1281.87</v>
       </c>
       <c r="E89" t="n">
         <v>299</v>
@@ -9305,13 +9485,13 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9325,7 +9505,7 @@
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1293.92</v>
+        <v>1283.85</v>
       </c>
       <c r="E90" t="n">
         <v>299</v>
@@ -9346,399 +9526,399 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1464.64</v>
+        <v>1288.09</v>
       </c>
       <c r="E91" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1473.54</v>
+        <v>1287.76</v>
       </c>
       <c r="E92" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1465.92</v>
+        <v>1299.6</v>
       </c>
       <c r="E93" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>4452.98</v>
+        <v>1299.6</v>
       </c>
       <c r="E94" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>4467.26</v>
+        <v>1299.6</v>
       </c>
       <c r="E95" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4471.19</v>
+        <v>1294.1</v>
       </c>
       <c r="E96" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>4492.85</v>
+        <v>1297.87</v>
       </c>
       <c r="E97" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>4485.35</v>
+        <v>1293.92</v>
       </c>
       <c r="E98" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>4524.98</v>
+        <v>1293.53</v>
       </c>
       <c r="E99" t="n">
-        <v>1190</v>
+        <v>299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>4524.98</v>
+        <v>1464.64</v>
       </c>
       <c r="E100" t="n">
-        <v>1190</v>
+        <v>387</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9747,39 +9927,39 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>4524.98</v>
+        <v>1473.54</v>
       </c>
       <c r="E101" t="n">
-        <v>1190</v>
+        <v>387</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9788,39 +9968,39 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>laufcycles.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>3746.75</v>
+        <v>1465.92</v>
       </c>
       <c r="E102" t="n">
-        <v>990</v>
+        <v>387</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9829,39 +10009,39 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>IBS-V1X</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>Infinity Bike Seat V1X</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>3769.52</v>
+        <v>1460.19</v>
       </c>
       <c r="E103" t="n">
-        <v>990</v>
+        <v>387</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9870,22 +10050,22 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>cyclingupgrades.com</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9899,10 +10079,10 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>3750.02</v>
+        <v>4452.98</v>
       </c>
       <c r="E104" t="n">
-        <v>990</v>
+        <v>1190</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9911,490 +10091,490 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>fullsusbikes.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>707.14</v>
+        <v>4467.26</v>
       </c>
       <c r="E105" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>707.39</v>
+        <v>4471.19</v>
       </c>
       <c r="E106" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>708.48</v>
+        <v>4492.85</v>
       </c>
       <c r="E107" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>710.8200000000001</v>
+        <v>4485.35</v>
       </c>
       <c r="E108" t="n">
-        <v>165</v>
+        <v>1190</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>sport-bittl.com</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>465.1</v>
+        <v>4524.98</v>
       </c>
       <c r="E109" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E110" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>469.38</v>
+        <v>4524.98</v>
       </c>
       <c r="E111" t="n">
-        <v>107.99</v>
+        <v>1190</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>laufcycles.com</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.laufcycles.com/product/lauf-carbonara</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>469.38</v>
+        <v>3746.75</v>
       </c>
       <c r="E112" t="n">
-        <v>107.99</v>
+        <v>990</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>467.39</v>
+        <v>3769.52</v>
       </c>
       <c r="E113" t="n">
-        <v>107.99</v>
+        <v>990</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>468.75</v>
+        <v>3750.02</v>
       </c>
       <c r="E114" t="n">
-        <v>107.99</v>
+        <v>990</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>LAUF-CARBONARA</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Lake MX190-X Wide</t>
+          <t>Lauf Carbonara fork</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>467.33</v>
+        <v>3735.37</v>
       </c>
       <c r="E115" t="n">
-        <v>107.99</v>
+        <v>990</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>alltricks.nl</t>
+          <t>fullsusbikes.com</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.alltricks.nl/C-1586355-lake</t>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1288.1</v>
+        <v>707.14</v>
       </c>
       <c r="E116" t="n">
-        <v>299.99</v>
+        <v>165</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10403,39 +10583,39 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1292.36</v>
+        <v>707.39</v>
       </c>
       <c r="E117" t="n">
-        <v>299.99</v>
+        <v>165</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10444,39 +10624,39 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1112.47</v>
+        <v>708.48</v>
       </c>
       <c r="E118" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10485,39 +10665,39 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1122.7</v>
+        <v>710.8200000000001</v>
       </c>
       <c r="E119" t="n">
-        <v>258.3</v>
+        <v>165</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10526,39 +10706,39 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>sport-bittl.com</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.sport-bittl.com/de/lake-mx190-wide-mountainbikeschuhe-schwarz::255373.html</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1122.7</v>
+        <v>465.1</v>
       </c>
       <c r="E120" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10567,39 +10747,39 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I120" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1122.7</v>
+        <v>469.38</v>
       </c>
       <c r="E121" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10608,39 +10788,39 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1117.95</v>
+        <v>469.38</v>
       </c>
       <c r="E122" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10649,39 +10829,39 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1121.2</v>
+        <v>469.38</v>
       </c>
       <c r="E123" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10690,39 +10870,39 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Lake MX242</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1117.79</v>
+        <v>467.39</v>
       </c>
       <c r="E124" t="n">
-        <v>258.3</v>
+        <v>107.99</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10731,162 +10911,162 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>bike-discount.de</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1799</v>
+        <v>468.75</v>
       </c>
       <c r="E125" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>1799</v>
+        <v>467.33</v>
       </c>
       <c r="E126" t="n">
-        <v>1799</v>
+        <v>107.99</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX190-X Wide</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>1399</v>
+        <v>467.19</v>
       </c>
       <c r="E127" t="n">
-        <v>1399</v>
+        <v>107.99</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>alltricks.nl</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1386.53</v>
+        <v>1288.1</v>
       </c>
       <c r="E128" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10895,39 +11075,39 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/de/lake-mx242-x-wide-mtb-schuhe-20154493</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>1386.53</v>
+        <v>1292.36</v>
       </c>
       <c r="E129" t="n">
-        <v>319</v>
+        <v>299.99</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -10936,39 +11116,39 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1386.53</v>
+        <v>1112.47</v>
       </c>
       <c r="E130" t="n">
-        <v>319</v>
+        <v>258.3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -10977,39 +11157,39 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1380.66</v>
+        <v>1122.7</v>
       </c>
       <c r="E131" t="n">
-        <v>319</v>
+        <v>258.3</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11018,39 +11198,39 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1384.68</v>
+        <v>1122.7</v>
       </c>
       <c r="E132" t="n">
-        <v>319</v>
+        <v>258.3</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11059,258 +11239,258 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>buycycle.com</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ROCK SHOX SID SL Select+</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>1399</v>
+        <v>1122.7</v>
       </c>
       <c r="E133" t="n">
-        <v>1399</v>
+        <v>258.3</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>PLN</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>centrumrowerowe.pl</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>1074.05</v>
+        <v>1117.95</v>
       </c>
       <c r="E134" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1073.61</v>
+        <v>1121.2</v>
       </c>
       <c r="E135" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>1073.29</v>
+        <v>1117.79</v>
       </c>
       <c r="E136" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>Lake MX242</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>1076.61</v>
+        <v>1117.46</v>
       </c>
       <c r="E137" t="n">
-        <v>230.34</v>
+        <v>258.3</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>bike-discount.de</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>1075.73</v>
+        <v>1799</v>
       </c>
       <c r="E138" t="n">
-        <v>230.34</v>
+        <v>1799</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -11320,65 +11500,65 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1086.21</v>
+        <v>1799</v>
       </c>
       <c r="E139" t="n">
-        <v>230.34</v>
+        <v>1799</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-pd49824/</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>702.37</v>
+        <v>1399</v>
       </c>
       <c r="E140" t="n">
-        <v>702.37</v>
+        <v>1399</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11387,203 +11567,203 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>bike24.pl</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>1086.21</v>
+        <v>1386.53</v>
       </c>
       <c r="E141" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1078.59</v>
+        <v>1386.53</v>
       </c>
       <c r="E142" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1079.4</v>
+        <v>1386.53</v>
       </c>
       <c r="E143" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ritchey WCS Carbon ErgoMax</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1077.16</v>
+        <v>1380.66</v>
       </c>
       <c r="E144" t="n">
-        <v>230.34</v>
+        <v>319</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>bikeshopzizers.ch</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SUPERLOGIC-ERGOMAX</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ritchey Superlogic ErgoMax 42cm</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>860.86</v>
+        <v>1384.68</v>
       </c>
       <c r="E145" t="n">
-        <v>198.9</v>
+        <v>319</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11592,97 +11772,753 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>actionsports.de</t>
+          <t>buycycle.com</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+          <t>https://buycycle.com/it-it/product/suspension-fork-rockshox-horquilla-sid-select-rl</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SUPERLOGIC-ERGOMAX</t>
+          <t>ROCK SHOX SID</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Ritchey Superlogic ErgoMax 42cm</t>
+          <t>ROCK SHOX SID SL Select+</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>863.37</v>
+        <v>1399</v>
       </c>
       <c r="E146" t="n">
-        <v>198.9</v>
+        <v>1399</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PLN</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>actionsports.de</t>
+          <t>centrumrowerowe.pl</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>ROCK SHOX SID SL Select+</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>1074.05</v>
+      </c>
+      <c r="E148" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1073.61</v>
+      </c>
+      <c r="E149" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>1073.29</v>
+      </c>
+      <c r="E150" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1076.61</v>
+      </c>
+      <c r="E151" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>1075.73</v>
+      </c>
+      <c r="E152" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E153" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="E154" t="n">
+        <v>702.37</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>PLN</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>bike24.pl</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=Ritchey+WCS+Carbon+ErgoMax+handlebar&amp;prds=localAnnotatedOfferId:1,catalogid:15460370949950614960,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=pl&amp;udm=28&amp;pvorigin=2</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>1086.21</v>
+      </c>
+      <c r="E155" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1078.59</v>
+      </c>
+      <c r="E156" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1079.4</v>
+      </c>
+      <c r="E157" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1077.16</v>
+      </c>
+      <c r="E158" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Ritchey WCS Carbon ErgoMax</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>1077.07</v>
+      </c>
+      <c r="E159" t="n">
+        <v>230.34</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
         <is>
           <t>SUPERLOGIC-ERGOMAX</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C160" t="inlineStr">
         <is>
           <t>Ritchey Superlogic ErgoMax 42cm</t>
         </is>
       </c>
-      <c r="D147" s="2" t="n">
+      <c r="D160" s="2" t="n">
+        <v>860.86</v>
+      </c>
+      <c r="E160" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>863.37</v>
+      </c>
+      <c r="E161" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
         <v>860.74</v>
       </c>
-      <c r="E147" t="n">
+      <c r="E162" t="n">
         <v>198.9</v>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F162" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G162" t="inlineStr">
         <is>
           <t>actionsports.de</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H162" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
       </c>
-      <c r="I147" t="n">
+      <c r="I162" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SUPERLOGIC-ERGOMAX</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Ritchey Superlogic ErgoMax 42cm</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>860.48</v>
+      </c>
+      <c r="E163" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
         <v>19</v>
       </c>
     </row>
@@ -11697,7 +12533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11943,6 +12779,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>10811.17</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>justpedal.nl</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
@@ -11960,7 +12816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12106,6 +12962,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>11676.41</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
@@ -12123,7 +12999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12269,6 +13145,26 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>5187.11</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bike-packing.de</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
@@ -12286,7 +13182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12532,6 +13428,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>3735.37</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fullsusbikes.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.fullsusbikes.com/product/lauf-carbonara-fat-bike-suspension-fork</t>
         </is>
@@ -12549,7 +13465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12635,6 +13551,26 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
+        <is>
+          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1460.19</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cyclingupgrades.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
         </is>
@@ -12652,7 +13588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12898,6 +13834,26 @@
         </is>
       </c>
       <c r="D12" t="inlineStr">
+        <is>
+          <t>https://www.alltricks.nl/C-1586355-lake</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>467.19</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>alltricks.nl</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://www.alltricks.nl/C-1586355-lake</t>
         </is>
@@ -12915,7 +13871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -13166,6 +14122,26 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>209.04</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>use-elitebikes.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/prices.xlsx
+++ b/output/prices.xlsx
@@ -209,12 +209,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FM2797'!$A$2:$A$13</f>
+              <f>'FM2797'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FM2797'!$B$2:$B$13</f>
+              <f>'FM2797'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -330,12 +330,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$5</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$5</f>
+              <f>'SUPERLOGIC-ERGOMAX'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -451,12 +451,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$13</f>
+              <f>'Canyon S14 VCLS 2.0'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$13</f>
+              <f>'Canyon S14 VCLS 2.0'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -572,12 +572,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-KIT'!$A$2:$A$13</f>
+              <f>'GX-T-KIT'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-KIT'!$B$2:$B$13</f>
+              <f>'GX-T-KIT'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,12 +693,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'GX-T-CHAIN'!$A$2:$A$13</f>
+              <f>'GX-T-CHAIN'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GX-T-CHAIN'!$B$2:$B$13</f>
+              <f>'GX-T-CHAIN'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -814,12 +814,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$13</f>
+              <f>'Cane Creek 40 IS41-IS52'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$13</f>
+              <f>'Cane Creek 40 IS41-IS52'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -935,12 +935,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'ROCK SHOX SID'!$A$2:$A$11</f>
+              <f>'ROCK SHOX SID'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'ROCK SHOX SID'!$B$2:$B$11</f>
+              <f>'ROCK SHOX SID'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1056,12 +1056,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX242'!$A$2:$A$11</f>
+              <f>'Lake MX242'!$A$2:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX242'!$B$2:$B$11</f>
+              <f>'Lake MX242'!$B$2:$B$12</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1177,12 +1177,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-TI'!$A$2:$A$8</f>
+              <f>'FARGO-TI'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-TI'!$B$2:$B$8</f>
+              <f>'FARGO-TI'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1298,12 +1298,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'FARGO-STEEL'!$A$2:$A$8</f>
+              <f>'FARGO-STEEL'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'FARGO-STEEL'!$B$2:$B$8</f>
+              <f>'FARGO-STEEL'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1419,12 +1419,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'LAUF-CARBONARA'!$A$2:$A$13</f>
+              <f>'LAUF-CARBONARA'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'LAUF-CARBONARA'!$B$2:$B$13</f>
+              <f>'LAUF-CARBONARA'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1540,12 +1540,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'IBS-V1X'!$A$2:$A$5</f>
+              <f>'IBS-V1X'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'IBS-V1X'!$B$2:$B$5</f>
+              <f>'IBS-V1X'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1661,12 +1661,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Lake MX190-X Wide'!$A$2:$A$13</f>
+              <f>'Lake MX190-X Wide'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Lake MX190-X Wide'!$B$2:$B$13</f>
+              <f>'Lake MX190-X Wide'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1782,12 +1782,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT Swiss Fatbike'!$A$2:$A$13</f>
+              <f>'DT Swiss Fatbike'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT Swiss Fatbike'!$B$2:$B$13</f>
+              <f>'DT Swiss Fatbike'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1903,12 +1903,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$A$2:$A$13</f>
+              <f>'DT SWISS 350 12x148'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DT SWISS 350 12x148'!$B$2:$B$13</f>
+              <f>'DT SWISS 350 12x148'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$13</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$A$2:$A$14</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$13</f>
+              <f>'Ritchey WCS Carbon ErgoMax'!$B$2:$B$14</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2888,11 +2888,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>10811.17</v>
+        <v>10850.66</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>9932.110000000001</v>
@@ -2926,11 +2926,11 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>11676.41</v>
+        <v>11719.06</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11676.41</v>
@@ -2964,11 +2964,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5187.11</v>
+        <v>5206.06</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>5187.11</v>
@@ -3002,11 +3002,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>3735.37</v>
+        <v>3757.15</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>3735.37</v>
@@ -3040,11 +3040,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1460.19</v>
+        <v>1468.7</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>1460.19</v>
@@ -3078,11 +3078,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>467.19</v>
+        <v>468.89</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>465.1</v>
@@ -3116,28 +3116,28 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>209.04</v>
+        <v>116.8</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>129.78</v>
+        <v>116.8</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>raaad.de</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,catalogid:17767464795082583901,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
     </row>
@@ -3154,11 +3154,11 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>228.86</v>
+        <v>229.69</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>227.84</v>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1077.07</v>
+        <v>1083.98</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>702.37</v>
@@ -3230,11 +3230,11 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>860.48</v>
+        <v>863.62</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>860.48</v>
@@ -3268,11 +3268,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>735.41</v>
+        <v>738.1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>735.41</v>
@@ -3306,11 +3306,11 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1293.53</v>
+        <v>1298.26</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1281.42</v>
@@ -3344,11 +3344,11 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>81.77</v>
+        <v>82.06</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>81.40000000000001</v>
@@ -3382,11 +3382,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>150.98</v>
+        <v>151.54</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>150.31</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -3458,11 +3458,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1117.46</v>
+        <v>1121.54</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1112.47</v>
@@ -3512,7 +3512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3778,6 +3778,26 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>229.69</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>whizz-wheels.de</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
@@ -3795,7 +3815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4061,6 +4081,26 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1083.98</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bikeshopzizers.ch</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://bikeshopzizers.ch/ritchey-road-lenker-wcs-ergomax-42cm-c-c-oben-ud-carbon-31-8mm/</t>
         </is>
@@ -4078,7 +4118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4184,6 +4224,26 @@
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>863.62</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>actionsports.de</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://www.actionsports.de/ritchey-superlogic-carbon-flat-2x-31-8/710mm-lenker-25835</t>
         </is>
@@ -4201,7 +4261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4467,6 +4527,26 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>738.1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>canyon.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
@@ -4484,7 +4564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4750,6 +4830,26 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1298.26</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>bike-components.de</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
@@ -4767,7 +4867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5033,6 +5133,26 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>82.06</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cingolanibikeshop.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
@@ -5050,7 +5170,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5316,6 +5436,26 @@
         </is>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>151.54</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>last-bikes.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
@@ -5333,7 +5473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5559,6 +5699,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>centrumrowerowe.pl</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.centrumrowerowe.pl/amortyzator-rowerowy-rock-shox-sid-sl-select-charger-rl-pd25547/</t>
         </is>
@@ -5576,7 +5736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5802,6 +5962,26 @@
         </is>
       </c>
       <c r="D11" t="inlineStr">
+        <is>
+          <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>1121.54</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bike-discount.de</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://www.bike-discount.de/en/lake-mx242-x-wide-mtb-shoes-20154493</t>
         </is>
@@ -5819,7 +5999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6375,24 +6555,24 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Canyon S14 VCLS 2.0</t>
+          <t>Cane Creek 40 IS41/IS52</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>857.1</v>
+        <v>151.54</v>
       </c>
       <c r="E14" t="n">
-        <v>199.99</v>
+        <v>34.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -6401,22 +6581,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>canyon.com</t>
+          <t>last-bikes.com</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
+          <t>https://www.last-bikes.com/Artikeldetail?Language=en&amp;ClientID=a30f076f-d7c3-4db1-8649-8599fa71aee6%2Ca30f076f-d7c3-4db1-8649-8599fa71aee6&amp;StuffID=5345f6ed-c61f-4449-95de-81a85bc44587</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6430,7 +6610,7 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>857.4</v>
+        <v>857.1</v>
       </c>
       <c r="E15" t="n">
         <v>199.99</v>
@@ -6457,7 +6637,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6471,7 +6651,7 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>858.72</v>
+        <v>857.4</v>
       </c>
       <c r="E16" t="n">
         <v>199.99</v>
@@ -6498,7 +6678,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6512,7 +6692,7 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>861.5599999999999</v>
+        <v>858.72</v>
       </c>
       <c r="E17" t="n">
         <v>199.99</v>
@@ -6539,7 +6719,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6553,14 +6733,14 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>840.59</v>
+        <v>861.5599999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>179.99</v>
+        <v>199.99</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6570,17 +6750,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/de-de/fahrradzubehoer/fahrradteile/sattelstuetze-sattelklemme/canyon-s14-vcls-2.0-27.2mm-cf-sattelstuetze/148286.html</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6594,7 +6774,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>848.78</v>
+        <v>840.59</v>
       </c>
       <c r="E19" t="n">
         <v>179.99</v>
@@ -6621,7 +6801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6635,14 +6815,14 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>738.86</v>
+        <v>848.78</v>
       </c>
       <c r="E20" t="n">
-        <v>169.99</v>
+        <v>179.99</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6652,17 +6832,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
+          <t>https://www.canyon.com/it-ch/accessori-biciclette/componenti/reggisella-collarini/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6703,7 +6883,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6717,7 +6897,7 @@
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>735.73</v>
+        <v>738.86</v>
       </c>
       <c r="E22" t="n">
         <v>169.99</v>
@@ -6738,13 +6918,13 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -6758,7 +6938,7 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>737.88</v>
+        <v>735.73</v>
       </c>
       <c r="E23" t="n">
         <v>169.99</v>
@@ -6785,7 +6965,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6799,7 +6979,7 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>735.63</v>
+        <v>737.88</v>
       </c>
       <c r="E24" t="n">
         <v>169.99</v>
@@ -6826,7 +7006,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6840,7 +7020,7 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>735.41</v>
+        <v>735.63</v>
       </c>
       <c r="E25" t="n">
         <v>169.99</v>
@@ -6867,24 +7047,24 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>514.24</v>
+        <v>735.41</v>
       </c>
       <c r="E26" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -6893,39 +7073,39 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DT SWISS 350 12x148</t>
+          <t>Canyon S14 VCLS 2.0</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>514.42</v>
+        <v>738.1</v>
       </c>
       <c r="E27" t="n">
-        <v>119.99</v>
+        <v>169.99</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -6934,22 +7114,22 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>canyon.com</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
+          <t>https://www.canyon.com/en-is/gear/bike-parts/posts-and-clamps/canyon-s14-vcls-2.0-27.2mm-cf-seatpost/148286.html</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -6963,10 +7143,10 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>398.89</v>
+        <v>514.24</v>
       </c>
       <c r="E28" t="n">
-        <v>92.90000000000001</v>
+        <v>119.99</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -6975,22 +7155,22 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7004,10 +7184,10 @@
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>227.89</v>
+        <v>514.42</v>
       </c>
       <c r="E29" t="n">
-        <v>52.9</v>
+        <v>119.99</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -7016,22 +7196,22 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>whizz-wheels.de</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://www.bike-components.de/de/DT-Swiss/350-Classic-MTB-Boost-Disc-Center-Lock-HR-Nabe-p84203/</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7045,10 +7225,10 @@
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>227.84</v>
+        <v>398.89</v>
       </c>
       <c r="E30" t="n">
-        <v>52.9</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -7062,17 +7242,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
+          <t>https://whizz-wheels.de/shop/DT-Swiss-350-Hybrid-Disc-IS-100-mm-32-Loch-MY2023-Vorderradnabe/H350ADQXR32SO0732S</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7086,7 +7266,7 @@
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>229.93</v>
+        <v>227.89</v>
       </c>
       <c r="E31" t="n">
         <v>52.9</v>
@@ -7107,13 +7287,13 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>94</v>
+        <v>23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -7127,7 +7307,7 @@
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>229.93</v>
+        <v>227.84</v>
       </c>
       <c r="E32" t="n">
         <v>52.9</v>
@@ -7148,13 +7328,13 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7189,13 +7369,13 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -7209,7 +7389,7 @@
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>228.96</v>
+        <v>229.93</v>
       </c>
       <c r="E34" t="n">
         <v>52.9</v>
@@ -7230,13 +7410,13 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>113</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7250,7 +7430,7 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>229.62</v>
+        <v>229.93</v>
       </c>
       <c r="E35" t="n">
         <v>52.9</v>
@@ -7271,13 +7451,13 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7291,7 +7471,7 @@
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>228.92</v>
+        <v>228.96</v>
       </c>
       <c r="E36" t="n">
         <v>52.9</v>
@@ -7312,13 +7492,13 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7332,7 +7512,7 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>228.86</v>
+        <v>229.62</v>
       </c>
       <c r="E37" t="n">
         <v>52.9</v>
@@ -7353,30 +7533,30 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>308.53</v>
+        <v>228.92</v>
       </c>
       <c r="E38" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -7385,39 +7565,39 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>308.64</v>
+        <v>228.86</v>
       </c>
       <c r="E39" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -7426,39 +7606,39 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DT Swiss Fatbike</t>
+          <t>DT SWISS 350 12x148</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>309.11</v>
+        <v>229.69</v>
       </c>
       <c r="E40" t="n">
-        <v>71.98999999999999</v>
+        <v>52.9</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -7467,22 +7647,22 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>rczbikeshop.com</t>
+          <t>whizz-wheels.de</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
+          <t>https://whizz-wheels.de/shop/Tool-Kit-Set-For-FW-350-370-SA15/HWTXXX00N5290S</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7496,7 +7676,7 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>310.13</v>
+        <v>308.53</v>
       </c>
       <c r="E41" t="n">
         <v>71.98999999999999</v>
@@ -7523,7 +7703,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7537,7 +7717,7 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>310.05</v>
+        <v>308.64</v>
       </c>
       <c r="E42" t="n">
         <v>71.98999999999999</v>
@@ -7558,13 +7738,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7578,10 +7758,10 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>130.35</v>
+        <v>309.11</v>
       </c>
       <c r="E43" t="n">
-        <v>29.99</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -7590,22 +7770,22 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7619,10 +7799,10 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>210.02</v>
+        <v>310.13</v>
       </c>
       <c r="E44" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -7631,22 +7811,22 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7660,10 +7840,10 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>210.02</v>
+        <v>310.05</v>
       </c>
       <c r="E45" t="n">
-        <v>48.32</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -7672,22 +7852,22 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>rczbikeshop.com</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.rczbikeshop.com/default/dt-swiss-rear-hub-350-classic-fatbike-is-32h-12x197mm-exp-xd-7613052319606.html?___store=default&amp;___from_store=de</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7701,7 +7881,7 @@
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>129.8</v>
+        <v>130.35</v>
       </c>
       <c r="E46" t="n">
         <v>29.99</v>
@@ -7722,13 +7902,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7742,10 +7922,10 @@
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>130.18</v>
+        <v>210.02</v>
       </c>
       <c r="E47" t="n">
-        <v>29.99</v>
+        <v>48.32</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -7754,22 +7934,22 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -7783,10 +7963,10 @@
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>129.78</v>
+        <v>210.02</v>
       </c>
       <c r="E48" t="n">
-        <v>29.99</v>
+        <v>48.32</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -7795,22 +7975,22 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>bike24.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7824,10 +8004,10 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>209.04</v>
+        <v>129.8</v>
       </c>
       <c r="E49" t="n">
-        <v>48.32</v>
+        <v>29.99</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -7836,39 +8016,39 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>use-elitebikes.com</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>5211.45</v>
+        <v>130.18</v>
       </c>
       <c r="E50" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -7877,39 +8057,39 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>5211.45</v>
+        <v>129.78</v>
       </c>
       <c r="E51" t="n">
-        <v>1199</v>
+        <v>29.99</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -7918,39 +8098,39 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>bike24.de</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,productid:10606755683998234321,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5211.45</v>
+        <v>209.04</v>
       </c>
       <c r="E52" t="n">
-        <v>1199</v>
+        <v>48.32</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -7959,39 +8139,39 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>use-elitebikes.com</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.use-elitebikes.com/naben/15966-dt-swiss-350-nabe-vorne-15x110-28l-disc-is-neu.html</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FARGO-STEEL</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
+          <t>DT Swiss Fatbike</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>5189.39</v>
+        <v>116.8</v>
       </c>
       <c r="E53" t="n">
-        <v>1199</v>
+        <v>26.9</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -8000,22 +8180,22 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>bike-packing.de</t>
+          <t>raaad.de</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
+          <t>https://www.google.com/search?ibp=oshop&amp;q=DT+Swiss+350+Fatbike+hub+15x150&amp;prds=localAnnotatedOfferId:1,catalogid:17767464795082583901,pvo:2,pvt:hg,rds:PC_6027158597472037202%7CPROD_PC_6027158597472037202&amp;gl=de&amp;udm=28&amp;pvorigin=2</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8029,7 +8209,7 @@
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>5204.5</v>
+        <v>5211.45</v>
       </c>
       <c r="E54" t="n">
         <v>1199</v>
@@ -8050,13 +8230,13 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8070,7 +8250,7 @@
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>5188.67</v>
+        <v>5211.45</v>
       </c>
       <c r="E55" t="n">
         <v>1199</v>
@@ -8091,13 +8271,13 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8111,7 +8291,7 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>5187.11</v>
+        <v>5211.45</v>
       </c>
       <c r="E56" t="n">
         <v>1199</v>
@@ -8132,30 +8312,30 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>11731.2</v>
+        <v>5189.39</v>
       </c>
       <c r="E57" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8169,34 +8349,34 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>11731.2</v>
+        <v>5204.5</v>
       </c>
       <c r="E58" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8210,34 +8390,34 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>11731.2</v>
+        <v>5188.67</v>
       </c>
       <c r="E59" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8251,34 +8431,34 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>11681.54</v>
+        <v>5187.11</v>
       </c>
       <c r="E60" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8292,34 +8472,34 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FARGO-TI</t>
+          <t>FARGO-STEEL</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salsa Fargo Ti Frameset</t>
+          <t>Salsa Fargo Steel Frameset 27.5+/29 Gunmetal Grey</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>11715.55</v>
+        <v>5206.06</v>
       </c>
       <c r="E61" t="n">
-        <v>2699</v>
+        <v>1199</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8333,17 +8513,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
+          <t>https://www.bike-packing.de/en/salsa-fargo-steel-frameset-275-29-gunmetal-grey</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -8357,7 +8537,7 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>11679.92</v>
+        <v>11731.2</v>
       </c>
       <c r="E62" t="n">
         <v>2699</v>
@@ -8384,7 +8564,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8398,7 +8578,7 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>11676.41</v>
+        <v>11731.2</v>
       </c>
       <c r="E63" t="n">
         <v>2699</v>
@@ -8425,24 +8605,24 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>9932.110000000001</v>
+        <v>11731.2</v>
       </c>
       <c r="E64" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8451,39 +8631,39 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>9935.59</v>
+        <v>11681.54</v>
       </c>
       <c r="E65" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8492,39 +8672,39 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>9950.879999999999</v>
+        <v>11715.55</v>
       </c>
       <c r="E66" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8533,39 +8713,39 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>9983.790000000001</v>
+        <v>11679.92</v>
       </c>
       <c r="E67" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8574,39 +8754,39 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>9981.24</v>
+        <v>11676.41</v>
       </c>
       <c r="E68" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8615,39 +8795,39 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FM2797</t>
+          <t>FARGO-TI</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Salsa Cutthroat C Frameset</t>
+          <t>Salsa Fargo Ti Frameset</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>10073.01</v>
+        <v>11719.06</v>
       </c>
       <c r="E69" t="n">
-        <v>2317.5</v>
+        <v>2699</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8656,22 +8836,22 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>imfixies.it</t>
+          <t>bike-packing.de</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
+          <t>https://www.bike-packing.de/salsa-fargo-ti-frameset-titanium-rahmenkit</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -8685,7 +8865,7 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>10073.01</v>
+        <v>9932.110000000001</v>
       </c>
       <c r="E70" t="n">
         <v>2317.5</v>
@@ -8706,13 +8886,13 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8726,7 +8906,7 @@
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>10073.01</v>
+        <v>9935.59</v>
       </c>
       <c r="E71" t="n">
         <v>2317.5</v>
@@ -8747,13 +8927,13 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8767,7 +8947,7 @@
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>10030.37</v>
+        <v>9950.879999999999</v>
       </c>
       <c r="E72" t="n">
         <v>2317.5</v>
@@ -8788,13 +8968,13 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -8808,7 +8988,7 @@
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>10059.57</v>
+        <v>9983.790000000001</v>
       </c>
       <c r="E73" t="n">
         <v>2317.5</v>
@@ -8829,13 +9009,13 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8849,10 +9029,10 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>10814.42</v>
+        <v>9981.24</v>
       </c>
       <c r="E74" t="n">
-        <v>2499</v>
+        <v>2317.5</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8861,22 +9041,22 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>justpedal.nl</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8890,10 +9070,10 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>10811.17</v>
+        <v>10073.01</v>
       </c>
       <c r="E75" t="n">
-        <v>2499</v>
+        <v>2317.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8902,39 +9082,39 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>justpedal.nl</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>128.53</v>
+        <v>10073.01</v>
       </c>
       <c r="E76" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8943,39 +9123,39 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>128.57</v>
+        <v>10073.01</v>
       </c>
       <c r="E77" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8984,39 +9164,39 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>128.77</v>
+        <v>10030.37</v>
       </c>
       <c r="E78" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9025,39 +9205,39 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>129.2</v>
+        <v>10059.57</v>
       </c>
       <c r="E79" t="n">
-        <v>29.99</v>
+        <v>2317.5</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9066,39 +9246,39 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>alutech-cycles.com</t>
+          <t>imfixies.it</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
+          <t>https://imfixies.it/telai-gravel/telaio-gravel-salsa-cutthroat-c-29-carbonio.html</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>81.40000000000001</v>
+        <v>10814.42</v>
       </c>
       <c r="E80" t="n">
-        <v>18.9</v>
+        <v>2499</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9107,39 +9287,39 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10811.17</v>
       </c>
       <c r="E81" t="n">
-        <v>18.9</v>
+        <v>2499</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9148,39 +9328,39 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>74</v>
+        <v>9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GX-T-CHAIN</t>
+          <t>FM2797</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Łańcuch</t>
+          <t>Salsa Cutthroat C Frameset</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>10850.66</v>
       </c>
       <c r="E82" t="n">
-        <v>18.9</v>
+        <v>2499</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9189,22 +9369,22 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>justpedal.nl</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://www.justpedal.nl/fm2797/salsa-cutthroat-frame-black-udh.html</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9218,10 +9398,10 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>82.15000000000001</v>
+        <v>128.53</v>
       </c>
       <c r="E83" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9230,22 +9410,22 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9259,10 +9439,10 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>81.8</v>
+        <v>128.57</v>
       </c>
       <c r="E84" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9271,22 +9451,22 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9300,10 +9480,10 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>82.04000000000001</v>
+        <v>128.77</v>
       </c>
       <c r="E85" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9312,22 +9492,22 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>83</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9341,10 +9521,10 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>81.79000000000001</v>
+        <v>129.2</v>
       </c>
       <c r="E86" t="n">
-        <v>18.9</v>
+        <v>29.99</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9353,22 +9533,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>cingolanibikeshop.com</t>
+          <t>alutech-cycles.com</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
+          <t>https://alutech-cycles.com/SRAM-chain-GX-T-Type-118-12-speed-silver</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>79</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9382,7 +9562,7 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>81.77</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="E87" t="n">
         <v>18.9</v>
@@ -9403,30 +9583,30 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1281.42</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E88" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9435,39 +9615,39 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1281.87</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9476,39 +9656,39 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1283.85</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E90" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9517,39 +9697,39 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1288.09</v>
+        <v>81.8</v>
       </c>
       <c r="E91" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9558,39 +9738,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1287.76</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9599,39 +9779,39 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>31</v>
+        <v>83</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="E93" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9640,39 +9820,39 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1299.6</v>
+        <v>81.77</v>
       </c>
       <c r="E94" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9681,39 +9861,39 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GX-T-KIT</t>
+          <t>GX-T-CHAIN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
+          <t>SRAM GX Eagle Transmission Łańcuch</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1299.6</v>
+        <v>82.06</v>
       </c>
       <c r="E95" t="n">
-        <v>299</v>
+        <v>18.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9722,22 +9902,22 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>bike-components.de</t>
+          <t>cingolanibikeshop.com</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
+          <t>https://www.cingolanibikeshop.com/componenti/trasmissione/catene/sram/</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9751,7 +9931,7 @@
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1294.1</v>
+        <v>1281.42</v>
       </c>
       <c r="E96" t="n">
         <v>299</v>
@@ -9772,13 +9952,13 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9792,7 +9972,7 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1297.87</v>
+        <v>1281.87</v>
       </c>
       <c r="E97" t="n">
         <v>299</v>
@@ -9813,13 +9993,13 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9833,7 +10013,7 @@
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1293.92</v>
+        <v>1283.85</v>
       </c>
       <c r="E98" t="n">
         <v>299</v>
@@ -9854,13 +10034,13 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9874,7 +10054,7 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1293.53</v>
+        <v>1288.09</v>
       </c>
       <c r="E99" t="n">
         <v>299</v>
@@ -9895,399 +10075,399 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1464.64</v>
+        <v>1287.76</v>
       </c>
       <c r="E100" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1473.54</v>
+        <v>1299.6</v>
       </c>
       <c r="E101" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1465.92</v>
+        <v>1299.6</v>
       </c>
       <c r="E102" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>IBS-V1X</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Infinity Bike Seat V1X</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1460.19</v>
+        <v>1299.6</v>
       </c>
       <c r="E103" t="n">
-        <v>387</v>
+        <v>299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>cyclingupgrades.com</t>
+          <t>bike-components.de</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.cyclingupgrades.com/products/new-_infinity_vegan_v1x_black_7x7mm_stainless_rails_saddle06242025-1104-05</t>
+          <t>https://www.bike-components.de/en/SRAM/GX-Eagle-Transmission-Upgrade-Kit-p172400/</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LAUF-CARBONARA</t>
+          <t>GX-T-KIT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lauf Carbonara fork</t>
+          <t>SRAM GX Eagle Transmission Upgrade Kit</t>
         </is>
       <